--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF84B81D-0959-4764-BF92-275F0CAB14FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD60592F-1094-4E69-8DDF-CFFC5FB8D43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -56,19 +45,88 @@
     <t xml:space="preserve">Modelo/Descrição </t>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 24.09.2025</t>
+    <t xml:space="preserve">Anexo </t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 27.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 27.10.2025</t>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>135126805</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 28.10.2025</t>
+  </si>
+  <si>
+    <t>135126971</t>
+  </si>
+  <si>
+    <t>135127549</t>
+  </si>
+  <si>
+    <t>135127725</t>
+  </si>
+  <si>
+    <t>135134543</t>
+  </si>
+  <si>
+    <t>135129319</t>
+  </si>
+  <si>
+    <t>135129524</t>
+  </si>
+  <si>
+    <t>135129711</t>
+  </si>
+  <si>
+    <t>135130064</t>
+  </si>
+  <si>
+    <t>135132669</t>
+  </si>
+  <si>
+    <t>135133308</t>
+  </si>
+  <si>
+    <t>135134566</t>
+  </si>
+  <si>
+    <t>135134993</t>
+  </si>
+  <si>
+    <t>135138411</t>
+  </si>
+  <si>
+    <t>135143191</t>
+  </si>
+  <si>
+    <t>135141290</t>
+  </si>
+  <si>
+    <t>135142378</t>
+  </si>
+  <si>
+    <t>135144911</t>
+  </si>
+  <si>
+    <t>135133913</t>
+  </si>
+  <si>
+    <t>135133874</t>
+  </si>
+  <si>
+    <t>135134008</t>
+  </si>
+  <si>
+    <t>135139614</t>
+  </si>
+  <si>
+    <t>135144160</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 28.10.2025</t>
   </si>
 </sst>
 </file>
@@ -126,7 +184,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -134,26 +192,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -171,16 +214,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -500,7 +533,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +554,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -531,408 +564,418 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>135107753</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>135107899</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>135108509</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
-        <v>135111898</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>9</v>
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
-        <v>135111238</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>8</v>
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
-        <v>135122977</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>9</v>
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
-        <v>135115108</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>9</v>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
-        <v>135116803</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>9</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
-        <v>135115386</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
-        <v>135115503</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>9</v>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>135122036</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>8</v>
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
-        <v>135119301</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>9</v>
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
-        <v>135119758</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>9</v>
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
-        <v>135120194</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>9</v>
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
-        <v>135120998</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>9</v>
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
-        <v>135121252</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
-        <v>135121086</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
-        <v>135122286</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
-        <v>135123403</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>135121481</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="9"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="6"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD60592F-1094-4E69-8DDF-CFFC5FB8D43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1CE04F-C75D-4829-A80B-D3C4AE1E12BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,82 +51,100 @@
     <t>971</t>
   </si>
   <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>135126805</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 28.10.2025</t>
-  </si>
-  <si>
-    <t>135126971</t>
-  </si>
-  <si>
-    <t>135127549</t>
-  </si>
-  <si>
-    <t>135127725</t>
-  </si>
-  <si>
-    <t>135134543</t>
-  </si>
-  <si>
-    <t>135129319</t>
-  </si>
-  <si>
-    <t>135129524</t>
-  </si>
-  <si>
-    <t>135129711</t>
-  </si>
-  <si>
-    <t>135130064</t>
-  </si>
-  <si>
-    <t>135132669</t>
-  </si>
-  <si>
-    <t>135133308</t>
-  </si>
-  <si>
-    <t>135134566</t>
-  </si>
-  <si>
-    <t>135134993</t>
-  </si>
-  <si>
-    <t>135138411</t>
-  </si>
-  <si>
-    <t>135143191</t>
-  </si>
-  <si>
-    <t>135141290</t>
-  </si>
-  <si>
-    <t>135142378</t>
-  </si>
-  <si>
-    <t>135144911</t>
-  </si>
-  <si>
-    <t>135133913</t>
-  </si>
-  <si>
-    <t>135133874</t>
-  </si>
-  <si>
-    <t>135134008</t>
-  </si>
-  <si>
-    <t>135139614</t>
-  </si>
-  <si>
-    <t>135144160</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 28.10.2025</t>
+    <t>135146718</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 29.10.2025</t>
+  </si>
+  <si>
+    <t>135160236</t>
+  </si>
+  <si>
+    <t>135160317</t>
+  </si>
+  <si>
+    <t>135147930</t>
+  </si>
+  <si>
+    <t>135149229</t>
+  </si>
+  <si>
+    <t>135152670</t>
+  </si>
+  <si>
+    <t>135149696</t>
+  </si>
+  <si>
+    <t>135149602</t>
+  </si>
+  <si>
+    <t>135151554</t>
+  </si>
+  <si>
+    <t>135156400</t>
+  </si>
+  <si>
+    <t>135157511</t>
+  </si>
+  <si>
+    <t>135157976</t>
+  </si>
+  <si>
+    <t>135160493</t>
+  </si>
+  <si>
+    <t>135163674</t>
+  </si>
+  <si>
+    <t>135162768</t>
+  </si>
+  <si>
+    <t>132512956</t>
+  </si>
+  <si>
+    <t>135162573</t>
+  </si>
+  <si>
+    <t>135162937</t>
+  </si>
+  <si>
+    <t>135163218</t>
+  </si>
+  <si>
+    <t>135163557</t>
+  </si>
+  <si>
+    <t>135163670</t>
+  </si>
+  <si>
+    <t>135153707</t>
+  </si>
+  <si>
+    <t>135149819</t>
+  </si>
+  <si>
+    <t>135147449</t>
+  </si>
+  <si>
+    <t>135148265</t>
+  </si>
+  <si>
+    <t>135149751</t>
+  </si>
+  <si>
+    <t>135152033</t>
+  </si>
+  <si>
+    <t>135152575</t>
+  </si>
+  <si>
+    <t>135153669</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 29.10.2025</t>
+  </si>
+  <si>
+    <t>Processar</t>
   </si>
 </sst>
 </file>
@@ -533,7 +551,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -565,417 +583,519 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24"/>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -991,31 +1111,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1CE04F-C75D-4829-A80B-D3C4AE1E12BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46817A3-4257-41DA-8336-6D249DE7B810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,100 +51,94 @@
     <t>971</t>
   </si>
   <si>
-    <t>135146718</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 29.10.2025</t>
-  </si>
-  <si>
-    <t>135160236</t>
-  </si>
-  <si>
-    <t>135160317</t>
-  </si>
-  <si>
-    <t>135147930</t>
-  </si>
-  <si>
-    <t>135149229</t>
-  </si>
-  <si>
-    <t>135152670</t>
-  </si>
-  <si>
-    <t>135149696</t>
-  </si>
-  <si>
-    <t>135149602</t>
-  </si>
-  <si>
-    <t>135151554</t>
-  </si>
-  <si>
-    <t>135156400</t>
-  </si>
-  <si>
-    <t>135157511</t>
-  </si>
-  <si>
-    <t>135157976</t>
-  </si>
-  <si>
-    <t>135160493</t>
-  </si>
-  <si>
-    <t>135163674</t>
-  </si>
-  <si>
-    <t>135162768</t>
-  </si>
-  <si>
-    <t>132512956</t>
-  </si>
-  <si>
-    <t>135162573</t>
-  </si>
-  <si>
-    <t>135162937</t>
-  </si>
-  <si>
-    <t>135163218</t>
-  </si>
-  <si>
-    <t>135163557</t>
-  </si>
-  <si>
-    <t>135163670</t>
-  </si>
-  <si>
-    <t>135153707</t>
-  </si>
-  <si>
-    <t>135149819</t>
-  </si>
-  <si>
-    <t>135147449</t>
-  </si>
-  <si>
-    <t>135148265</t>
-  </si>
-  <si>
-    <t>135149751</t>
-  </si>
-  <si>
-    <t>135152033</t>
-  </si>
-  <si>
-    <t>135152575</t>
-  </si>
-  <si>
-    <t>135153669</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 29.10.2025</t>
-  </si>
-  <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>135165708</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 30.10.2025</t>
+  </si>
+  <si>
+    <t>135165760</t>
+  </si>
+  <si>
+    <t>135165908</t>
+  </si>
+  <si>
+    <t>135165797</t>
+  </si>
+  <si>
+    <t>135167137</t>
+  </si>
+  <si>
+    <t>135167079</t>
+  </si>
+  <si>
+    <t>135167656</t>
+  </si>
+  <si>
+    <t>135178040</t>
+  </si>
+  <si>
+    <t>135169382</t>
+  </si>
+  <si>
+    <t>135172343</t>
+  </si>
+  <si>
+    <t>135172570</t>
+  </si>
+  <si>
+    <t>135174185</t>
+  </si>
+  <si>
+    <t>135174345</t>
+  </si>
+  <si>
+    <t>135182654</t>
+  </si>
+  <si>
+    <t>135176038</t>
+  </si>
+  <si>
+    <t>135180305</t>
+  </si>
+  <si>
+    <t>135177561</t>
+  </si>
+  <si>
+    <t>135180980</t>
+  </si>
+  <si>
+    <t>135181363</t>
+  </si>
+  <si>
+    <t>135180917</t>
+  </si>
+  <si>
+    <t>135181306</t>
+  </si>
+  <si>
+    <t>135181056</t>
+  </si>
+  <si>
+    <t>135181115</t>
+  </si>
+  <si>
+    <t>135181926</t>
+  </si>
+  <si>
+    <t>135183029</t>
+  </si>
+  <si>
+    <t>135170351</t>
+  </si>
+  <si>
+    <t>135172128</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 30.10.2025</t>
   </si>
 </sst>
 </file>
@@ -551,7 +545,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -583,518 +577,484 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1111,31 +1071,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46817A3-4257-41DA-8336-6D249DE7B810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D610686-157D-4B01-B05C-6EABEA8769D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="44">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,112 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>135165708</t>
-  </si>
-  <si>
     <t>Bloqueios Honda 30.10.2025</t>
   </si>
   <si>
-    <t>135165760</t>
-  </si>
-  <si>
-    <t>135165908</t>
-  </si>
-  <si>
-    <t>135165797</t>
-  </si>
-  <si>
-    <t>135167137</t>
-  </si>
-  <si>
-    <t>135167079</t>
-  </si>
-  <si>
-    <t>135167656</t>
-  </si>
-  <si>
-    <t>135178040</t>
-  </si>
-  <si>
-    <t>135169382</t>
-  </si>
-  <si>
-    <t>135172343</t>
-  </si>
-  <si>
-    <t>135172570</t>
-  </si>
-  <si>
-    <t>135174185</t>
-  </si>
-  <si>
-    <t>135174345</t>
-  </si>
-  <si>
-    <t>135182654</t>
-  </si>
-  <si>
-    <t>135176038</t>
-  </si>
-  <si>
-    <t>135180305</t>
-  </si>
-  <si>
-    <t>135177561</t>
-  </si>
-  <si>
-    <t>135180980</t>
-  </si>
-  <si>
-    <t>135181363</t>
-  </si>
-  <si>
-    <t>135180917</t>
-  </si>
-  <si>
-    <t>135181306</t>
-  </si>
-  <si>
-    <t>135181056</t>
-  </si>
-  <si>
-    <t>135181115</t>
-  </si>
-  <si>
-    <t>135181926</t>
-  </si>
-  <si>
-    <t>135183029</t>
-  </si>
-  <si>
-    <t>135170351</t>
-  </si>
-  <si>
-    <t>135172128</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 30.10.2025</t>
+    <t>135187384</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 31.10.2025</t>
+  </si>
+  <si>
+    <t>135187780</t>
+  </si>
+  <si>
+    <t>135190315</t>
+  </si>
+  <si>
+    <t>135191370</t>
+  </si>
+  <si>
+    <t>135191769</t>
+  </si>
+  <si>
+    <t>135192168</t>
+  </si>
+  <si>
+    <t>135191635</t>
+  </si>
+  <si>
+    <t>135202849</t>
+  </si>
+  <si>
+    <t>135198080</t>
+  </si>
+  <si>
+    <t>135198342</t>
+  </si>
+  <si>
+    <t>135201880</t>
+  </si>
+  <si>
+    <t>135201510</t>
+  </si>
+  <si>
+    <t>135202378</t>
+  </si>
+  <si>
+    <t>135202144</t>
+  </si>
+  <si>
+    <t>135202418</t>
+  </si>
+  <si>
+    <t>135202968</t>
+  </si>
+  <si>
+    <t>135203083</t>
+  </si>
+  <si>
+    <t>135203790</t>
+  </si>
+  <si>
+    <t>135204253</t>
+  </si>
+  <si>
+    <t>135204285</t>
+  </si>
+  <si>
+    <t>135185869</t>
+  </si>
+  <si>
+    <t>135186895</t>
+  </si>
+  <si>
+    <t>135187761</t>
+  </si>
+  <si>
+    <t>135189335</t>
+  </si>
+  <si>
+    <t>135188444</t>
+  </si>
+  <si>
+    <t>135201557</t>
+  </si>
+  <si>
+    <t>135197373</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 31.10.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 01.11.2025</t>
+  </si>
+  <si>
+    <t>135204961</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 01.11.2025</t>
+  </si>
+  <si>
+    <t>135205083</t>
+  </si>
+  <si>
+    <t>135205202</t>
+  </si>
+  <si>
+    <t>135205483</t>
   </si>
 </sst>
 </file>
@@ -545,7 +566,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -577,16 +598,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -595,16 +616,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -613,16 +634,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -631,16 +652,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -649,16 +670,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -667,16 +688,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -685,16 +706,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -703,16 +724,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -721,16 +742,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -739,16 +760,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -757,16 +778,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -775,16 +796,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -793,16 +814,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -811,16 +832,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -829,16 +850,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -847,16 +868,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -865,16 +886,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -883,16 +904,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -901,16 +922,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -919,16 +940,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -937,16 +958,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -955,16 +976,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -973,16 +994,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -991,16 +1012,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1008,16 +1029,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1025,16 +1046,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1042,18 +1063,86 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D610686-157D-4B01-B05C-6EABEA8769D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54FC34E-5E6A-47D3-81F9-7971540836E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,112 +54,76 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Bloqueios Honda 30.10.2025</t>
-  </si>
-  <si>
-    <t>135187384</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 31.10.2025</t>
-  </si>
-  <si>
-    <t>135187780</t>
-  </si>
-  <si>
-    <t>135190315</t>
-  </si>
-  <si>
-    <t>135191370</t>
-  </si>
-  <si>
-    <t>135191769</t>
-  </si>
-  <si>
-    <t>135192168</t>
-  </si>
-  <si>
-    <t>135191635</t>
-  </si>
-  <si>
-    <t>135202849</t>
-  </si>
-  <si>
-    <t>135198080</t>
-  </si>
-  <si>
-    <t>135198342</t>
-  </si>
-  <si>
-    <t>135201880</t>
-  </si>
-  <si>
-    <t>135201510</t>
-  </si>
-  <si>
-    <t>135202378</t>
-  </si>
-  <si>
-    <t>135202144</t>
-  </si>
-  <si>
-    <t>135202418</t>
-  </si>
-  <si>
-    <t>135202968</t>
-  </si>
-  <si>
-    <t>135203083</t>
-  </si>
-  <si>
-    <t>135203790</t>
-  </si>
-  <si>
-    <t>135204253</t>
-  </si>
-  <si>
-    <t>135204285</t>
-  </si>
-  <si>
-    <t>135185869</t>
-  </si>
-  <si>
-    <t>135186895</t>
-  </si>
-  <si>
-    <t>135187761</t>
-  </si>
-  <si>
-    <t>135189335</t>
-  </si>
-  <si>
-    <t>135188444</t>
-  </si>
-  <si>
-    <t>135201557</t>
-  </si>
-  <si>
-    <t>135197373</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 31.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 01.11.2025</t>
-  </si>
-  <si>
-    <t>135204961</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 01.11.2025</t>
-  </si>
-  <si>
-    <t>135205083</t>
-  </si>
-  <si>
-    <t>135205202</t>
-  </si>
-  <si>
-    <t>135205483</t>
+    <t>135207160</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 03/11/2025</t>
+  </si>
+  <si>
+    <t>135207535</t>
+  </si>
+  <si>
+    <t>135208117</t>
+  </si>
+  <si>
+    <t>135217247</t>
+  </si>
+  <si>
+    <t>135211287</t>
+  </si>
+  <si>
+    <t>135217226</t>
+  </si>
+  <si>
+    <t>135219632</t>
+  </si>
+  <si>
+    <t>135218290</t>
+  </si>
+  <si>
+    <t>135219652</t>
+  </si>
+  <si>
+    <t>135220531</t>
+  </si>
+  <si>
+    <t>135220839</t>
+  </si>
+  <si>
+    <t>135224127</t>
+  </si>
+  <si>
+    <t>135219978</t>
+  </si>
+  <si>
+    <t>135210576</t>
+  </si>
+  <si>
+    <t>135212914</t>
+  </si>
+  <si>
+    <t>135212408</t>
+  </si>
+  <si>
+    <t>135212289</t>
+  </si>
+  <si>
+    <t>135213274</t>
+  </si>
+  <si>
+    <t>135214607</t>
+  </si>
+  <si>
+    <t>135215894</t>
+  </si>
+  <si>
+    <t>135216935</t>
+  </si>
+  <si>
+    <t>135219788</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 03.11.2025</t>
   </si>
 </sst>
 </file>
@@ -566,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -598,16 +562,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -616,16 +580,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -634,16 +598,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -652,16 +616,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -670,16 +634,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -688,16 +652,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -706,16 +670,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -724,16 +688,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -742,16 +706,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -760,16 +724,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -778,16 +742,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -796,16 +760,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -814,16 +778,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -832,16 +796,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -850,16 +814,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -868,16 +832,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -886,16 +850,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -904,16 +868,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -922,16 +886,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -940,16 +904,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -958,16 +922,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -976,175 +940,21 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1160,31 +970,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54FC34E-5E6A-47D3-81F9-7971540836E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D8815C-675B-4E07-9D23-3B04B675F264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="58">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,76 +54,154 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>135207160</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 03/11/2025</t>
-  </si>
-  <si>
-    <t>135207535</t>
-  </si>
-  <si>
-    <t>135208117</t>
-  </si>
-  <si>
-    <t>135217247</t>
-  </si>
-  <si>
-    <t>135211287</t>
-  </si>
-  <si>
-    <t>135217226</t>
-  </si>
-  <si>
-    <t>135219632</t>
-  </si>
-  <si>
-    <t>135218290</t>
-  </si>
-  <si>
-    <t>135219652</t>
-  </si>
-  <si>
-    <t>135220531</t>
-  </si>
-  <si>
-    <t>135220839</t>
-  </si>
-  <si>
-    <t>135224127</t>
-  </si>
-  <si>
-    <t>135219978</t>
-  </si>
-  <si>
-    <t>135210576</t>
-  </si>
-  <si>
-    <t>135212914</t>
-  </si>
-  <si>
-    <t>135212408</t>
-  </si>
-  <si>
-    <t>135212289</t>
-  </si>
-  <si>
-    <t>135213274</t>
-  </si>
-  <si>
-    <t>135214607</t>
-  </si>
-  <si>
-    <t>135215894</t>
-  </si>
-  <si>
-    <t>135216935</t>
-  </si>
-  <si>
-    <t>135219788</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 03.11.2025</t>
+    <t>135228356</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 04/11/2025</t>
+  </si>
+  <si>
+    <t>135229109</t>
+  </si>
+  <si>
+    <t>135229790</t>
+  </si>
+  <si>
+    <t>135230430</t>
+  </si>
+  <si>
+    <t>135234776</t>
+  </si>
+  <si>
+    <t>135231458</t>
+  </si>
+  <si>
+    <t>135233641</t>
+  </si>
+  <si>
+    <t>135233300</t>
+  </si>
+  <si>
+    <t>135237278</t>
+  </si>
+  <si>
+    <t>135236616</t>
+  </si>
+  <si>
+    <t>135226876</t>
+  </si>
+  <si>
+    <t>135236518</t>
+  </si>
+  <si>
+    <t>135239283</t>
+  </si>
+  <si>
+    <t>135240026</t>
+  </si>
+  <si>
+    <t>135242379</t>
+  </si>
+  <si>
+    <t>135243050</t>
+  </si>
+  <si>
+    <t>135243831</t>
+  </si>
+  <si>
+    <t>135243577</t>
+  </si>
+  <si>
+    <t>135227018</t>
+  </si>
+  <si>
+    <t>135227350</t>
+  </si>
+  <si>
+    <t>135227855</t>
+  </si>
+  <si>
+    <t>135230166</t>
+  </si>
+  <si>
+    <t>135229976</t>
+  </si>
+  <si>
+    <t>135232024</t>
+  </si>
+  <si>
+    <t>135232512</t>
+  </si>
+  <si>
+    <t>135232618</t>
+  </si>
+  <si>
+    <t>135236074</t>
+  </si>
+  <si>
+    <t>135241464</t>
+  </si>
+  <si>
+    <t>135241989</t>
+  </si>
+  <si>
+    <t>Bloqueadas 04.11.25 - Honda</t>
+  </si>
+  <si>
+    <t>135247592</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 05/11/2025</t>
+  </si>
+  <si>
+    <t>135249519</t>
+  </si>
+  <si>
+    <t>135252514</t>
+  </si>
+  <si>
+    <t>135253228</t>
+  </si>
+  <si>
+    <t>135265596</t>
+  </si>
+  <si>
+    <t>135258508</t>
+  </si>
+  <si>
+    <t>135258755</t>
+  </si>
+  <si>
+    <t>135259875</t>
+  </si>
+  <si>
+    <t>135260328</t>
+  </si>
+  <si>
+    <t>135265007</t>
+  </si>
+  <si>
+    <t>135264010</t>
+  </si>
+  <si>
+    <t>135247300</t>
+  </si>
+  <si>
+    <t>135260890</t>
+  </si>
+  <si>
+    <t>135247955</t>
+  </si>
+  <si>
+    <t>135249634</t>
+  </si>
+  <si>
+    <t>135250845</t>
+  </si>
+  <si>
+    <t>135253077</t>
+  </si>
+  <si>
+    <t>Bloqueio Honda 05.11.25</t>
   </si>
 </sst>
 </file>
@@ -530,7 +608,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -589,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -607,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -625,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -643,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -661,7 +739,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -679,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -697,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -715,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -733,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -751,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -769,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -787,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -805,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -823,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -841,7 +919,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -859,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -877,7 +955,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -895,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -913,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -931,7 +1009,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -949,12 +1027,420 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23"/>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634BC534-83F0-4F0B-A292-058B0A9B86DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5527B62-3161-4064-A57F-6F4EED623AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -48,52 +48,94 @@
     <t xml:space="preserve">Anexo </t>
   </si>
   <si>
+    <t>Processar</t>
+  </si>
+  <si>
+    <t>135313027</t>
+  </si>
+  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
-    <t>135268699</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 06/11/2025</t>
-  </si>
-  <si>
-    <t>135272486</t>
-  </si>
-  <si>
-    <t>135283574</t>
-  </si>
-  <si>
-    <t>135280763</t>
-  </si>
-  <si>
-    <t>135276037</t>
-  </si>
-  <si>
-    <t>135276156</t>
-  </si>
-  <si>
-    <t>135279157</t>
-  </si>
-  <si>
-    <t>135280612</t>
-  </si>
-  <si>
-    <t>135282213</t>
-  </si>
-  <si>
-    <t>135283702</t>
-  </si>
-  <si>
-    <t>135284792</t>
-  </si>
-  <si>
-    <t>135285248</t>
-  </si>
-  <si>
-    <t>Bloqueio Honda 06.11.25</t>
+    <t>Bloqueios Honda 08/11/2025</t>
+  </si>
+  <si>
+    <t>135313171</t>
+  </si>
+  <si>
+    <t>135313396</t>
+  </si>
+  <si>
+    <t>135313587</t>
+  </si>
+  <si>
+    <t>135313595</t>
+  </si>
+  <si>
+    <t>135313642</t>
+  </si>
+  <si>
+    <t>135313720</t>
+  </si>
+  <si>
+    <t>135313818</t>
+  </si>
+  <si>
+    <t>Bloqueadas 08.11.25 - Honda</t>
+  </si>
+  <si>
+    <t>135289648</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 07/11/2025</t>
+  </si>
+  <si>
+    <t>135290514</t>
+  </si>
+  <si>
+    <t>135290747</t>
+  </si>
+  <si>
+    <t>135307135</t>
+  </si>
+  <si>
+    <t>135299128</t>
+  </si>
+  <si>
+    <t>135305617</t>
+  </si>
+  <si>
+    <t>135306709</t>
+  </si>
+  <si>
+    <t>135307220</t>
+  </si>
+  <si>
+    <t>135307601</t>
+  </si>
+  <si>
+    <t>135307291</t>
+  </si>
+  <si>
+    <t>135309468</t>
+  </si>
+  <si>
+    <t>135310075</t>
+  </si>
+  <si>
+    <t>135293118</t>
+  </si>
+  <si>
+    <t>135294661</t>
+  </si>
+  <si>
+    <t>135297947</t>
+  </si>
+  <si>
+    <t>135299824</t>
+  </si>
+  <si>
+    <t>Bloqueadas 07.11.25 - Honda</t>
   </si>
 </sst>
 </file>
@@ -500,7 +542,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -532,19 +574,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2"/>
     </row>
@@ -553,16 +595,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3"/>
     </row>
@@ -571,16 +613,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4"/>
     </row>
@@ -589,16 +631,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5"/>
     </row>
@@ -607,16 +649,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6"/>
     </row>
@@ -625,16 +667,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7"/>
     </row>
@@ -643,16 +685,16 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8"/>
     </row>
@@ -661,90 +703,294 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -760,31 +1006,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5527B62-3161-4064-A57F-6F4EED623AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4F27A6-EF19-43CE-82C5-8D597F84BC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,91 +51,55 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>135313027</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 08/11/2025</t>
-  </si>
-  <si>
-    <t>135313171</t>
-  </si>
-  <si>
-    <t>135313396</t>
-  </si>
-  <si>
-    <t>135313587</t>
-  </si>
-  <si>
-    <t>135313595</t>
-  </si>
-  <si>
-    <t>135313642</t>
-  </si>
-  <si>
-    <t>135313720</t>
-  </si>
-  <si>
-    <t>135313818</t>
-  </si>
-  <si>
-    <t>Bloqueadas 08.11.25 - Honda</t>
-  </si>
-  <si>
-    <t>135289648</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 07/11/2025</t>
-  </si>
-  <si>
-    <t>135290514</t>
-  </si>
-  <si>
-    <t>135290747</t>
-  </si>
-  <si>
-    <t>135307135</t>
-  </si>
-  <si>
-    <t>135299128</t>
-  </si>
-  <si>
-    <t>135305617</t>
-  </si>
-  <si>
-    <t>135306709</t>
-  </si>
-  <si>
-    <t>135307220</t>
-  </si>
-  <si>
-    <t>135307601</t>
-  </si>
-  <si>
-    <t>135307291</t>
-  </si>
-  <si>
-    <t>135309468</t>
-  </si>
-  <si>
-    <t>135310075</t>
-  </si>
-  <si>
-    <t>135293118</t>
-  </si>
-  <si>
-    <t>135294661</t>
-  </si>
-  <si>
-    <t>135297947</t>
-  </si>
-  <si>
-    <t>135299824</t>
-  </si>
-  <si>
-    <t>Bloqueadas 07.11.25 - Honda</t>
+    <t>135318499</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 10/11/2025</t>
+  </si>
+  <si>
+    <t>135317699</t>
+  </si>
+  <si>
+    <t>135318337</t>
+  </si>
+  <si>
+    <t>135320997</t>
+  </si>
+  <si>
+    <t>135322656</t>
+  </si>
+  <si>
+    <t>135322713</t>
+  </si>
+  <si>
+    <t>135322740</t>
+  </si>
+  <si>
+    <t>135325693</t>
+  </si>
+  <si>
+    <t>135331430</t>
+  </si>
+  <si>
+    <t>135332883</t>
+  </si>
+  <si>
+    <t>135320998</t>
+  </si>
+  <si>
+    <t>135316125</t>
+  </si>
+  <si>
+    <t>135317638</t>
+  </si>
+  <si>
+    <t>135317259</t>
+  </si>
+  <si>
+    <t>Bloqueadas 10.11.25 - Honda</t>
   </si>
 </sst>
 </file>
@@ -542,7 +506,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -574,16 +538,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,13 +559,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,13 +577,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,13 +595,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,13 +613,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,13 +631,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,13 +649,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,13 +667,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -718,16 +682,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -736,16 +700,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -754,16 +718,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -772,16 +736,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -790,16 +754,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -807,188 +771,18 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1006,31 +800,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4F27A6-EF19-43CE-82C5-8D597F84BC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF458CFC-3D94-4983-AE2A-8F5E9DDE4686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="25">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,52 +54,55 @@
     <t>971</t>
   </si>
   <si>
-    <t>135318499</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 10/11/2025</t>
-  </si>
-  <si>
-    <t>135317699</t>
-  </si>
-  <si>
-    <t>135318337</t>
-  </si>
-  <si>
-    <t>135320997</t>
-  </si>
-  <si>
-    <t>135322656</t>
-  </si>
-  <si>
-    <t>135322713</t>
-  </si>
-  <si>
-    <t>135322740</t>
-  </si>
-  <si>
-    <t>135325693</t>
-  </si>
-  <si>
-    <t>135331430</t>
-  </si>
-  <si>
-    <t>135332883</t>
-  </si>
-  <si>
-    <t>135320998</t>
-  </si>
-  <si>
-    <t>135316125</t>
-  </si>
-  <si>
-    <t>135317638</t>
-  </si>
-  <si>
-    <t>135317259</t>
-  </si>
-  <si>
-    <t>Bloqueadas 10.11.25 - Honda</t>
+    <t>135336315</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 11/11/2025</t>
+  </si>
+  <si>
+    <t>135336344</t>
+  </si>
+  <si>
+    <t>135338935</t>
+  </si>
+  <si>
+    <t>135341777</t>
+  </si>
+  <si>
+    <t>135344162</t>
+  </si>
+  <si>
+    <t>135349787</t>
+  </si>
+  <si>
+    <t>135351227</t>
+  </si>
+  <si>
+    <t>135351911</t>
+  </si>
+  <si>
+    <t>135349683</t>
+  </si>
+  <si>
+    <t>135335834</t>
+  </si>
+  <si>
+    <t>135336776</t>
+  </si>
+  <si>
+    <t>135337444</t>
+  </si>
+  <si>
+    <t>135340093</t>
+  </si>
+  <si>
+    <t>135340216</t>
+  </si>
+  <si>
+    <t>135349919</t>
+  </si>
+  <si>
+    <t>BLOQUEIO HONDA 11.11.2025</t>
   </si>
 </sst>
 </file>
@@ -506,7 +509,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -547,7 +550,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -565,7 +568,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -583,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -601,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -619,7 +622,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -637,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -655,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -673,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -691,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -709,7 +712,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -727,7 +730,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -745,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -763,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -780,9 +783,26 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -800,31 +820,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF458CFC-3D94-4983-AE2A-8F5E9DDE4686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725C4203-67A5-4DDA-92B3-A246F30B36AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,55 +54,55 @@
     <t>971</t>
   </si>
   <si>
-    <t>135336315</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 11/11/2025</t>
-  </si>
-  <si>
-    <t>135336344</t>
-  </si>
-  <si>
-    <t>135338935</t>
-  </si>
-  <si>
-    <t>135341777</t>
-  </si>
-  <si>
-    <t>135344162</t>
-  </si>
-  <si>
-    <t>135349787</t>
-  </si>
-  <si>
-    <t>135351227</t>
-  </si>
-  <si>
-    <t>135351911</t>
-  </si>
-  <si>
-    <t>135349683</t>
-  </si>
-  <si>
-    <t>135335834</t>
-  </si>
-  <si>
-    <t>135336776</t>
-  </si>
-  <si>
-    <t>135337444</t>
-  </si>
-  <si>
-    <t>135340093</t>
-  </si>
-  <si>
-    <t>135340216</t>
-  </si>
-  <si>
-    <t>135349919</t>
-  </si>
-  <si>
-    <t>BLOQUEIO HONDA 11.11.2025</t>
+    <t>135355715</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 12/11/2025</t>
+  </si>
+  <si>
+    <t>135356022</t>
+  </si>
+  <si>
+    <t>135356426</t>
+  </si>
+  <si>
+    <t>134634892</t>
+  </si>
+  <si>
+    <t>135360570</t>
+  </si>
+  <si>
+    <t>133214701</t>
+  </si>
+  <si>
+    <t>135359352</t>
+  </si>
+  <si>
+    <t>135364149</t>
+  </si>
+  <si>
+    <t>135364380</t>
+  </si>
+  <si>
+    <t>135365955</t>
+  </si>
+  <si>
+    <t>135369074</t>
+  </si>
+  <si>
+    <t>135369190</t>
+  </si>
+  <si>
+    <t>135370160</t>
+  </si>
+  <si>
+    <t>135370520</t>
+  </si>
+  <si>
+    <t>135361755</t>
+  </si>
+  <si>
+    <t>Bloqueados 12.11.2025 HONDA</t>
   </si>
 </sst>
 </file>
@@ -820,31 +820,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725C4203-67A5-4DDA-92B3-A246F30B36AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B09196C-7718-4533-A08C-BA0145600F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,55 +54,58 @@
     <t>971</t>
   </si>
   <si>
-    <t>135355715</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 12/11/2025</t>
-  </si>
-  <si>
-    <t>135356022</t>
-  </si>
-  <si>
-    <t>135356426</t>
-  </si>
-  <si>
-    <t>134634892</t>
-  </si>
-  <si>
-    <t>135360570</t>
-  </si>
-  <si>
-    <t>133214701</t>
-  </si>
-  <si>
-    <t>135359352</t>
-  </si>
-  <si>
-    <t>135364149</t>
-  </si>
-  <si>
-    <t>135364380</t>
-  </si>
-  <si>
-    <t>135365955</t>
-  </si>
-  <si>
-    <t>135369074</t>
-  </si>
-  <si>
-    <t>135369190</t>
-  </si>
-  <si>
-    <t>135370160</t>
-  </si>
-  <si>
-    <t>135370520</t>
-  </si>
-  <si>
-    <t>135361755</t>
-  </si>
-  <si>
-    <t>Bloqueados 12.11.2025 HONDA</t>
+    <t>133118221</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 13/11/2025</t>
+  </si>
+  <si>
+    <t>135376570</t>
+  </si>
+  <si>
+    <t>135385858</t>
+  </si>
+  <si>
+    <t>135382149</t>
+  </si>
+  <si>
+    <t>135387312</t>
+  </si>
+  <si>
+    <t>135387671</t>
+  </si>
+  <si>
+    <t>135391788</t>
+  </si>
+  <si>
+    <t>135374694</t>
+  </si>
+  <si>
+    <t>135374812</t>
+  </si>
+  <si>
+    <t>135375296</t>
+  </si>
+  <si>
+    <t>135383281</t>
+  </si>
+  <si>
+    <t>135384090</t>
+  </si>
+  <si>
+    <t>133294325</t>
+  </si>
+  <si>
+    <t>135380476</t>
+  </si>
+  <si>
+    <t>135381503</t>
+  </si>
+  <si>
+    <t>135382934</t>
+  </si>
+  <si>
+    <t>Bloqueados 13.11.2025 HONDA</t>
   </si>
 </sst>
 </file>
@@ -509,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -550,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -568,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -586,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -604,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -622,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -640,7 +643,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -658,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -676,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -694,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -712,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -730,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -748,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -766,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -783,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -800,9 +803,26 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -820,31 +840,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B09196C-7718-4533-A08C-BA0145600F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B04679-2F06-4AB1-92BA-456228CE52DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,58 +54,55 @@
     <t>971</t>
   </si>
   <si>
-    <t>133118221</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 13/11/2025</t>
-  </si>
-  <si>
-    <t>135376570</t>
-  </si>
-  <si>
-    <t>135385858</t>
-  </si>
-  <si>
-    <t>135382149</t>
-  </si>
-  <si>
-    <t>135387312</t>
-  </si>
-  <si>
-    <t>135387671</t>
-  </si>
-  <si>
-    <t>135391788</t>
-  </si>
-  <si>
-    <t>135374694</t>
-  </si>
-  <si>
-    <t>135374812</t>
-  </si>
-  <si>
-    <t>135375296</t>
-  </si>
-  <si>
-    <t>135383281</t>
-  </si>
-  <si>
-    <t>135384090</t>
-  </si>
-  <si>
-    <t>133294325</t>
-  </si>
-  <si>
-    <t>135380476</t>
-  </si>
-  <si>
-    <t>135381503</t>
-  </si>
-  <si>
-    <t>135382934</t>
-  </si>
-  <si>
-    <t>Bloqueados 13.11.2025 HONDA</t>
+    <t>135415185</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 15/11/2025</t>
+  </si>
+  <si>
+    <t>Bloqueadas 15.11.25 - Honda</t>
+  </si>
+  <si>
+    <t>135396902</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 14/11/2025</t>
+  </si>
+  <si>
+    <t>135397654</t>
+  </si>
+  <si>
+    <t>135403536</t>
+  </si>
+  <si>
+    <t>135400948</t>
+  </si>
+  <si>
+    <t>135401369</t>
+  </si>
+  <si>
+    <t>135406362</t>
+  </si>
+  <si>
+    <t>135404757</t>
+  </si>
+  <si>
+    <t>135407004</t>
+  </si>
+  <si>
+    <t>135412067</t>
+  </si>
+  <si>
+    <t>135407772</t>
+  </si>
+  <si>
+    <t>135410719</t>
+  </si>
+  <si>
+    <t>135410755</t>
+  </si>
+  <si>
+    <t>Bloqueadas 14.11.25 - Honda</t>
   </si>
 </sst>
 </file>
@@ -512,7 +509,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -553,7 +550,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -562,16 +559,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -580,16 +577,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -598,16 +595,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -616,16 +613,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -634,16 +631,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -652,16 +649,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -670,16 +667,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -688,16 +685,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -706,16 +703,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -724,16 +721,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -742,16 +739,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -760,69 +757,18 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B04679-2F06-4AB1-92BA-456228CE52DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4178DE-18F9-4A26-8099-F70915F14713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="80">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,55 +54,220 @@
     <t>971</t>
   </si>
   <si>
-    <t>135415185</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 15/11/2025</t>
-  </si>
-  <si>
-    <t>Bloqueadas 15.11.25 - Honda</t>
-  </si>
-  <si>
-    <t>135396902</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 14/11/2025</t>
-  </si>
-  <si>
-    <t>135397654</t>
-  </si>
-  <si>
-    <t>135403536</t>
-  </si>
-  <si>
-    <t>135400948</t>
-  </si>
-  <si>
-    <t>135401369</t>
-  </si>
-  <si>
-    <t>135406362</t>
-  </si>
-  <si>
-    <t>135404757</t>
-  </si>
-  <si>
-    <t>135407004</t>
-  </si>
-  <si>
-    <t>135412067</t>
-  </si>
-  <si>
-    <t>135407772</t>
-  </si>
-  <si>
-    <t>135410719</t>
-  </si>
-  <si>
-    <t>135410755</t>
-  </si>
-  <si>
-    <t>Bloqueadas 14.11.25 - Honda</t>
+    <t>135221510</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 14/11/2025</t>
+  </si>
+  <si>
+    <t>135263800</t>
+  </si>
+  <si>
+    <t>135287207</t>
+  </si>
+  <si>
+    <t>135281063</t>
+  </si>
+  <si>
+    <t>135282367</t>
+  </si>
+  <si>
+    <t>135293095</t>
+  </si>
+  <si>
+    <t>135262233</t>
+  </si>
+  <si>
+    <t>131080088</t>
+  </si>
+  <si>
+    <t>135330565</t>
+  </si>
+  <si>
+    <t>135325691</t>
+  </si>
+  <si>
+    <t>135319962</t>
+  </si>
+  <si>
+    <t>135321443</t>
+  </si>
+  <si>
+    <t>135323320</t>
+  </si>
+  <si>
+    <t>135321250</t>
+  </si>
+  <si>
+    <t>135323047</t>
+  </si>
+  <si>
+    <t>135333394</t>
+  </si>
+  <si>
+    <t>135316045</t>
+  </si>
+  <si>
+    <t>135300342</t>
+  </si>
+  <si>
+    <t>135308037</t>
+  </si>
+  <si>
+    <t>135300192</t>
+  </si>
+  <si>
+    <t>135350435</t>
+  </si>
+  <si>
+    <t>135345296</t>
+  </si>
+  <si>
+    <t>135331405</t>
+  </si>
+  <si>
+    <t>135365432</t>
+  </si>
+  <si>
+    <t>135367671</t>
+  </si>
+  <si>
+    <t>135377037</t>
+  </si>
+  <si>
+    <t>135380112</t>
+  </si>
+  <si>
+    <t>135382360</t>
+  </si>
+  <si>
+    <t>135290629</t>
+  </si>
+  <si>
+    <t>135391601</t>
+  </si>
+  <si>
+    <t>135388823</t>
+  </si>
+  <si>
+    <t>135197451</t>
+  </si>
+  <si>
+    <t>135204216</t>
+  </si>
+  <si>
+    <t>135196907</t>
+  </si>
+  <si>
+    <t>135398027</t>
+  </si>
+  <si>
+    <t>135395880</t>
+  </si>
+  <si>
+    <t>135309279</t>
+  </si>
+  <si>
+    <t>132444484</t>
+  </si>
+  <si>
+    <t>135212284</t>
+  </si>
+  <si>
+    <t>135212304</t>
+  </si>
+  <si>
+    <t>135212771</t>
+  </si>
+  <si>
+    <t>135398869</t>
+  </si>
+  <si>
+    <t>135280741</t>
+  </si>
+  <si>
+    <t>135399604</t>
+  </si>
+  <si>
+    <t>135309586</t>
+  </si>
+  <si>
+    <t>135400515</t>
+  </si>
+  <si>
+    <t>135398238</t>
+  </si>
+  <si>
+    <t>135218134</t>
+  </si>
+  <si>
+    <t>135221567</t>
+  </si>
+  <si>
+    <t>135402656</t>
+  </si>
+  <si>
+    <t>135230036</t>
+  </si>
+  <si>
+    <t>135366618</t>
+  </si>
+  <si>
+    <t>135254531</t>
+  </si>
+  <si>
+    <t>135284046</t>
+  </si>
+  <si>
+    <t>135341800</t>
+  </si>
+  <si>
+    <t>135257127</t>
+  </si>
+  <si>
+    <t>135300111</t>
+  </si>
+  <si>
+    <t>135406440</t>
+  </si>
+  <si>
+    <t>135302389</t>
+  </si>
+  <si>
+    <t>135408322</t>
+  </si>
+  <si>
+    <t>135262676</t>
+  </si>
+  <si>
+    <t>135305579</t>
+  </si>
+  <si>
+    <t>135326308</t>
+  </si>
+  <si>
+    <t>135323049</t>
+  </si>
+  <si>
+    <t>135332271</t>
+  </si>
+  <si>
+    <t>135309477</t>
+  </si>
+  <si>
+    <t>135283214</t>
+  </si>
+  <si>
+    <t>135411477</t>
+  </si>
+  <si>
+    <t>135279658</t>
+  </si>
+  <si>
+    <t>135305825</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_14.11.2025</t>
   </si>
 </sst>
 </file>
@@ -172,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -191,6 +356,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +677,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -543,14 +711,14 @@
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -559,16 +727,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -577,16 +745,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -595,16 +763,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -613,16 +781,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -631,16 +799,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -649,16 +817,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -667,16 +835,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -685,16 +853,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -703,16 +871,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -721,16 +889,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -739,16 +907,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -757,18 +925,987 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -786,31 +1923,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD094B2B-7283-45EE-B90A-217E8FF2B37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A1F475-746E-4F68-96C8-5164F4219DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="28">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t>135453526</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -565,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -583,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -601,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -619,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -637,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -655,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -673,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -691,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -709,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -727,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -745,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -763,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -781,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -798,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -815,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -832,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -849,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -866,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -883,7 +880,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -903,31 +900,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A1F475-746E-4F68-96C8-5164F4219DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C385F2BD-844A-44CA-9174-24060BD1A7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -900,31 +900,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C385F2BD-844A-44CA-9174-24060BD1A7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E1021F-E016-47B7-BD52-7852905887BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>135453526</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -562,7 +565,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -580,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -598,7 +601,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -616,7 +619,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -634,7 +637,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -652,7 +655,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -670,7 +673,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -688,7 +691,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -706,7 +709,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -724,7 +727,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -742,7 +745,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -760,7 +763,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -778,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -795,7 +798,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -812,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -829,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -846,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -863,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -880,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -900,31 +903,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E1021F-E016-47B7-BD52-7852905887BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5788C7A-DF53-4A50-AD6A-E0AA6274BCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5788C7A-DF53-4A50-AD6A-E0AA6274BCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4931A2FD-A354-49A5-A851-185F130180DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,67 +54,58 @@
     <t>971</t>
   </si>
   <si>
-    <t>130964511</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 18.11.2025</t>
-  </si>
-  <si>
-    <t>135438959</t>
-  </si>
-  <si>
-    <t>135439729</t>
-  </si>
-  <si>
-    <t>135438590</t>
-  </si>
-  <si>
-    <t>135444710</t>
-  </si>
-  <si>
-    <t>135446005</t>
-  </si>
-  <si>
-    <t>135446789</t>
-  </si>
-  <si>
-    <t>135446284</t>
-  </si>
-  <si>
-    <t>135453390</t>
-  </si>
-  <si>
-    <t>135446829</t>
-  </si>
-  <si>
-    <t>135449007</t>
-  </si>
-  <si>
-    <t>135449394</t>
-  </si>
-  <si>
-    <t>135449948</t>
-  </si>
-  <si>
-    <t>135450368</t>
-  </si>
-  <si>
-    <t>135451939</t>
-  </si>
-  <si>
-    <t>135451562</t>
-  </si>
-  <si>
-    <t>135451706</t>
-  </si>
-  <si>
-    <t>135452639</t>
-  </si>
-  <si>
-    <t>135453526</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 18.11.2025</t>
+    <t>135471740</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 19.11.2025</t>
+  </si>
+  <si>
+    <t>135458665</t>
+  </si>
+  <si>
+    <t>135459645</t>
+  </si>
+  <si>
+    <t>135460116</t>
+  </si>
+  <si>
+    <t>135460848</t>
+  </si>
+  <si>
+    <t>135461468</t>
+  </si>
+  <si>
+    <t>135465841</t>
+  </si>
+  <si>
+    <t>135466753</t>
+  </si>
+  <si>
+    <t>135471785</t>
+  </si>
+  <si>
+    <t>135472493</t>
+  </si>
+  <si>
+    <t>135473759</t>
+  </si>
+  <si>
+    <t>135474681</t>
+  </si>
+  <si>
+    <t>135475701</t>
+  </si>
+  <si>
+    <t>135457896</t>
+  </si>
+  <si>
+    <t>135466896</t>
+  </si>
+  <si>
+    <t>135463815</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 19.11.2025</t>
   </si>
 </sst>
 </file>
@@ -524,7 +515,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -565,7 +556,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -583,7 +574,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -601,7 +592,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -619,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -637,7 +628,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -655,7 +646,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -673,7 +664,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -691,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -709,7 +700,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -727,7 +718,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -745,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -763,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -781,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -798,7 +789,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -815,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -832,60 +823,9 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4931A2FD-A354-49A5-A851-185F130180DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FECF35-8DA6-4AB2-A123-E377F537650C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,58 +54,79 @@
     <t>971</t>
   </si>
   <si>
-    <t>135471740</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 19.11.2025</t>
-  </si>
-  <si>
-    <t>135458665</t>
-  </si>
-  <si>
-    <t>135459645</t>
-  </si>
-  <si>
-    <t>135460116</t>
-  </si>
-  <si>
-    <t>135460848</t>
-  </si>
-  <si>
-    <t>135461468</t>
-  </si>
-  <si>
-    <t>135465841</t>
-  </si>
-  <si>
-    <t>135466753</t>
-  </si>
-  <si>
-    <t>135471785</t>
-  </si>
-  <si>
-    <t>135472493</t>
-  </si>
-  <si>
-    <t>135473759</t>
-  </si>
-  <si>
-    <t>135474681</t>
-  </si>
-  <si>
-    <t>135475701</t>
-  </si>
-  <si>
-    <t>135457896</t>
-  </si>
-  <si>
-    <t>135466896</t>
-  </si>
-  <si>
-    <t>135463815</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 19.11.2025</t>
+    <t>135503834</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 22.11.2025</t>
+  </si>
+  <si>
+    <t>135503937</t>
+  </si>
+  <si>
+    <t>135504053</t>
+  </si>
+  <si>
+    <t>135504037</t>
+  </si>
+  <si>
+    <t>135504405</t>
+  </si>
+  <si>
+    <t>135504616</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.11.2025</t>
+  </si>
+  <si>
+    <t>135496293</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 21.11.2025</t>
+  </si>
+  <si>
+    <t>135484355</t>
+  </si>
+  <si>
+    <t>135485335</t>
+  </si>
+  <si>
+    <t>135500247</t>
+  </si>
+  <si>
+    <t>135487683</t>
+  </si>
+  <si>
+    <t>135488057</t>
+  </si>
+  <si>
+    <t>135489285</t>
+  </si>
+  <si>
+    <t>135491004</t>
+  </si>
+  <si>
+    <t>135489680</t>
+  </si>
+  <si>
+    <t>135490341</t>
+  </si>
+  <si>
+    <t>133976404</t>
+  </si>
+  <si>
+    <t>135493651</t>
+  </si>
+  <si>
+    <t>135493694</t>
+  </si>
+  <si>
+    <t>133317110</t>
+  </si>
+  <si>
+    <t>135497002</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 21.11.2025</t>
   </si>
 </sst>
 </file>
@@ -515,7 +536,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -556,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -574,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -592,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -610,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -628,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -646,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -655,16 +676,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -673,16 +694,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -691,16 +712,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -709,16 +730,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -727,16 +748,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -745,16 +766,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -763,16 +784,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -780,16 +801,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -797,16 +818,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -814,18 +835,103 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FECF35-8DA6-4AB2-A123-E377F537650C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1101331E-C21D-4EBA-9F9D-D0AD20580090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,79 +54,79 @@
     <t>971</t>
   </si>
   <si>
-    <t>135503834</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 22.11.2025</t>
-  </si>
-  <si>
-    <t>135503937</t>
-  </si>
-  <si>
-    <t>135504053</t>
-  </si>
-  <si>
-    <t>135504037</t>
-  </si>
-  <si>
-    <t>135504405</t>
-  </si>
-  <si>
-    <t>135504616</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.11.2025</t>
-  </si>
-  <si>
-    <t>135496293</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 21.11.2025</t>
-  </si>
-  <si>
-    <t>135484355</t>
-  </si>
-  <si>
-    <t>135485335</t>
-  </si>
-  <si>
-    <t>135500247</t>
-  </si>
-  <si>
-    <t>135487683</t>
-  </si>
-  <si>
-    <t>135488057</t>
-  </si>
-  <si>
-    <t>135489285</t>
-  </si>
-  <si>
-    <t>135491004</t>
-  </si>
-  <si>
-    <t>135489680</t>
-  </si>
-  <si>
-    <t>135490341</t>
-  </si>
-  <si>
-    <t>133976404</t>
-  </si>
-  <si>
-    <t>135493651</t>
-  </si>
-  <si>
-    <t>135493694</t>
-  </si>
-  <si>
-    <t>133317110</t>
-  </si>
-  <si>
-    <t>135497002</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 21.11.2025</t>
+    <t>135506855</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 24.11.2025</t>
+  </si>
+  <si>
+    <t>135521866</t>
+  </si>
+  <si>
+    <t>135510604</t>
+  </si>
+  <si>
+    <t>135512631</t>
+  </si>
+  <si>
+    <t>135511193</t>
+  </si>
+  <si>
+    <t>135512902</t>
+  </si>
+  <si>
+    <t>135514601</t>
+  </si>
+  <si>
+    <t>135515183</t>
+  </si>
+  <si>
+    <t>135518215</t>
+  </si>
+  <si>
+    <t>135517168</t>
+  </si>
+  <si>
+    <t>135517446</t>
+  </si>
+  <si>
+    <t>135517430</t>
+  </si>
+  <si>
+    <t>135518264</t>
+  </si>
+  <si>
+    <t>135518871</t>
+  </si>
+  <si>
+    <t>135518894</t>
+  </si>
+  <si>
+    <t>135520190</t>
+  </si>
+  <si>
+    <t>135524202</t>
+  </si>
+  <si>
+    <t>135521217</t>
+  </si>
+  <si>
+    <t>135521592</t>
+  </si>
+  <si>
+    <t>135521872</t>
+  </si>
+  <si>
+    <t>135522301</t>
+  </si>
+  <si>
+    <t>135524083</t>
+  </si>
+  <si>
+    <t>135524988</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 24.11.2025</t>
   </si>
 </sst>
 </file>
@@ -536,7 +536,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -577,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -676,13 +676,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>32</v>
@@ -694,13 +694,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>32</v>
@@ -712,13 +712,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -730,13 +730,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>32</v>
@@ -748,13 +748,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>32</v>
@@ -766,13 +766,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>32</v>
@@ -784,13 +784,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>32</v>
@@ -801,13 +801,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>32</v>
@@ -818,13 +818,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>32</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>32</v>
@@ -852,13 +852,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>32</v>
@@ -869,13 +869,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>32</v>
@@ -886,13 +886,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>32</v>
@@ -903,13 +903,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>32</v>
@@ -920,18 +920,52 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -949,31 +983,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1101331E-C21D-4EBA-9F9D-D0AD20580090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5477579-629C-4661-AC13-08E2BDB7ADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,79 +54,70 @@
     <t>971</t>
   </si>
   <si>
-    <t>135506855</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 24.11.2025</t>
-  </si>
-  <si>
-    <t>135521866</t>
-  </si>
-  <si>
-    <t>135510604</t>
-  </si>
-  <si>
-    <t>135512631</t>
-  </si>
-  <si>
-    <t>135511193</t>
-  </si>
-  <si>
-    <t>135512902</t>
-  </si>
-  <si>
-    <t>135514601</t>
-  </si>
-  <si>
-    <t>135515183</t>
-  </si>
-  <si>
-    <t>135518215</t>
-  </si>
-  <si>
-    <t>135517168</t>
-  </si>
-  <si>
-    <t>135517446</t>
-  </si>
-  <si>
-    <t>135517430</t>
-  </si>
-  <si>
-    <t>135518264</t>
-  </si>
-  <si>
-    <t>135518871</t>
-  </si>
-  <si>
-    <t>135518894</t>
-  </si>
-  <si>
-    <t>135520190</t>
-  </si>
-  <si>
-    <t>135524202</t>
-  </si>
-  <si>
-    <t>135521217</t>
-  </si>
-  <si>
-    <t>135521592</t>
-  </si>
-  <si>
-    <t>135521872</t>
-  </si>
-  <si>
-    <t>135522301</t>
-  </si>
-  <si>
-    <t>135524083</t>
-  </si>
-  <si>
-    <t>135524988</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 24.11.2025</t>
+    <t>135530566</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  25.11.2025</t>
+  </si>
+  <si>
+    <t>135530546</t>
+  </si>
+  <si>
+    <t>135533311</t>
+  </si>
+  <si>
+    <t>135539364</t>
+  </si>
+  <si>
+    <t>135539075</t>
+  </si>
+  <si>
+    <t>135540549</t>
+  </si>
+  <si>
+    <t>135540972</t>
+  </si>
+  <si>
+    <t>135542100</t>
+  </si>
+  <si>
+    <t>135546018</t>
+  </si>
+  <si>
+    <t>135547953</t>
+  </si>
+  <si>
+    <t>135548192</t>
+  </si>
+  <si>
+    <t>135548460</t>
+  </si>
+  <si>
+    <t>135536429</t>
+  </si>
+  <si>
+    <t>135536549</t>
+  </si>
+  <si>
+    <t>135532440</t>
+  </si>
+  <si>
+    <t>135530876</t>
+  </si>
+  <si>
+    <t>135537277</t>
+  </si>
+  <si>
+    <t>135537819</t>
+  </si>
+  <si>
+    <t>135538830</t>
+  </si>
+  <si>
+    <t>135545740</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.11.2025</t>
   </si>
 </sst>
 </file>
@@ -536,7 +527,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -577,7 +568,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +622,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,7 +712,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,7 +730,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -793,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -810,7 +801,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -827,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -844,7 +835,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -861,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -912,60 +903,9 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -983,31 +923,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5477579-629C-4661-AC13-08E2BDB7ADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E1BA72-14C6-4DBB-BAD3-9909B829A88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>BLOQUEIOS HONDA 25.11.2025</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; BLOQUEIOS HONDA 25.11.2025.xlsx.</t>
   </si>
 </sst>
 </file>
@@ -571,9 +577,11 @@
         <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -589,9 +597,11 @@
         <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -607,9 +617,11 @@
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4"/>
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -625,9 +637,11 @@
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -643,9 +657,11 @@
         <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6"/>
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -661,9 +677,11 @@
         <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7"/>
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -679,9 +697,11 @@
         <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8"/>
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -697,9 +717,11 @@
         <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9"/>
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -715,9 +737,11 @@
         <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10"/>
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -733,9 +757,11 @@
         <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11"/>
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -751,9 +777,11 @@
         <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -769,9 +797,11 @@
         <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -787,7 +817,10 @@
         <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -804,7 +837,10 @@
         <v>29</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,10 +857,13 @@
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -838,10 +877,13 @@
         <v>29</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -855,10 +897,11 @@
         <v>29</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -874,8 +917,9 @@
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -889,10 +933,13 @@
         <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -906,7 +953,10 @@
         <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -923,31 +973,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E1BA72-14C6-4DBB-BAD3-9909B829A88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AB8524-D711-4535-B2DF-A3E871BB8356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,76 +54,73 @@
     <t>971</t>
   </si>
   <si>
-    <t>135530566</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  25.11.2025</t>
-  </si>
-  <si>
-    <t>135530546</t>
-  </si>
-  <si>
-    <t>135533311</t>
-  </si>
-  <si>
-    <t>135539364</t>
-  </si>
-  <si>
-    <t>135539075</t>
-  </si>
-  <si>
-    <t>135540549</t>
-  </si>
-  <si>
-    <t>135540972</t>
-  </si>
-  <si>
-    <t>135542100</t>
-  </si>
-  <si>
-    <t>135546018</t>
-  </si>
-  <si>
-    <t>135547953</t>
-  </si>
-  <si>
-    <t>135548192</t>
-  </si>
-  <si>
-    <t>135548460</t>
-  </si>
-  <si>
-    <t>135536429</t>
-  </si>
-  <si>
-    <t>135536549</t>
-  </si>
-  <si>
-    <t>135532440</t>
-  </si>
-  <si>
-    <t>135530876</t>
-  </si>
-  <si>
-    <t>135537277</t>
-  </si>
-  <si>
-    <t>135537819</t>
-  </si>
-  <si>
-    <t>135538830</t>
-  </si>
-  <si>
-    <t>135545740</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.11.2025</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; BLOQUEIOS HONDA 25.11.2025.xlsx.</t>
+    <t>135564710</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  26.11.2025</t>
+  </si>
+  <si>
+    <t>135554745</t>
+  </si>
+  <si>
+    <t>135555047</t>
+  </si>
+  <si>
+    <t>135562821</t>
+  </si>
+  <si>
+    <t>135553554</t>
+  </si>
+  <si>
+    <t>135562243</t>
+  </si>
+  <si>
+    <t>135560306</t>
+  </si>
+  <si>
+    <t>135561067</t>
+  </si>
+  <si>
+    <t>135564592</t>
+  </si>
+  <si>
+    <t>135561929</t>
+  </si>
+  <si>
+    <t>135564204</t>
+  </si>
+  <si>
+    <t>135568150</t>
+  </si>
+  <si>
+    <t>135566642</t>
+  </si>
+  <si>
+    <t>135567690</t>
+  </si>
+  <si>
+    <t>135568854</t>
+  </si>
+  <si>
+    <t>135569006</t>
+  </si>
+  <si>
+    <t>135569502</t>
+  </si>
+  <si>
+    <t>135569725</t>
+  </si>
+  <si>
+    <t>135571216</t>
+  </si>
+  <si>
+    <t>135565016</t>
+  </si>
+  <si>
+    <t>135553482</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 26.11.2025</t>
   </si>
 </sst>
 </file>
@@ -533,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -574,14 +571,12 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -594,14 +589,12 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -614,14 +607,12 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -634,14 +625,12 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -654,14 +643,12 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -674,14 +661,12 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -694,14 +679,12 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -714,14 +697,12 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -734,14 +715,12 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -754,14 +733,12 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -774,14 +751,12 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -794,14 +769,12 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>31</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -814,13 +787,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -834,13 +804,10 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -854,16 +821,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -874,16 +838,13 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -894,14 +855,13 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -912,14 +872,13 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -930,16 +889,13 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -950,13 +906,27 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>31</v>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5561688F-A4BA-46F7-9EAE-D749880B4275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF84936-74B6-48F6-AD3F-F32DF00660B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,97 @@
     <t>971</t>
   </si>
   <si>
-    <t>135572235</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 27.11.2025</t>
-  </si>
-  <si>
-    <t>135580149</t>
-  </si>
-  <si>
-    <t>135574892</t>
-  </si>
-  <si>
-    <t>135573656</t>
-  </si>
-  <si>
-    <t>135573871</t>
-  </si>
-  <si>
-    <t>135575409</t>
-  </si>
-  <si>
-    <t>135576042</t>
-  </si>
-  <si>
-    <t>135578384</t>
-  </si>
-  <si>
-    <t>135588463</t>
-  </si>
-  <si>
-    <t>135583669</t>
-  </si>
-  <si>
-    <t>135581623</t>
-  </si>
-  <si>
-    <t>135582287</t>
-  </si>
-  <si>
-    <t>135584630</t>
-  </si>
-  <si>
-    <t>135585606</t>
-  </si>
-  <si>
-    <t>135585914</t>
-  </si>
-  <si>
-    <t>135586416</t>
-  </si>
-  <si>
-    <t>135588327</t>
-  </si>
-  <si>
-    <t>135588866</t>
-  </si>
-  <si>
-    <t>135589264</t>
-  </si>
-  <si>
-    <t>135590234</t>
-  </si>
-  <si>
-    <t>135591289</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 27.11.2025</t>
+    <t>135595844</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  28.11.2025</t>
+  </si>
+  <si>
+    <t>135595524</t>
+  </si>
+  <si>
+    <t>135612243</t>
+  </si>
+  <si>
+    <t>135597290</t>
+  </si>
+  <si>
+    <t>135596550</t>
+  </si>
+  <si>
+    <t>135597436</t>
+  </si>
+  <si>
+    <t>135597562</t>
+  </si>
+  <si>
+    <t>135598608</t>
+  </si>
+  <si>
+    <t>135602412</t>
+  </si>
+  <si>
+    <t>135617479</t>
+  </si>
+  <si>
+    <t>135601983</t>
+  </si>
+  <si>
+    <t>135602161</t>
+  </si>
+  <si>
+    <t>135603353</t>
+  </si>
+  <si>
+    <t>135603365</t>
+  </si>
+  <si>
+    <t>135605580</t>
+  </si>
+  <si>
+    <t>135606921</t>
+  </si>
+  <si>
+    <t>135608471</t>
+  </si>
+  <si>
+    <t>135611494</t>
+  </si>
+  <si>
+    <t>135611656</t>
+  </si>
+  <si>
+    <t>135613445</t>
+  </si>
+  <si>
+    <t>135615966</t>
+  </si>
+  <si>
+    <t>135616031</t>
+  </si>
+  <si>
+    <t>135617138</t>
+  </si>
+  <si>
+    <t>135617470</t>
+  </si>
+  <si>
+    <t>135619972</t>
+  </si>
+  <si>
+    <t>135619703</t>
+  </si>
+  <si>
+    <t>135601579</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 28.11.2025</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  29.11.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 29.11.2025</t>
   </si>
 </sst>
 </file>
@@ -178,7 +202,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -186,11 +210,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -212,6 +288,22 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,7 +622,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -570,9 +662,6 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
@@ -589,7 +678,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,7 +714,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,7 +732,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,7 +750,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,7 +768,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,7 +804,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,7 +840,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,7 +876,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -804,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -821,7 +910,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -838,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -855,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -872,7 +961,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -889,7 +978,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -906,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -923,9 +1012,298 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>135621231</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>135623225</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>135623181</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>135621281</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>135621378</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>135621637</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>135622022</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>135621980</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>135622164</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>135622605</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <v>135622691</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF84936-74B6-48F6-AD3F-F32DF00660B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3C243F-B75C-42DF-AE32-8BC447526015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="31">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,97 +54,73 @@
     <t>971</t>
   </si>
   <si>
-    <t>135595844</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  28.11.2025</t>
-  </si>
-  <si>
-    <t>135595524</t>
-  </si>
-  <si>
-    <t>135612243</t>
-  </si>
-  <si>
-    <t>135597290</t>
-  </si>
-  <si>
-    <t>135596550</t>
-  </si>
-  <si>
-    <t>135597436</t>
-  </si>
-  <si>
-    <t>135597562</t>
-  </si>
-  <si>
-    <t>135598608</t>
-  </si>
-  <si>
-    <t>135602412</t>
-  </si>
-  <si>
-    <t>135617479</t>
-  </si>
-  <si>
-    <t>135601983</t>
-  </si>
-  <si>
-    <t>135602161</t>
-  </si>
-  <si>
-    <t>135603353</t>
-  </si>
-  <si>
-    <t>135603365</t>
-  </si>
-  <si>
-    <t>135605580</t>
-  </si>
-  <si>
-    <t>135606921</t>
-  </si>
-  <si>
-    <t>135608471</t>
-  </si>
-  <si>
-    <t>135611494</t>
-  </si>
-  <si>
-    <t>135611656</t>
-  </si>
-  <si>
-    <t>135613445</t>
-  </si>
-  <si>
-    <t>135615966</t>
-  </si>
-  <si>
-    <t>135616031</t>
-  </si>
-  <si>
-    <t>135617138</t>
-  </si>
-  <si>
-    <t>135617470</t>
-  </si>
-  <si>
-    <t>135619972</t>
-  </si>
-  <si>
-    <t>135619703</t>
-  </si>
-  <si>
-    <t>135601579</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 28.11.2025</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  29.11.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 29.11.2025</t>
+    <t>135572235</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 27.11.2025</t>
+  </si>
+  <si>
+    <t>135580149</t>
+  </si>
+  <si>
+    <t>135574892</t>
+  </si>
+  <si>
+    <t>23034211287</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 01.12.2025</t>
+  </si>
+  <si>
+    <t>92712525</t>
+  </si>
+  <si>
+    <t>27834181858</t>
+  </si>
+  <si>
+    <t>5864373125</t>
+  </si>
+  <si>
+    <t>11034020480</t>
+  </si>
+  <si>
+    <t>1879414759</t>
+  </si>
+  <si>
+    <t>84782935404</t>
+  </si>
+  <si>
+    <t>62822950253</t>
+  </si>
+  <si>
+    <t>1257577433</t>
+  </si>
+  <si>
+    <t>5852400351</t>
+  </si>
+  <si>
+    <t>9837284455</t>
+  </si>
+  <si>
+    <t>96817291534</t>
+  </si>
+  <si>
+    <t>16489940752</t>
+  </si>
+  <si>
+    <t>13435036710</t>
+  </si>
+  <si>
+    <t>12588426700</t>
+  </si>
+  <si>
+    <t>10054029813</t>
+  </si>
+  <si>
+    <t>10211980722</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 01.12.2025</t>
   </si>
 </sst>
 </file>
@@ -202,7 +178,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -210,63 +186,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -288,22 +212,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -662,6 +570,9 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
@@ -678,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -696,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -711,10 +622,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -723,16 +634,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -741,16 +652,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -759,16 +670,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -777,16 +688,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -795,16 +706,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -813,16 +724,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -831,16 +742,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -849,16 +760,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -867,16 +778,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -884,16 +795,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -901,16 +812,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -918,16 +829,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -935,16 +846,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -952,16 +863,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -969,16 +880,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -986,324 +897,18 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>135621231</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>135623225</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>135623181</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>135621281</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>135621378</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>135621637</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>135622022</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>135621980</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>135622164</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>135622605</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
-        <v>135622691</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1321,31 +926,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3C243F-B75C-42DF-AE32-8BC447526015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E399B18-F27F-461D-8077-84B173EEA1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="27">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,61 @@
     <t>971</t>
   </si>
   <si>
-    <t>135572235</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 27.11.2025</t>
-  </si>
-  <si>
-    <t>135580149</t>
-  </si>
-  <si>
-    <t>135574892</t>
-  </si>
-  <si>
-    <t>23034211287</t>
-  </si>
-  <si>
     <t>Bloqueios Honda 01.12.2025</t>
   </si>
   <si>
-    <t>92712525</t>
-  </si>
-  <si>
-    <t>27834181858</t>
-  </si>
-  <si>
-    <t>5864373125</t>
-  </si>
-  <si>
-    <t>11034020480</t>
-  </si>
-  <si>
-    <t>1879414759</t>
-  </si>
-  <si>
-    <t>84782935404</t>
-  </si>
-  <si>
-    <t>62822950253</t>
-  </si>
-  <si>
-    <t>1257577433</t>
-  </si>
-  <si>
-    <t>5852400351</t>
-  </si>
-  <si>
-    <t>9837284455</t>
-  </si>
-  <si>
-    <t>96817291534</t>
-  </si>
-  <si>
-    <t>16489940752</t>
-  </si>
-  <si>
-    <t>13435036710</t>
-  </si>
-  <si>
-    <t>12588426700</t>
-  </si>
-  <si>
-    <t>10054029813</t>
-  </si>
-  <si>
-    <t>10211980722</t>
-  </si>
-  <si>
     <t>BLOQUEIOS HONDA 01.12.2025</t>
+  </si>
+  <si>
+    <t>135629369</t>
+  </si>
+  <si>
+    <t>135629428</t>
+  </si>
+  <si>
+    <t>135629005</t>
+  </si>
+  <si>
+    <t>135629389</t>
+  </si>
+  <si>
+    <t>135642376</t>
+  </si>
+  <si>
+    <t>135631839</t>
+  </si>
+  <si>
+    <t>132351314</t>
+  </si>
+  <si>
+    <t>135634649</t>
+  </si>
+  <si>
+    <t>135636982</t>
+  </si>
+  <si>
+    <t>135638217</t>
+  </si>
+  <si>
+    <t>135639726</t>
+  </si>
+  <si>
+    <t>135640668</t>
+  </si>
+  <si>
+    <t>135642548</t>
+  </si>
+  <si>
+    <t>135626554</t>
+  </si>
+  <si>
+    <t>135629550</t>
+  </si>
+  <si>
+    <t>135635129</t>
+  </si>
+  <si>
+    <t>135347333</t>
   </si>
 </sst>
 </file>
@@ -530,7 +518,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -562,16 +550,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -580,16 +568,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -598,16 +586,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -616,16 +604,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -640,10 +628,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -658,10 +646,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -676,10 +664,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -694,10 +682,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -712,10 +700,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -730,10 +718,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -748,10 +736,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -766,10 +754,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -784,10 +772,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -801,10 +789,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -818,10 +806,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -835,10 +823,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -852,63 +840,12 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -926,31 +863,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E399B18-F27F-461D-8077-84B173EEA1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1988AC71-A33C-4A0A-A26F-8FF6E04D78CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -863,31 +863,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1988AC71-A33C-4A0A-A26F-8FF6E04D78CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B933EF18-09CA-4278-9065-81219C7167A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,61 +54,91 @@
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 01.12.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 01.12.2025</t>
-  </si>
-  <si>
-    <t>135629369</t>
-  </si>
-  <si>
-    <t>135629428</t>
-  </si>
-  <si>
-    <t>135629005</t>
-  </si>
-  <si>
-    <t>135629389</t>
-  </si>
-  <si>
-    <t>135642376</t>
-  </si>
-  <si>
-    <t>135631839</t>
-  </si>
-  <si>
-    <t>132351314</t>
-  </si>
-  <si>
-    <t>135634649</t>
-  </si>
-  <si>
-    <t>135636982</t>
-  </si>
-  <si>
-    <t>135638217</t>
-  </si>
-  <si>
-    <t>135639726</t>
-  </si>
-  <si>
-    <t>135640668</t>
-  </si>
-  <si>
-    <t>135642548</t>
-  </si>
-  <si>
-    <t>135626554</t>
-  </si>
-  <si>
-    <t>135629550</t>
-  </si>
-  <si>
-    <t>135635129</t>
-  </si>
-  <si>
-    <t>135347333</t>
+    <t>135648309</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 02.12.2025</t>
+  </si>
+  <si>
+    <t>135666160</t>
+  </si>
+  <si>
+    <t>135648470</t>
+  </si>
+  <si>
+    <t>135648853</t>
+  </si>
+  <si>
+    <t>135649407</t>
+  </si>
+  <si>
+    <t>135649882</t>
+  </si>
+  <si>
+    <t>135651021</t>
+  </si>
+  <si>
+    <t>135652117</t>
+  </si>
+  <si>
+    <t>135653296</t>
+  </si>
+  <si>
+    <t>135654225</t>
+  </si>
+  <si>
+    <t>135655453</t>
+  </si>
+  <si>
+    <t>135655803</t>
+  </si>
+  <si>
+    <t>135657158</t>
+  </si>
+  <si>
+    <t>135657851</t>
+  </si>
+  <si>
+    <t>135669221</t>
+  </si>
+  <si>
+    <t>135659657</t>
+  </si>
+  <si>
+    <t>135659680</t>
+  </si>
+  <si>
+    <t>135660112</t>
+  </si>
+  <si>
+    <t>135660630</t>
+  </si>
+  <si>
+    <t>135661814</t>
+  </si>
+  <si>
+    <t>135663391</t>
+  </si>
+  <si>
+    <t>135668310</t>
+  </si>
+  <si>
+    <t>135663686</t>
+  </si>
+  <si>
+    <t>135666045</t>
+  </si>
+  <si>
+    <t>135666453</t>
+  </si>
+  <si>
+    <t>135666443</t>
+  </si>
+  <si>
+    <t>135666563</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 02.12.2025</t>
   </si>
 </sst>
 </file>
@@ -518,7 +548,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -550,16 +580,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -568,16 +598,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -586,16 +616,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -604,16 +634,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -622,16 +652,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -640,16 +670,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -658,16 +688,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -676,16 +706,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -694,16 +724,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -712,16 +742,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -730,16 +760,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -748,16 +778,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -766,16 +796,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -783,16 +813,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -800,16 +830,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -817,16 +847,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -834,18 +864,188 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -863,31 +1063,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B933EF18-09CA-4278-9065-81219C7167A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8B711A-2727-4958-A03E-E808C74EB092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,43 @@
     <t>971</t>
   </si>
   <si>
-    <t>135648309</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 02.12.2025</t>
-  </si>
-  <si>
-    <t>135666160</t>
-  </si>
-  <si>
-    <t>135648470</t>
-  </si>
-  <si>
-    <t>135648853</t>
-  </si>
-  <si>
-    <t>135649407</t>
-  </si>
-  <si>
-    <t>135649882</t>
-  </si>
-  <si>
-    <t>135651021</t>
-  </si>
-  <si>
-    <t>135652117</t>
-  </si>
-  <si>
-    <t>135653296</t>
-  </si>
-  <si>
-    <t>135654225</t>
-  </si>
-  <si>
-    <t>135655453</t>
-  </si>
-  <si>
-    <t>135655803</t>
-  </si>
-  <si>
-    <t>135657158</t>
-  </si>
-  <si>
-    <t>135657851</t>
-  </si>
-  <si>
-    <t>135669221</t>
-  </si>
-  <si>
-    <t>135659657</t>
-  </si>
-  <si>
-    <t>135659680</t>
-  </si>
-  <si>
-    <t>135660112</t>
-  </si>
-  <si>
-    <t>135660630</t>
-  </si>
-  <si>
-    <t>135661814</t>
-  </si>
-  <si>
-    <t>135663391</t>
-  </si>
-  <si>
-    <t>135668310</t>
-  </si>
-  <si>
-    <t>135663686</t>
-  </si>
-  <si>
-    <t>135666045</t>
-  </si>
-  <si>
-    <t>135666453</t>
-  </si>
-  <si>
-    <t>135666443</t>
-  </si>
-  <si>
-    <t>135666563</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 02.12.2025</t>
+    <t>135670096</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 03.12.2025</t>
+  </si>
+  <si>
+    <t>135670268</t>
+  </si>
+  <si>
+    <t>135671163</t>
+  </si>
+  <si>
+    <t>135678901</t>
+  </si>
+  <si>
+    <t>135675787</t>
+  </si>
+  <si>
+    <t>135678954</t>
+  </si>
+  <si>
+    <t>135677511</t>
+  </si>
+  <si>
+    <t>135682035</t>
+  </si>
+  <si>
+    <t>135688164</t>
+  </si>
+  <si>
+    <t>135688688</t>
+  </si>
+  <si>
+    <t>135674255</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 03.12.2025</t>
   </si>
 </sst>
 </file>
@@ -548,7 +500,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -589,7 +541,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -607,7 +559,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -625,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -643,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -661,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -679,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -697,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -715,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -733,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -751,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -769,285 +721,12 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1063,31 +742,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8B711A-2727-4958-A03E-E808C74EB092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9D3C6B-3A31-450B-A5D7-D230EE1A68C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,43 +54,73 @@
     <t>971</t>
   </si>
   <si>
-    <t>135670096</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 03.12.2025</t>
-  </si>
-  <si>
-    <t>135670268</t>
-  </si>
-  <si>
-    <t>135671163</t>
-  </si>
-  <si>
-    <t>135678901</t>
-  </si>
-  <si>
-    <t>135675787</t>
-  </si>
-  <si>
-    <t>135678954</t>
-  </si>
-  <si>
-    <t>135677511</t>
-  </si>
-  <si>
-    <t>135682035</t>
-  </si>
-  <si>
-    <t>135688164</t>
-  </si>
-  <si>
-    <t>135688688</t>
-  </si>
-  <si>
-    <t>135674255</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 03.12.2025</t>
+    <t>135699628</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 04.12.2025</t>
+  </si>
+  <si>
+    <t>135695838</t>
+  </si>
+  <si>
+    <t>135699096</t>
+  </si>
+  <si>
+    <t>135700674</t>
+  </si>
+  <si>
+    <t>135702594</t>
+  </si>
+  <si>
+    <t>135701621</t>
+  </si>
+  <si>
+    <t>135703658</t>
+  </si>
+  <si>
+    <t>135705117</t>
+  </si>
+  <si>
+    <t>135708193</t>
+  </si>
+  <si>
+    <t>135708426</t>
+  </si>
+  <si>
+    <t>135709140</t>
+  </si>
+  <si>
+    <t>135710930</t>
+  </si>
+  <si>
+    <t>135693903</t>
+  </si>
+  <si>
+    <t>135693017</t>
+  </si>
+  <si>
+    <t>132928866</t>
+  </si>
+  <si>
+    <t>135694464</t>
+  </si>
+  <si>
+    <t>135696725</t>
+  </si>
+  <si>
+    <t>135695852</t>
+  </si>
+  <si>
+    <t>135696207</t>
+  </si>
+  <si>
+    <t>135697080</t>
+  </si>
+  <si>
+    <t>135696753</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 04.12.2025</t>
   </si>
 </sst>
 </file>
@@ -500,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -541,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -559,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -577,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -595,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -613,7 +643,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -631,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -649,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -667,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -685,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -703,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -721,12 +751,182 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -742,31 +942,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9D3C6B-3A31-450B-A5D7-D230EE1A68C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2715250-9EB9-4916-AB54-DEEE608A0DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,118 @@
     <t>971</t>
   </si>
   <si>
-    <t>135699628</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 04.12.2025</t>
-  </si>
-  <si>
-    <t>135695838</t>
-  </si>
-  <si>
-    <t>135699096</t>
-  </si>
-  <si>
-    <t>135700674</t>
-  </si>
-  <si>
-    <t>135702594</t>
-  </si>
-  <si>
-    <t>135701621</t>
-  </si>
-  <si>
-    <t>135703658</t>
-  </si>
-  <si>
-    <t>135705117</t>
-  </si>
-  <si>
-    <t>135708193</t>
-  </si>
-  <si>
-    <t>135708426</t>
-  </si>
-  <si>
-    <t>135709140</t>
-  </si>
-  <si>
-    <t>135710930</t>
-  </si>
-  <si>
-    <t>135693903</t>
-  </si>
-  <si>
-    <t>135693017</t>
-  </si>
-  <si>
-    <t>132928866</t>
-  </si>
-  <si>
-    <t>135694464</t>
-  </si>
-  <si>
-    <t>135696725</t>
-  </si>
-  <si>
-    <t>135695852</t>
-  </si>
-  <si>
-    <t>135696207</t>
-  </si>
-  <si>
-    <t>135697080</t>
-  </si>
-  <si>
-    <t>135696753</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 04.12.2025</t>
+    <t>135716664</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  05.12.2025</t>
+  </si>
+  <si>
+    <t>135716962</t>
+  </si>
+  <si>
+    <t>135717619</t>
+  </si>
+  <si>
+    <t>135723357</t>
+  </si>
+  <si>
+    <t>135717488</t>
+  </si>
+  <si>
+    <t>135718525</t>
+  </si>
+  <si>
+    <t>135719202</t>
+  </si>
+  <si>
+    <t>135720723</t>
+  </si>
+  <si>
+    <t>135720289</t>
+  </si>
+  <si>
+    <t>135735227</t>
+  </si>
+  <si>
+    <t>135730594</t>
+  </si>
+  <si>
+    <t>135723680</t>
+  </si>
+  <si>
+    <t>135725135</t>
+  </si>
+  <si>
+    <t>135726843</t>
+  </si>
+  <si>
+    <t>135726904</t>
+  </si>
+  <si>
+    <t>135727730</t>
+  </si>
+  <si>
+    <t>135729832</t>
+  </si>
+  <si>
+    <t>135731468</t>
+  </si>
+  <si>
+    <t>135732450</t>
+  </si>
+  <si>
+    <t>135736136</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 05.12.2025</t>
+  </si>
+  <si>
+    <t>135739746</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  06.12.2025</t>
+  </si>
+  <si>
+    <t>135739073</t>
+  </si>
+  <si>
+    <t>135739788</t>
+  </si>
+  <si>
+    <t>135739243</t>
+  </si>
+  <si>
+    <t>135739249</t>
+  </si>
+  <si>
+    <t>135739336</t>
+  </si>
+  <si>
+    <t>135740079</t>
+  </si>
+  <si>
+    <t>135739423</t>
+  </si>
+  <si>
+    <t>135739564</t>
+  </si>
+  <si>
+    <t>135739588</t>
+  </si>
+  <si>
+    <t>135739704</t>
+  </si>
+  <si>
+    <t>135740095</t>
+  </si>
+  <si>
+    <t>135740045</t>
+  </si>
+  <si>
+    <t>135740302</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 06.12.2025</t>
   </si>
 </sst>
 </file>
@@ -530,7 +575,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -786,7 +831,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -820,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -837,7 +882,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -854,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -871,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -888,7 +933,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -905,7 +950,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -913,18 +958,239 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -942,31 +1208,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2715250-9EB9-4916-AB54-DEEE608A0DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B30D83-FD89-4F0A-8CFE-16DFA3A6EC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="38">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,118 +54,94 @@
     <t>971</t>
   </si>
   <si>
-    <t>135716664</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  05.12.2025</t>
-  </si>
-  <si>
-    <t>135716962</t>
-  </si>
-  <si>
-    <t>135717619</t>
-  </si>
-  <si>
-    <t>135723357</t>
-  </si>
-  <si>
-    <t>135717488</t>
-  </si>
-  <si>
-    <t>135718525</t>
-  </si>
-  <si>
-    <t>135719202</t>
-  </si>
-  <si>
-    <t>135720723</t>
-  </si>
-  <si>
-    <t>135720289</t>
-  </si>
-  <si>
-    <t>135735227</t>
-  </si>
-  <si>
-    <t>135730594</t>
-  </si>
-  <si>
-    <t>135723680</t>
-  </si>
-  <si>
-    <t>135725135</t>
-  </si>
-  <si>
-    <t>135726843</t>
-  </si>
-  <si>
-    <t>135726904</t>
-  </si>
-  <si>
-    <t>135727730</t>
-  </si>
-  <si>
-    <t>135729832</t>
-  </si>
-  <si>
-    <t>135731468</t>
-  </si>
-  <si>
-    <t>135732450</t>
-  </si>
-  <si>
-    <t>135736136</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 05.12.2025</t>
-  </si>
-  <si>
-    <t>135739746</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  06.12.2025</t>
-  </si>
-  <si>
-    <t>135739073</t>
-  </si>
-  <si>
-    <t>135739788</t>
-  </si>
-  <si>
-    <t>135739243</t>
-  </si>
-  <si>
-    <t>135739249</t>
-  </si>
-  <si>
-    <t>135739336</t>
-  </si>
-  <si>
-    <t>135740079</t>
-  </si>
-  <si>
-    <t>135739423</t>
-  </si>
-  <si>
-    <t>135739564</t>
-  </si>
-  <si>
-    <t>135739588</t>
-  </si>
-  <si>
-    <t>135739704</t>
-  </si>
-  <si>
-    <t>135740095</t>
-  </si>
-  <si>
-    <t>135740045</t>
-  </si>
-  <si>
-    <t>135740302</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 06.12.2025</t>
+    <t>135743449</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  08.12.2025</t>
+  </si>
+  <si>
+    <t>135744079</t>
+  </si>
+  <si>
+    <t>135745822</t>
+  </si>
+  <si>
+    <t>135745777</t>
+  </si>
+  <si>
+    <t>135746611</t>
+  </si>
+  <si>
+    <t>135752051</t>
+  </si>
+  <si>
+    <t>135749594</t>
+  </si>
+  <si>
+    <t>135749650</t>
+  </si>
+  <si>
+    <t>135750475</t>
+  </si>
+  <si>
+    <t>135757204</t>
+  </si>
+  <si>
+    <t>135751200</t>
+  </si>
+  <si>
+    <t>135751419</t>
+  </si>
+  <si>
+    <t>135751721</t>
+  </si>
+  <si>
+    <t>135752802</t>
+  </si>
+  <si>
+    <t>135756611</t>
+  </si>
+  <si>
+    <t>135753350</t>
+  </si>
+  <si>
+    <t>135752028</t>
+  </si>
+  <si>
+    <t>135753338</t>
+  </si>
+  <si>
+    <t>135753325</t>
+  </si>
+  <si>
+    <t>135754123</t>
+  </si>
+  <si>
+    <t>135754478</t>
+  </si>
+  <si>
+    <t>135754240</t>
+  </si>
+  <si>
+    <t>135755201</t>
+  </si>
+  <si>
+    <t>135755383</t>
+  </si>
+  <si>
+    <t>135755752</t>
+  </si>
+  <si>
+    <t>135756188</t>
+  </si>
+  <si>
+    <t>135757287</t>
+  </si>
+  <si>
+    <t>135757460</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 08.12.2025</t>
   </si>
 </sst>
 </file>
@@ -575,7 +551,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -616,7 +592,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -634,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -652,7 +628,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -670,7 +646,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -688,7 +664,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -706,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -724,7 +700,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -742,7 +718,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -760,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -778,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -796,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -814,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -831,7 +807,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -848,7 +824,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -865,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -882,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -899,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -916,7 +892,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -933,7 +909,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -950,7 +926,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -958,16 +934,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -975,16 +951,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -992,16 +968,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1009,16 +985,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1026,16 +1002,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1043,16 +1019,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1060,16 +1036,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1077,120 +1053,18 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1208,31 +1082,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD60592F-1094-4E69-8DDF-CFFC5FB8D43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A536B1F-D86E-465E-8539-044302FB845E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,82 +51,94 @@
     <t>971</t>
   </si>
   <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>135126805</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 28.10.2025</t>
-  </si>
-  <si>
-    <t>135126971</t>
-  </si>
-  <si>
-    <t>135127549</t>
-  </si>
-  <si>
-    <t>135127725</t>
-  </si>
-  <si>
-    <t>135134543</t>
-  </si>
-  <si>
-    <t>135129319</t>
-  </si>
-  <si>
-    <t>135129524</t>
-  </si>
-  <si>
-    <t>135129711</t>
-  </si>
-  <si>
-    <t>135130064</t>
-  </si>
-  <si>
-    <t>135132669</t>
-  </si>
-  <si>
-    <t>135133308</t>
-  </si>
-  <si>
-    <t>135134566</t>
-  </si>
-  <si>
-    <t>135134993</t>
-  </si>
-  <si>
-    <t>135138411</t>
-  </si>
-  <si>
-    <t>135143191</t>
-  </si>
-  <si>
-    <t>135141290</t>
-  </si>
-  <si>
-    <t>135142378</t>
-  </si>
-  <si>
-    <t>135144911</t>
-  </si>
-  <si>
-    <t>135133913</t>
-  </si>
-  <si>
-    <t>135133874</t>
-  </si>
-  <si>
-    <t>135134008</t>
-  </si>
-  <si>
-    <t>135139614</t>
-  </si>
-  <si>
-    <t>135144160</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 28.10.2025</t>
+    <t>135948651</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 19.12.2025</t>
+  </si>
+  <si>
+    <t>135952749</t>
+  </si>
+  <si>
+    <t>135941106</t>
+  </si>
+  <si>
+    <t>135947117</t>
+  </si>
+  <si>
+    <t>135956570</t>
+  </si>
+  <si>
+    <t>135957889</t>
+  </si>
+  <si>
+    <t>135958141</t>
+  </si>
+  <si>
+    <t>135959947</t>
+  </si>
+  <si>
+    <t>135962049</t>
+  </si>
+  <si>
+    <t>135962730</t>
+  </si>
+  <si>
+    <t>135962424</t>
+  </si>
+  <si>
+    <t>135963147</t>
+  </si>
+  <si>
+    <t>135950781</t>
+  </si>
+  <si>
+    <t>135953155</t>
+  </si>
+  <si>
+    <t>135954567</t>
+  </si>
+  <si>
+    <t>135954658</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 19.12.2025</t>
+  </si>
+  <si>
+    <t>135965099</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 20.12.2025</t>
+  </si>
+  <si>
+    <t>135965096</t>
+  </si>
+  <si>
+    <t>135965232</t>
+  </si>
+  <si>
+    <t>135965285</t>
+  </si>
+  <si>
+    <t>135965699</t>
+  </si>
+  <si>
+    <t>135965747</t>
+  </si>
+  <si>
+    <t>135966029</t>
+  </si>
+  <si>
+    <t>135966027</t>
+  </si>
+  <si>
+    <t>135966190</t>
+  </si>
+  <si>
+    <t>Processar</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 20.12.2025</t>
   </si>
 </sst>
 </file>
@@ -533,7 +545,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -565,289 +577,289 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F17"/>
     </row>
@@ -859,123 +871,157 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A536B1F-D86E-465E-8539-044302FB845E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30200078-B505-4291-85C1-168372F93501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="47">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,94 +51,124 @@
     <t>971</t>
   </si>
   <si>
-    <t>135948651</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 19.12.2025</t>
-  </si>
-  <si>
-    <t>135952749</t>
-  </si>
-  <si>
-    <t>135941106</t>
-  </si>
-  <si>
-    <t>135947117</t>
-  </si>
-  <si>
-    <t>135956570</t>
-  </si>
-  <si>
-    <t>135957889</t>
-  </si>
-  <si>
-    <t>135958141</t>
-  </si>
-  <si>
-    <t>135959947</t>
-  </si>
-  <si>
-    <t>135962049</t>
-  </si>
-  <si>
-    <t>135962730</t>
-  </si>
-  <si>
-    <t>135962424</t>
-  </si>
-  <si>
-    <t>135963147</t>
-  </si>
-  <si>
-    <t>135950781</t>
-  </si>
-  <si>
-    <t>135953155</t>
-  </si>
-  <si>
-    <t>135954567</t>
-  </si>
-  <si>
-    <t>135954658</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 19.12.2025</t>
-  </si>
-  <si>
-    <t>135965099</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 20.12.2025</t>
-  </si>
-  <si>
-    <t>135965096</t>
-  </si>
-  <si>
-    <t>135965232</t>
-  </si>
-  <si>
-    <t>135965285</t>
-  </si>
-  <si>
-    <t>135965699</t>
-  </si>
-  <si>
-    <t>135965747</t>
-  </si>
-  <si>
-    <t>135966029</t>
-  </si>
-  <si>
-    <t>135966027</t>
-  </si>
-  <si>
-    <t>135966190</t>
-  </si>
-  <si>
     <t>Processar</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 20.12.2025</t>
+    <t>7046708525</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 22.12.2025</t>
+  </si>
+  <si>
+    <t>3437052900</t>
+  </si>
+  <si>
+    <t>5414874506</t>
+  </si>
+  <si>
+    <t>6141236316</t>
+  </si>
+  <si>
+    <t>7454220398</t>
+  </si>
+  <si>
+    <t>3605599567</t>
+  </si>
+  <si>
+    <t>45154260287</t>
+  </si>
+  <si>
+    <t>86500832507</t>
+  </si>
+  <si>
+    <t>11186832428</t>
+  </si>
+  <si>
+    <t>70555232492</t>
+  </si>
+  <si>
+    <t>5586185377</t>
+  </si>
+  <si>
+    <t>36607673368</t>
+  </si>
+  <si>
+    <t>3003633201</t>
+  </si>
+  <si>
+    <t>61022269330</t>
+  </si>
+  <si>
+    <t>502339551</t>
+  </si>
+  <si>
+    <t>41394054149</t>
+  </si>
+  <si>
+    <t>84636076249</t>
+  </si>
+  <si>
+    <t>62738143415</t>
+  </si>
+  <si>
+    <t>70371359414</t>
+  </si>
+  <si>
+    <t>67317723304</t>
+  </si>
+  <si>
+    <t>3259976400</t>
+  </si>
+  <si>
+    <t>4769713657</t>
+  </si>
+  <si>
+    <t>2941919414</t>
+  </si>
+  <si>
+    <t>99915308515</t>
+  </si>
+  <si>
+    <t>70465671152</t>
+  </si>
+  <si>
+    <t>342420666</t>
+  </si>
+  <si>
+    <t>3484824778</t>
+  </si>
+  <si>
+    <t>86728032304</t>
+  </si>
+  <si>
+    <t>45943613404</t>
+  </si>
+  <si>
+    <t>1580749631</t>
+  </si>
+  <si>
+    <t>53016912287</t>
+  </si>
+  <si>
+    <t>10067180442</t>
+  </si>
+  <si>
+    <t>73356913115</t>
+  </si>
+  <si>
+    <t>4160724450</t>
+  </si>
+  <si>
+    <t>42257077253</t>
+  </si>
+  <si>
+    <t>338393528</t>
+  </si>
+  <si>
+    <t>7854533695</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.12.2025</t>
   </si>
 </sst>
 </file>
@@ -545,7 +575,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -577,289 +607,289 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F17"/>
     </row>
@@ -871,156 +901,360 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>35</v>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1037,31 +1271,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30200078-B505-4291-85C1-168372F93501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9415B3F-5786-4336-9CAD-7BE8A13FD293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="94">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,10 +54,109 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>135990534</t>
+  </si>
+  <si>
+    <t>Bloqueios HONDA 23.12.2025</t>
+  </si>
+  <si>
+    <t>135990376</t>
+  </si>
+  <si>
+    <t>135991139</t>
+  </si>
+  <si>
+    <t>133424124</t>
+  </si>
+  <si>
+    <t>135992713</t>
+  </si>
+  <si>
+    <t>135992979</t>
+  </si>
+  <si>
+    <t>135993100</t>
+  </si>
+  <si>
+    <t>135994435</t>
+  </si>
+  <si>
+    <t>135995481</t>
+  </si>
+  <si>
+    <t>135996028</t>
+  </si>
+  <si>
+    <t>136000040</t>
+  </si>
+  <si>
+    <t>135996764</t>
+  </si>
+  <si>
+    <t>135997683</t>
+  </si>
+  <si>
+    <t>136001355</t>
+  </si>
+  <si>
+    <t>135997531</t>
+  </si>
+  <si>
+    <t>136004325</t>
+  </si>
+  <si>
+    <t>135998135</t>
+  </si>
+  <si>
+    <t>136007887</t>
+  </si>
+  <si>
+    <t>136002168</t>
+  </si>
+  <si>
+    <t>136002903</t>
+  </si>
+  <si>
+    <t>136001256</t>
+  </si>
+  <si>
+    <t>136002406</t>
+  </si>
+  <si>
+    <t>136002284</t>
+  </si>
+  <si>
+    <t>136003113</t>
+  </si>
+  <si>
+    <t>136004646</t>
+  </si>
+  <si>
+    <t>136004827</t>
+  </si>
+  <si>
+    <t>136004828</t>
+  </si>
+  <si>
+    <t>136005964</t>
+  </si>
+  <si>
+    <t>136006426</t>
+  </si>
+  <si>
+    <t>136010413</t>
+  </si>
+  <si>
+    <t>136008910</t>
+  </si>
+  <si>
+    <t>136009858</t>
+  </si>
+  <si>
     <t>7046708525</t>
   </si>
   <si>
-    <t>Bloqueios Honda 22.12.2025</t>
+    <t>Bloqueios HONDA 22.12.2025</t>
   </si>
   <si>
     <t>3437052900</t>
@@ -168,7 +267,49 @@
     <t>7854533695</t>
   </si>
   <si>
+    <t>BLOQUEIOS HONDA 23.12.2025</t>
+  </si>
+  <si>
     <t>BLOQUEIOS HONDA 22.12.2025</t>
+  </si>
+  <si>
+    <t>136012040</t>
+  </si>
+  <si>
+    <t>Bloqueios HONDA 24.12.2025</t>
+  </si>
+  <si>
+    <t>136012685</t>
+  </si>
+  <si>
+    <t>136013056</t>
+  </si>
+  <si>
+    <t>133154519</t>
+  </si>
+  <si>
+    <t>136014320</t>
+  </si>
+  <si>
+    <t>136014636</t>
+  </si>
+  <si>
+    <t>136012371</t>
+  </si>
+  <si>
+    <t>136014410</t>
+  </si>
+  <si>
+    <t>136014709</t>
+  </si>
+  <si>
+    <t>136015611</t>
+  </si>
+  <si>
+    <t>136016309</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 24.12.2025</t>
   </si>
 </sst>
 </file>
@@ -575,7 +716,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -616,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -634,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -652,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -670,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -688,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -706,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -724,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -742,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -760,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -778,7 +919,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -796,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -814,7 +955,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -832,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -850,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -868,7 +1009,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -886,7 +1027,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -904,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -922,7 +1063,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -940,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -958,7 +1099,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -976,7 +1117,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -994,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1012,7 +1153,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1030,7 +1171,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1047,7 +1188,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1064,7 +1205,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1081,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1098,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1115,7 +1256,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1132,7 +1273,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1149,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1166,7 +1307,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1180,10 +1321,10 @@
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1191,16 +1332,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1208,16 +1349,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1225,16 +1366,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1242,18 +1383,749 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF633041-D484-4856-BC01-55FC68959070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5BC700-2451-4B49-8882-FF8CF53FFDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,120 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136034563</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios HONDA 27.12.2025</t>
+  </si>
+  <si>
+    <t>136034627</t>
+  </si>
+  <si>
+    <t>136035888</t>
+  </si>
+  <si>
+    <t>136034863</t>
+  </si>
+  <si>
+    <t>136034830</t>
+  </si>
+  <si>
+    <t>136035068</t>
+  </si>
+  <si>
+    <t>136035164</t>
+  </si>
+  <si>
+    <t>136035351</t>
+  </si>
+  <si>
+    <t>136035306</t>
+  </si>
+  <si>
+    <t>136035398</t>
+  </si>
+  <si>
+    <t>136036218</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 27.12.2025</t>
+  </si>
+  <si>
+    <t>136018494</t>
+  </si>
+  <si>
+    <t>Bloqueios HONDA 26.12.2025</t>
+  </si>
+  <si>
+    <t>136024425</t>
+  </si>
+  <si>
+    <t>136019520</t>
+  </si>
+  <si>
+    <t>136019433</t>
+  </si>
+  <si>
+    <t>136021214</t>
+  </si>
+  <si>
+    <t>136021271</t>
+  </si>
+  <si>
+    <t>136021651</t>
+  </si>
+  <si>
+    <t>136023849</t>
+  </si>
+  <si>
+    <t>136024075</t>
+  </si>
+  <si>
+    <t>136025271</t>
+  </si>
+  <si>
+    <t>136024539</t>
+  </si>
+  <si>
+    <t>136026197</t>
+  </si>
+  <si>
+    <t>136026478</t>
+  </si>
+  <si>
+    <t>136028053</t>
+  </si>
+  <si>
+    <t>136028668</t>
+  </si>
+  <si>
+    <t>136029907</t>
+  </si>
+  <si>
+    <t>136030677</t>
+  </si>
+  <si>
+    <t>136030898</t>
+  </si>
+  <si>
+    <t>136031274</t>
+  </si>
+  <si>
+    <t>132669170</t>
+  </si>
+  <si>
+    <t>136033852</t>
+  </si>
+  <si>
+    <t>136034028</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 26.12.2025</t>
   </si>
 </sst>
 </file>
@@ -455,7 +569,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,426 +600,586 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5BC700-2451-4B49-8882-FF8CF53FFDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041BD55D-0FA4-41E7-95A0-BF75427A2B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,118 +51,82 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136034563</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios HONDA 27.12.2025</t>
-  </si>
-  <si>
-    <t>136034627</t>
-  </si>
-  <si>
-    <t>136035888</t>
-  </si>
-  <si>
-    <t>136034863</t>
-  </si>
-  <si>
-    <t>136034830</t>
-  </si>
-  <si>
-    <t>136035068</t>
-  </si>
-  <si>
-    <t>136035164</t>
-  </si>
-  <si>
-    <t>136035351</t>
-  </si>
-  <si>
-    <t>136035306</t>
-  </si>
-  <si>
-    <t>136035398</t>
-  </si>
-  <si>
-    <t>136036218</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 27.12.2025</t>
-  </si>
-  <si>
-    <t>136018494</t>
-  </si>
-  <si>
-    <t>Bloqueios HONDA 26.12.2025</t>
-  </si>
-  <si>
-    <t>136024425</t>
-  </si>
-  <si>
-    <t>136019520</t>
-  </si>
-  <si>
-    <t>136019433</t>
-  </si>
-  <si>
-    <t>136021214</t>
-  </si>
-  <si>
-    <t>136021271</t>
-  </si>
-  <si>
-    <t>136021651</t>
-  </si>
-  <si>
-    <t>136023849</t>
-  </si>
-  <si>
-    <t>136024075</t>
-  </si>
-  <si>
-    <t>136025271</t>
-  </si>
-  <si>
-    <t>136024539</t>
-  </si>
-  <si>
-    <t>136026197</t>
-  </si>
-  <si>
-    <t>136026478</t>
-  </si>
-  <si>
-    <t>136028053</t>
-  </si>
-  <si>
-    <t>136028668</t>
-  </si>
-  <si>
-    <t>136029907</t>
-  </si>
-  <si>
-    <t>136030677</t>
-  </si>
-  <si>
-    <t>136030898</t>
-  </si>
-  <si>
-    <t>136031274</t>
-  </si>
-  <si>
-    <t>132669170</t>
-  </si>
-  <si>
-    <t>136033852</t>
-  </si>
-  <si>
-    <t>136034028</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 26.12.2025</t>
+    <t>136038072</t>
+  </si>
+  <si>
+    <t>Bloqueios HONDA 29.12.2025</t>
+  </si>
+  <si>
+    <t>136037851</t>
+  </si>
+  <si>
+    <t>133796877</t>
+  </si>
+  <si>
+    <t>136041297</t>
+  </si>
+  <si>
+    <t>136040045</t>
+  </si>
+  <si>
+    <t>136040531</t>
+  </si>
+  <si>
+    <t>136040668</t>
+  </si>
+  <si>
+    <t>136042122</t>
+  </si>
+  <si>
+    <t>136042408</t>
+  </si>
+  <si>
+    <t>136042435</t>
+  </si>
+  <si>
+    <t>136042457</t>
+  </si>
+  <si>
+    <t>136043504</t>
+  </si>
+  <si>
+    <t>136043755</t>
+  </si>
+  <si>
+    <t>136045573</t>
+  </si>
+  <si>
+    <t>136045381</t>
+  </si>
+  <si>
+    <t>136048154</t>
+  </si>
+  <si>
+    <t>136048807</t>
+  </si>
+  <si>
+    <t>136051619</t>
+  </si>
+  <si>
+    <t>136050240</t>
+  </si>
+  <si>
+    <t>136050361</t>
+  </si>
+  <si>
+    <t>136052036</t>
+  </si>
+  <si>
+    <t>136054738</t>
+  </si>
+  <si>
+    <t>136039825</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 29.12.2025</t>
   </si>
 </sst>
 </file>
@@ -569,7 +533,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -601,16 +565,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -622,13 +586,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -640,13 +604,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -658,13 +622,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -676,13 +640,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -694,13 +658,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -712,13 +676,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -730,13 +694,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -748,13 +712,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -766,13 +730,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -784,13 +748,13 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -799,16 +763,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -817,16 +781,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -835,16 +799,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -853,16 +817,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -871,16 +835,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -889,16 +853,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -907,16 +871,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -925,16 +889,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -943,16 +907,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -961,16 +925,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -979,16 +943,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -997,191 +961,21 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1197,31 +991,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041BD55D-0FA4-41E7-95A0-BF75427A2B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F40820C-744C-47A7-88F2-F2352AD95048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,82 +51,136 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>136055997</t>
+  </si>
+  <si>
     <t>971</t>
   </si>
   <si>
-    <t>136038072</t>
-  </si>
-  <si>
-    <t>Bloqueios HONDA 29.12.2025</t>
-  </si>
-  <si>
-    <t>136037851</t>
-  </si>
-  <si>
-    <t>133796877</t>
-  </si>
-  <si>
-    <t>136041297</t>
-  </si>
-  <si>
-    <t>136040045</t>
-  </si>
-  <si>
-    <t>136040531</t>
-  </si>
-  <si>
-    <t>136040668</t>
-  </si>
-  <si>
-    <t>136042122</t>
-  </si>
-  <si>
-    <t>136042408</t>
-  </si>
-  <si>
-    <t>136042435</t>
-  </si>
-  <si>
-    <t>136042457</t>
-  </si>
-  <si>
-    <t>136043504</t>
-  </si>
-  <si>
-    <t>136043755</t>
-  </si>
-  <si>
-    <t>136045573</t>
-  </si>
-  <si>
-    <t>136045381</t>
-  </si>
-  <si>
-    <t>136048154</t>
-  </si>
-  <si>
-    <t>136048807</t>
-  </si>
-  <si>
-    <t>136051619</t>
-  </si>
-  <si>
-    <t>136050240</t>
-  </si>
-  <si>
-    <t>136050361</t>
-  </si>
-  <si>
-    <t>136052036</t>
-  </si>
-  <si>
-    <t>136054738</t>
-  </si>
-  <si>
-    <t>136039825</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 29.12.2025</t>
+    <t>Bloqueios Honda 30.12.2025</t>
+  </si>
+  <si>
+    <t>136056337</t>
+  </si>
+  <si>
+    <t>136056879</t>
+  </si>
+  <si>
+    <t>136056690</t>
+  </si>
+  <si>
+    <t>136056835</t>
+  </si>
+  <si>
+    <t>136057394</t>
+  </si>
+  <si>
+    <t>136057782</t>
+  </si>
+  <si>
+    <t>136058029</t>
+  </si>
+  <si>
+    <t>136059458</t>
+  </si>
+  <si>
+    <t>136063816</t>
+  </si>
+  <si>
+    <t>136060251</t>
+  </si>
+  <si>
+    <t>136069892</t>
+  </si>
+  <si>
+    <t>136066965</t>
+  </si>
+  <si>
+    <t>136061380</t>
+  </si>
+  <si>
+    <t>136063073</t>
+  </si>
+  <si>
+    <t>136061708</t>
+  </si>
+  <si>
+    <t>136062901</t>
+  </si>
+  <si>
+    <t>136063534</t>
+  </si>
+  <si>
+    <t>136067322</t>
+  </si>
+  <si>
+    <t>136065443</t>
+  </si>
+  <si>
+    <t>136065886</t>
+  </si>
+  <si>
+    <t>136066582</t>
+  </si>
+  <si>
+    <t>136067724</t>
+  </si>
+  <si>
+    <t>136068058</t>
+  </si>
+  <si>
+    <t>136069471</t>
+  </si>
+  <si>
+    <t>136068913</t>
+  </si>
+  <si>
+    <t>136069439</t>
+  </si>
+  <si>
+    <t>133837056</t>
+  </si>
+  <si>
+    <t>136070893</t>
+  </si>
+  <si>
+    <t>136071454</t>
+  </si>
+  <si>
+    <t>136072512</t>
+  </si>
+  <si>
+    <t>136072928</t>
+  </si>
+  <si>
+    <t>136073325</t>
+  </si>
+  <si>
+    <t>135371634</t>
+  </si>
+  <si>
+    <t>136074307</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 31.12.2025</t>
+  </si>
+  <si>
+    <t>136076499</t>
+  </si>
+  <si>
+    <t>136075034</t>
+  </si>
+  <si>
+    <t>136075384</t>
+  </si>
+  <si>
+    <t>136076347</t>
+  </si>
+  <si>
+    <t>136076809</t>
+  </si>
+  <si>
+    <t>136077150</t>
   </si>
 </sst>
 </file>
@@ -533,7 +587,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -565,16 +619,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -586,13 +640,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -604,13 +658,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -622,13 +676,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -640,13 +694,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -658,13 +712,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -676,13 +730,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -694,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -712,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -730,13 +784,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -748,13 +802,13 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -766,13 +820,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -784,13 +838,13 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -802,13 +856,13 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -820,13 +874,13 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -838,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -856,13 +910,13 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -874,13 +928,13 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -892,13 +946,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -910,13 +964,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -928,13 +982,13 @@
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -946,13 +1000,13 @@
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -964,18 +1018,324 @@
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F40820C-744C-47A7-88F2-F2352AD95048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700CB020-01A2-4755-A6FF-24FD89BC0F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,136 +51,85 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136055997</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 30.12.2025</t>
-  </si>
-  <si>
-    <t>136056337</t>
-  </si>
-  <si>
-    <t>136056879</t>
-  </si>
-  <si>
-    <t>136056690</t>
-  </si>
-  <si>
-    <t>136056835</t>
-  </si>
-  <si>
-    <t>136057394</t>
-  </si>
-  <si>
-    <t>136057782</t>
-  </si>
-  <si>
-    <t>136058029</t>
-  </si>
-  <si>
-    <t>136059458</t>
-  </si>
-  <si>
-    <t>136063816</t>
-  </si>
-  <si>
-    <t>136060251</t>
-  </si>
-  <si>
-    <t>136069892</t>
-  </si>
-  <si>
-    <t>136066965</t>
-  </si>
-  <si>
-    <t>136061380</t>
-  </si>
-  <si>
-    <t>136063073</t>
-  </si>
-  <si>
-    <t>136061708</t>
-  </si>
-  <si>
-    <t>136062901</t>
-  </si>
-  <si>
-    <t>136063534</t>
-  </si>
-  <si>
-    <t>136067322</t>
-  </si>
-  <si>
-    <t>136065443</t>
-  </si>
-  <si>
-    <t>136065886</t>
-  </si>
-  <si>
-    <t>136066582</t>
-  </si>
-  <si>
-    <t>136067724</t>
-  </si>
-  <si>
-    <t>136068058</t>
-  </si>
-  <si>
-    <t>136069471</t>
-  </si>
-  <si>
-    <t>136068913</t>
-  </si>
-  <si>
-    <t>136069439</t>
-  </si>
-  <si>
-    <t>133837056</t>
-  </si>
-  <si>
-    <t>136070893</t>
-  </si>
-  <si>
-    <t>136071454</t>
-  </si>
-  <si>
-    <t>136072512</t>
-  </si>
-  <si>
-    <t>136072928</t>
-  </si>
-  <si>
-    <t>136073325</t>
-  </si>
-  <si>
-    <t>135371634</t>
-  </si>
-  <si>
-    <t>136074307</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 31.12.2025</t>
-  </si>
-  <si>
-    <t>136076499</t>
-  </si>
-  <si>
-    <t>136075034</t>
-  </si>
-  <si>
-    <t>136075384</t>
-  </si>
-  <si>
-    <t>136076347</t>
-  </si>
-  <si>
-    <t>136076809</t>
-  </si>
-  <si>
-    <t>136077150</t>
+    <t>136078577</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 02.01.2026</t>
+  </si>
+  <si>
+    <t>136082626</t>
+  </si>
+  <si>
+    <t>136079615</t>
+  </si>
+  <si>
+    <t>136080452</t>
+  </si>
+  <si>
+    <t>136080930</t>
+  </si>
+  <si>
+    <t>136082297</t>
+  </si>
+  <si>
+    <t>136082434</t>
+  </si>
+  <si>
+    <t>136083066</t>
+  </si>
+  <si>
+    <t>136083298</t>
+  </si>
+  <si>
+    <t>136087715</t>
+  </si>
+  <si>
+    <t>136085804</t>
+  </si>
+  <si>
+    <t>136089955</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 02.01.2026</t>
+  </si>
+  <si>
+    <t>136090751</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 03.01.2026</t>
+  </si>
+  <si>
+    <t>136090935</t>
+  </si>
+  <si>
+    <t>136090974</t>
+  </si>
+  <si>
+    <t>136091040</t>
+  </si>
+  <si>
+    <t>136091089</t>
+  </si>
+  <si>
+    <t>136091194</t>
+  </si>
+  <si>
+    <t>136091264</t>
+  </si>
+  <si>
+    <t>136091278</t>
+  </si>
+  <si>
+    <t>136091363</t>
+  </si>
+  <si>
+    <t>136090959</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 03.01.2026</t>
   </si>
 </sst>
 </file>
@@ -587,7 +536,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -619,16 +568,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -640,13 +589,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -658,13 +607,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -676,13 +625,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -694,13 +643,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -712,13 +661,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -730,13 +679,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -748,13 +697,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -766,13 +715,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -784,13 +733,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -802,13 +751,13 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -820,13 +769,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -835,16 +784,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -853,16 +802,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -871,16 +820,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>9</v>
+      <c r="D16" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -889,16 +838,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -907,16 +856,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -925,16 +874,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -943,16 +892,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -961,16 +910,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -979,16 +928,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -997,345 +946,21 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700CB020-01A2-4755-A6FF-24FD89BC0F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD6B591-A36B-4F98-A287-8E019CAF52EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,73 @@
     <t>971</t>
   </si>
   <si>
-    <t>136078577</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 02.01.2026</t>
-  </si>
-  <si>
-    <t>136082626</t>
-  </si>
-  <si>
-    <t>136079615</t>
-  </si>
-  <si>
-    <t>136080452</t>
-  </si>
-  <si>
-    <t>136080930</t>
-  </si>
-  <si>
-    <t>136082297</t>
-  </si>
-  <si>
-    <t>136082434</t>
-  </si>
-  <si>
-    <t>136083066</t>
-  </si>
-  <si>
-    <t>136083298</t>
-  </si>
-  <si>
-    <t>136087715</t>
-  </si>
-  <si>
-    <t>136085804</t>
-  </si>
-  <si>
-    <t>136089955</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 02.01.2026</t>
-  </si>
-  <si>
-    <t>136090751</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 03.01.2026</t>
-  </si>
-  <si>
-    <t>136090935</t>
-  </si>
-  <si>
-    <t>136090974</t>
-  </si>
-  <si>
-    <t>136091040</t>
-  </si>
-  <si>
-    <t>136091089</t>
-  </si>
-  <si>
-    <t>136091194</t>
-  </si>
-  <si>
-    <t>136091264</t>
-  </si>
-  <si>
-    <t>136091278</t>
-  </si>
-  <si>
-    <t>136091363</t>
-  </si>
-  <si>
-    <t>136090959</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 03.01.2026</t>
+    <t>136093241</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 05.01.2026</t>
+  </si>
+  <si>
+    <t>136105359</t>
+  </si>
+  <si>
+    <t>136095798</t>
+  </si>
+  <si>
+    <t>136098774</t>
+  </si>
+  <si>
+    <t>136099042</t>
+  </si>
+  <si>
+    <t>136106964</t>
+  </si>
+  <si>
+    <t>136102576</t>
+  </si>
+  <si>
+    <t>136106528</t>
+  </si>
+  <si>
+    <t>136108118</t>
+  </si>
+  <si>
+    <t>136103249</t>
+  </si>
+  <si>
+    <t>136104158</t>
+  </si>
+  <si>
+    <t>136104374</t>
+  </si>
+  <si>
+    <t>136105037</t>
+  </si>
+  <si>
+    <t>136106643</t>
+  </si>
+  <si>
+    <t>136106178</t>
+  </si>
+  <si>
+    <t>136106394</t>
+  </si>
+  <si>
+    <t>136107453</t>
+  </si>
+  <si>
+    <t>136107642</t>
+  </si>
+  <si>
+    <t>136107995</t>
+  </si>
+  <si>
+    <t>136109188</t>
+  </si>
+  <si>
+    <t>136109268</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 05.01.2026</t>
   </si>
 </sst>
 </file>
@@ -577,7 +568,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +622,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,7 +712,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,7 +730,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -784,16 +775,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -802,16 +793,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -820,16 +811,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -838,16 +829,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -856,16 +847,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -874,16 +865,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -892,16 +883,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -910,16 +901,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -928,16 +919,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -945,21 +936,6 @@
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23"/>
     </row>
   </sheetData>
@@ -976,31 +952,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD6B591-A36B-4F98-A287-8E019CAF52EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C271EB-3A69-4E89-B5AD-7256928FFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,91 @@
     <t>971</t>
   </si>
   <si>
-    <t>136093241</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 05.01.2026</t>
-  </si>
-  <si>
-    <t>136105359</t>
-  </si>
-  <si>
-    <t>136095798</t>
-  </si>
-  <si>
-    <t>136098774</t>
-  </si>
-  <si>
-    <t>136099042</t>
-  </si>
-  <si>
-    <t>136106964</t>
-  </si>
-  <si>
-    <t>136102576</t>
-  </si>
-  <si>
-    <t>136106528</t>
-  </si>
-  <si>
-    <t>136108118</t>
-  </si>
-  <si>
-    <t>136103249</t>
-  </si>
-  <si>
-    <t>136104158</t>
-  </si>
-  <si>
-    <t>136104374</t>
-  </si>
-  <si>
-    <t>136105037</t>
-  </si>
-  <si>
-    <t>136106643</t>
-  </si>
-  <si>
-    <t>136106178</t>
-  </si>
-  <si>
-    <t>136106394</t>
-  </si>
-  <si>
-    <t>136107453</t>
-  </si>
-  <si>
-    <t>136107642</t>
-  </si>
-  <si>
-    <t>136107995</t>
-  </si>
-  <si>
-    <t>136109188</t>
-  </si>
-  <si>
-    <t>136109268</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 05.01.2026</t>
+    <t>Bloqueios Honda 06.01.2026</t>
+  </si>
+  <si>
+    <t>136110595</t>
+  </si>
+  <si>
+    <t>136111550</t>
+  </si>
+  <si>
+    <t>136111425</t>
+  </si>
+  <si>
+    <t>136111607</t>
+  </si>
+  <si>
+    <t>136112861</t>
+  </si>
+  <si>
+    <t>136115512</t>
+  </si>
+  <si>
+    <t>136127896</t>
+  </si>
+  <si>
+    <t>136114260</t>
+  </si>
+  <si>
+    <t>136114862</t>
+  </si>
+  <si>
+    <t>136116510</t>
+  </si>
+  <si>
+    <t>136115918</t>
+  </si>
+  <si>
+    <t>136116352</t>
+  </si>
+  <si>
+    <t>136116409</t>
+  </si>
+  <si>
+    <t>136117263</t>
+  </si>
+  <si>
+    <t>136117258</t>
+  </si>
+  <si>
+    <t>136120162</t>
+  </si>
+  <si>
+    <t>136120016</t>
+  </si>
+  <si>
+    <t>136121351</t>
+  </si>
+  <si>
+    <t>136127381</t>
+  </si>
+  <si>
+    <t>136124264</t>
+  </si>
+  <si>
+    <t>136125314</t>
+  </si>
+  <si>
+    <t>136127634</t>
+  </si>
+  <si>
+    <t>136127454</t>
+  </si>
+  <si>
+    <t>136128622</t>
+  </si>
+  <si>
+    <t>136128372</t>
+  </si>
+  <si>
+    <t>136129101</t>
+  </si>
+  <si>
+    <t>136129594</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 06.01.2026</t>
   </si>
 </sst>
 </file>
@@ -527,7 +545,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -558,17 +576,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -577,16 +592,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -595,16 +610,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -613,16 +628,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -631,16 +646,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -649,16 +664,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -667,16 +682,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -685,16 +700,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -703,16 +718,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -721,16 +736,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -739,16 +754,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -757,16 +772,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -775,16 +790,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -793,16 +808,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -811,16 +826,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -829,16 +844,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -847,16 +862,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -865,16 +880,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -883,16 +898,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -901,16 +916,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -919,24 +934,141 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F23"/>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -952,31 +1084,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C271EB-3A69-4E89-B5AD-7256928FFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BD0D17-62A0-4599-8842-34F52044731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,91 @@
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 06.01.2026</t>
-  </si>
-  <si>
-    <t>136110595</t>
-  </si>
-  <si>
-    <t>136111550</t>
-  </si>
-  <si>
-    <t>136111425</t>
-  </si>
-  <si>
-    <t>136111607</t>
-  </si>
-  <si>
-    <t>136112861</t>
-  </si>
-  <si>
-    <t>136115512</t>
-  </si>
-  <si>
-    <t>136127896</t>
-  </si>
-  <si>
-    <t>136114260</t>
-  </si>
-  <si>
-    <t>136114862</t>
-  </si>
-  <si>
-    <t>136116510</t>
-  </si>
-  <si>
-    <t>136115918</t>
-  </si>
-  <si>
-    <t>136116352</t>
-  </si>
-  <si>
-    <t>136116409</t>
-  </si>
-  <si>
-    <t>136117263</t>
-  </si>
-  <si>
-    <t>136117258</t>
-  </si>
-  <si>
-    <t>136120162</t>
-  </si>
-  <si>
-    <t>136120016</t>
-  </si>
-  <si>
-    <t>136121351</t>
-  </si>
-  <si>
-    <t>136127381</t>
-  </si>
-  <si>
-    <t>136124264</t>
-  </si>
-  <si>
-    <t>136125314</t>
-  </si>
-  <si>
-    <t>136127634</t>
-  </si>
-  <si>
-    <t>136127454</t>
-  </si>
-  <si>
-    <t>136128622</t>
-  </si>
-  <si>
-    <t>136128372</t>
-  </si>
-  <si>
-    <t>136129101</t>
-  </si>
-  <si>
-    <t>136129594</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 06.01.2026</t>
+    <t>136131140</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 07.01.2026</t>
+  </si>
+  <si>
+    <t>136132915</t>
+  </si>
+  <si>
+    <t>136131674</t>
+  </si>
+  <si>
+    <t>136131722</t>
+  </si>
+  <si>
+    <t>136134665</t>
+  </si>
+  <si>
+    <t>136135925</t>
+  </si>
+  <si>
+    <t>136136591</t>
+  </si>
+  <si>
+    <t>136136544</t>
+  </si>
+  <si>
+    <t>136136867</t>
+  </si>
+  <si>
+    <t>136137595</t>
+  </si>
+  <si>
+    <t>136138901</t>
+  </si>
+  <si>
+    <t>136139081</t>
+  </si>
+  <si>
+    <t>136139209</t>
+  </si>
+  <si>
+    <t>136145228</t>
+  </si>
+  <si>
+    <t>136141083</t>
+  </si>
+  <si>
+    <t>136143655</t>
+  </si>
+  <si>
+    <t>136143772</t>
+  </si>
+  <si>
+    <t>136143867</t>
+  </si>
+  <si>
+    <t>136143539</t>
+  </si>
+  <si>
+    <t>136145576</t>
+  </si>
+  <si>
+    <t>136146299</t>
+  </si>
+  <si>
+    <t>136146782</t>
+  </si>
+  <si>
+    <t>136147003</t>
+  </si>
+  <si>
+    <t>136147146</t>
+  </si>
+  <si>
+    <t>136147237</t>
+  </si>
+  <si>
+    <t>136147890</t>
+  </si>
+  <si>
+    <t>136149042</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 07.01.2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +545,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -576,11 +576,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
@@ -592,13 +595,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>36</v>
@@ -610,13 +613,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>36</v>
@@ -628,13 +631,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>36</v>
@@ -646,13 +649,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>36</v>
@@ -664,13 +667,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>36</v>
@@ -682,13 +685,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>36</v>
@@ -700,13 +703,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>36</v>
@@ -718,13 +721,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>36</v>
@@ -736,13 +739,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>36</v>
@@ -754,13 +757,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -772,13 +775,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>36</v>
@@ -790,13 +793,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>36</v>
@@ -808,13 +811,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>36</v>
@@ -826,13 +829,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>36</v>
@@ -844,13 +847,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>36</v>
@@ -862,13 +865,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>36</v>
@@ -880,13 +883,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>36</v>
@@ -898,13 +901,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>36</v>
@@ -916,13 +919,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>36</v>
@@ -934,13 +937,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>36</v>
@@ -952,13 +955,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>36</v>
@@ -970,13 +973,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>36</v>
@@ -987,13 +990,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>36</v>
@@ -1004,13 +1007,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>36</v>
@@ -1021,13 +1024,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>36</v>
@@ -1038,35 +1041,18 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1084,31 +1070,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BD0D17-62A0-4599-8842-34F52044731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4172AB3F-DBFE-4BEF-BA1F-DDBE63758219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,127 @@
     <t>971</t>
   </si>
   <si>
-    <t>136131140</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 07.01.2026</t>
-  </si>
-  <si>
-    <t>136132915</t>
-  </si>
-  <si>
-    <t>136131674</t>
-  </si>
-  <si>
-    <t>136131722</t>
-  </si>
-  <si>
-    <t>136134665</t>
-  </si>
-  <si>
-    <t>136135925</t>
-  </si>
-  <si>
-    <t>136136591</t>
-  </si>
-  <si>
-    <t>136136544</t>
-  </si>
-  <si>
-    <t>136136867</t>
-  </si>
-  <si>
-    <t>136137595</t>
-  </si>
-  <si>
-    <t>136138901</t>
-  </si>
-  <si>
-    <t>136139081</t>
-  </si>
-  <si>
-    <t>136139209</t>
-  </si>
-  <si>
-    <t>136145228</t>
-  </si>
-  <si>
-    <t>136141083</t>
-  </si>
-  <si>
-    <t>136143655</t>
-  </si>
-  <si>
-    <t>136143772</t>
-  </si>
-  <si>
-    <t>136143867</t>
-  </si>
-  <si>
-    <t>136143539</t>
-  </si>
-  <si>
-    <t>136145576</t>
-  </si>
-  <si>
-    <t>136146299</t>
-  </si>
-  <si>
-    <t>136146782</t>
-  </si>
-  <si>
-    <t>136147003</t>
-  </si>
-  <si>
-    <t>136147146</t>
-  </si>
-  <si>
-    <t>136147237</t>
-  </si>
-  <si>
-    <t>136147890</t>
-  </si>
-  <si>
-    <t>136149042</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 07.01.2026</t>
+    <t>136173858</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 09.01.2026</t>
+  </si>
+  <si>
+    <t>136170210</t>
+  </si>
+  <si>
+    <t>136171546</t>
+  </si>
+  <si>
+    <t>136175067</t>
+  </si>
+  <si>
+    <t>136183440</t>
+  </si>
+  <si>
+    <t>136178688</t>
+  </si>
+  <si>
+    <t>136180909</t>
+  </si>
+  <si>
+    <t>136181228</t>
+  </si>
+  <si>
+    <t>136183003</t>
+  </si>
+  <si>
+    <t>136182993</t>
+  </si>
+  <si>
+    <t>136183445</t>
+  </si>
+  <si>
+    <t>136183868</t>
+  </si>
+  <si>
+    <t>136184573</t>
+  </si>
+  <si>
+    <t>136189005</t>
+  </si>
+  <si>
+    <t>136190131</t>
+  </si>
+  <si>
+    <t>136190400</t>
+  </si>
+  <si>
+    <t>136191737</t>
+  </si>
+  <si>
+    <t>136171095</t>
+  </si>
+  <si>
+    <t>136173811</t>
+  </si>
+  <si>
+    <t>136175335</t>
+  </si>
+  <si>
+    <t>136180055</t>
+  </si>
+  <si>
+    <t>136175787</t>
+  </si>
+  <si>
+    <t>136179340</t>
+  </si>
+  <si>
+    <t>136179420</t>
+  </si>
+  <si>
+    <t>136180160</t>
+  </si>
+  <si>
+    <t>136187264</t>
+  </si>
+  <si>
+    <t>136188003</t>
+  </si>
+  <si>
+    <t>136188400</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 09.01.2026</t>
+  </si>
+  <si>
+    <t>136192393</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 10.01.2026</t>
+  </si>
+  <si>
+    <t>136192406</t>
+  </si>
+  <si>
+    <t>136192446</t>
+  </si>
+  <si>
+    <t>136192563</t>
+  </si>
+  <si>
+    <t>136192685</t>
+  </si>
+  <si>
+    <t>136192821</t>
+  </si>
+  <si>
+    <t>136192867</t>
+  </si>
+  <si>
+    <t>136193201</t>
+  </si>
+  <si>
+    <t>136193289</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 10.01.2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +581,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -586,7 +622,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -604,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -622,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -640,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -658,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -676,7 +712,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -694,7 +730,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -712,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -730,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -748,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -766,7 +802,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -784,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -802,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -820,7 +856,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -838,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -856,7 +892,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -874,7 +910,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -892,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -910,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -928,7 +964,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -946,7 +982,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -964,7 +1000,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -982,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -999,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1033,7 +1069,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1050,9 +1086,179 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4172AB3F-DBFE-4BEF-BA1F-DDBE63758219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79538C6C-C3AC-4776-8B16-66F51698AA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,76 @@
     <t>971</t>
   </si>
   <si>
-    <t>136173858</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 09.01.2026</t>
-  </si>
-  <si>
-    <t>136170210</t>
-  </si>
-  <si>
-    <t>136171546</t>
-  </si>
-  <si>
-    <t>136175067</t>
-  </si>
-  <si>
-    <t>136183440</t>
-  </si>
-  <si>
-    <t>136178688</t>
-  </si>
-  <si>
-    <t>136180909</t>
-  </si>
-  <si>
-    <t>136181228</t>
-  </si>
-  <si>
-    <t>136183003</t>
-  </si>
-  <si>
-    <t>136182993</t>
-  </si>
-  <si>
-    <t>136183445</t>
-  </si>
-  <si>
-    <t>136183868</t>
-  </si>
-  <si>
-    <t>136184573</t>
-  </si>
-  <si>
-    <t>136189005</t>
-  </si>
-  <si>
-    <t>136190131</t>
-  </si>
-  <si>
-    <t>136190400</t>
-  </si>
-  <si>
-    <t>136191737</t>
-  </si>
-  <si>
-    <t>136171095</t>
-  </si>
-  <si>
-    <t>136173811</t>
-  </si>
-  <si>
-    <t>136175335</t>
-  </si>
-  <si>
-    <t>136180055</t>
-  </si>
-  <si>
-    <t>136175787</t>
-  </si>
-  <si>
-    <t>136179340</t>
-  </si>
-  <si>
-    <t>136179420</t>
-  </si>
-  <si>
-    <t>136180160</t>
-  </si>
-  <si>
-    <t>136187264</t>
-  </si>
-  <si>
-    <t>136188003</t>
-  </si>
-  <si>
-    <t>136188400</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 09.01.2026</t>
-  </si>
-  <si>
-    <t>136192393</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 10.01.2026</t>
-  </si>
-  <si>
-    <t>136192406</t>
-  </si>
-  <si>
-    <t>136192446</t>
-  </si>
-  <si>
-    <t>136192563</t>
-  </si>
-  <si>
-    <t>136192685</t>
-  </si>
-  <si>
-    <t>136192821</t>
-  </si>
-  <si>
-    <t>136192867</t>
-  </si>
-  <si>
-    <t>136193201</t>
-  </si>
-  <si>
-    <t>136193289</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 10.01.2026</t>
+    <t>136195379</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 12.01.2026</t>
+  </si>
+  <si>
+    <t>136195347</t>
+  </si>
+  <si>
+    <t>136198144</t>
+  </si>
+  <si>
+    <t>136195758</t>
+  </si>
+  <si>
+    <t>136197327</t>
+  </si>
+  <si>
+    <t>136197125</t>
+  </si>
+  <si>
+    <t>136198641</t>
+  </si>
+  <si>
+    <t>136202046</t>
+  </si>
+  <si>
+    <t>136201958</t>
+  </si>
+  <si>
+    <t>136201676</t>
+  </si>
+  <si>
+    <t>136201859</t>
+  </si>
+  <si>
+    <t>136203620</t>
+  </si>
+  <si>
+    <t>136204723</t>
+  </si>
+  <si>
+    <t>136207148</t>
+  </si>
+  <si>
+    <t>136207584</t>
+  </si>
+  <si>
+    <t>136208630</t>
+  </si>
+  <si>
+    <t>136208314</t>
+  </si>
+  <si>
+    <t>136210724</t>
+  </si>
+  <si>
+    <t>136209005</t>
+  </si>
+  <si>
+    <t>136211894</t>
+  </si>
+  <si>
+    <t>136211696</t>
+  </si>
+  <si>
+    <t>136212538</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 12.01.2026</t>
   </si>
 </sst>
 </file>
@@ -581,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -622,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -640,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -658,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -676,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -694,7 +643,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -712,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -730,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -748,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -766,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -784,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -802,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -820,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -838,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -856,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -874,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -892,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -910,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -928,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -946,7 +895,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -964,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -982,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1000,267 +949,12 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1276,31 +970,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79538C6C-C3AC-4776-8B16-66F51698AA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E36B55-D298-4F01-AA6B-DEBF1BBA2144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,76 +54,91 @@
     <t>971</t>
   </si>
   <si>
-    <t>136195379</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 12.01.2026</t>
-  </si>
-  <si>
-    <t>136195347</t>
-  </si>
-  <si>
-    <t>136198144</t>
-  </si>
-  <si>
-    <t>136195758</t>
-  </si>
-  <si>
-    <t>136197327</t>
-  </si>
-  <si>
-    <t>136197125</t>
-  </si>
-  <si>
-    <t>136198641</t>
-  </si>
-  <si>
-    <t>136202046</t>
-  </si>
-  <si>
-    <t>136201958</t>
-  </si>
-  <si>
-    <t>136201676</t>
-  </si>
-  <si>
-    <t>136201859</t>
-  </si>
-  <si>
-    <t>136203620</t>
-  </si>
-  <si>
-    <t>136204723</t>
-  </si>
-  <si>
-    <t>136207148</t>
-  </si>
-  <si>
-    <t>136207584</t>
-  </si>
-  <si>
-    <t>136208630</t>
-  </si>
-  <si>
-    <t>136208314</t>
-  </si>
-  <si>
-    <t>136210724</t>
-  </si>
-  <si>
-    <t>136209005</t>
-  </si>
-  <si>
-    <t>136211894</t>
-  </si>
-  <si>
-    <t>136211696</t>
-  </si>
-  <si>
-    <t>136212538</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 12.01.2026</t>
+    <t>136214776</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 13.01.2026</t>
+  </si>
+  <si>
+    <t>136230945</t>
+  </si>
+  <si>
+    <t>136215997</t>
+  </si>
+  <si>
+    <t>136215727</t>
+  </si>
+  <si>
+    <t>136224643</t>
+  </si>
+  <si>
+    <t>136216352</t>
+  </si>
+  <si>
+    <t>136217072</t>
+  </si>
+  <si>
+    <t>136218438</t>
+  </si>
+  <si>
+    <t>136219099</t>
+  </si>
+  <si>
+    <t>136218884</t>
+  </si>
+  <si>
+    <t>136229542</t>
+  </si>
+  <si>
+    <t>136221800</t>
+  </si>
+  <si>
+    <t>136222108</t>
+  </si>
+  <si>
+    <t>136221904</t>
+  </si>
+  <si>
+    <t>136222135</t>
+  </si>
+  <si>
+    <t>136223495</t>
+  </si>
+  <si>
+    <t>136225062</t>
+  </si>
+  <si>
+    <t>136228649</t>
+  </si>
+  <si>
+    <t>136231937</t>
+  </si>
+  <si>
+    <t>136227037</t>
+  </si>
+  <si>
+    <t>136227998</t>
+  </si>
+  <si>
+    <t>136229148</t>
+  </si>
+  <si>
+    <t>136229580</t>
+  </si>
+  <si>
+    <t>136229833</t>
+  </si>
+  <si>
+    <t>136230600</t>
+  </si>
+  <si>
+    <t>136231386</t>
+  </si>
+  <si>
+    <t>136219756</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 13.01.2026</t>
   </si>
 </sst>
 </file>
@@ -530,7 +545,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,7 +622,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,7 +712,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,7 +730,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,7 +802,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -823,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -841,7 +856,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -877,7 +892,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,7 +910,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -931,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -949,12 +964,97 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -970,31 +1070,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E36B55-D298-4F01-AA6B-DEBF1BBA2144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DC3126-2AB1-48FB-8222-7AC2B58629C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,85 @@
     <t>971</t>
   </si>
   <si>
-    <t>136214776</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 13.01.2026</t>
-  </si>
-  <si>
-    <t>136230945</t>
-  </si>
-  <si>
-    <t>136215997</t>
-  </si>
-  <si>
-    <t>136215727</t>
-  </si>
-  <si>
-    <t>136224643</t>
-  </si>
-  <si>
-    <t>136216352</t>
-  </si>
-  <si>
-    <t>136217072</t>
-  </si>
-  <si>
-    <t>136218438</t>
-  </si>
-  <si>
-    <t>136219099</t>
-  </si>
-  <si>
-    <t>136218884</t>
-  </si>
-  <si>
-    <t>136229542</t>
-  </si>
-  <si>
-    <t>136221800</t>
-  </si>
-  <si>
-    <t>136222108</t>
-  </si>
-  <si>
-    <t>136221904</t>
-  </si>
-  <si>
-    <t>136222135</t>
-  </si>
-  <si>
-    <t>136223495</t>
-  </si>
-  <si>
-    <t>136225062</t>
-  </si>
-  <si>
-    <t>136228649</t>
-  </si>
-  <si>
-    <t>136231937</t>
-  </si>
-  <si>
-    <t>136227037</t>
-  </si>
-  <si>
-    <t>136227998</t>
-  </si>
-  <si>
-    <t>136229148</t>
-  </si>
-  <si>
-    <t>136229580</t>
-  </si>
-  <si>
-    <t>136229833</t>
-  </si>
-  <si>
-    <t>136230600</t>
-  </si>
-  <si>
-    <t>136231386</t>
-  </si>
-  <si>
-    <t>136219756</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 13.01.2026</t>
+    <t>136235713</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 14.01.2026</t>
+  </si>
+  <si>
+    <t>136236418</t>
+  </si>
+  <si>
+    <t>136249298</t>
+  </si>
+  <si>
+    <t>136236583</t>
+  </si>
+  <si>
+    <t>136236855</t>
+  </si>
+  <si>
+    <t>136237485</t>
+  </si>
+  <si>
+    <t>136237324</t>
+  </si>
+  <si>
+    <t>136239878</t>
+  </si>
+  <si>
+    <t>136238279</t>
+  </si>
+  <si>
+    <t>136238747</t>
+  </si>
+  <si>
+    <t>136239167</t>
+  </si>
+  <si>
+    <t>136242966</t>
+  </si>
+  <si>
+    <t>136242679</t>
+  </si>
+  <si>
+    <t>136243587</t>
+  </si>
+  <si>
+    <t>136244735</t>
+  </si>
+  <si>
+    <t>136245636</t>
+  </si>
+  <si>
+    <t>136246367</t>
+  </si>
+  <si>
+    <t>136247386</t>
+  </si>
+  <si>
+    <t>136247709</t>
+  </si>
+  <si>
+    <t>136247399</t>
+  </si>
+  <si>
+    <t>136248919</t>
+  </si>
+  <si>
+    <t>136248399</t>
+  </si>
+  <si>
+    <t>136249398</t>
+  </si>
+  <si>
+    <t>136249874</t>
+  </si>
+  <si>
+    <t>136251253</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +539,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -586,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -604,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -622,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -640,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -658,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -676,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -694,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -712,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -730,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -748,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -766,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -784,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -802,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -820,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -838,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -856,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -874,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -892,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -910,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -928,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -946,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -964,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -982,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -999,7 +993,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1016,43 +1010,9 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1070,31 +1030,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DC3126-2AB1-48FB-8222-7AC2B58629C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DE5639-690E-468E-B8B3-044E757257B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>136251253</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -580,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -598,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -616,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -634,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -652,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -670,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -688,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -706,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -724,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -742,7 +739,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -760,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -778,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -796,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -814,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -832,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -850,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -868,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -886,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -904,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -922,7 +919,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -940,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -958,7 +955,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -976,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -993,7 +990,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1010,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1030,31 +1027,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DE5639-690E-468E-B8B3-044E757257B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44DB49E-CDBD-4226-8E27-52F85D8FCDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>136251253</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -793,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -829,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -847,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -865,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -883,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -901,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -919,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -937,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -955,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -973,11 +976,12 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -990,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1007,7 +1011,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44DB49E-CDBD-4226-8E27-52F85D8FCDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516ADF13-9D5A-4B19-A633-478574FC36D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>136251253</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -580,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -598,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -616,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -634,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -652,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -670,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -688,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -706,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -724,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -742,7 +739,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -760,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -778,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -796,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -814,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -832,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -850,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -868,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -886,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -904,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -922,7 +919,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -940,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -958,7 +955,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -976,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -994,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1011,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1031,31 +1028,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516ADF13-9D5A-4B19-A633-478574FC36D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA258AA-C0FA-470C-8E14-D26580C0C3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,82 @@
     <t>971</t>
   </si>
   <si>
-    <t>136235713</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 14.01.2026</t>
-  </si>
-  <si>
-    <t>136236418</t>
-  </si>
-  <si>
-    <t>136249298</t>
-  </si>
-  <si>
-    <t>136236583</t>
-  </si>
-  <si>
-    <t>136236855</t>
-  </si>
-  <si>
-    <t>136237485</t>
-  </si>
-  <si>
-    <t>136237324</t>
-  </si>
-  <si>
-    <t>136239878</t>
-  </si>
-  <si>
-    <t>136238279</t>
-  </si>
-  <si>
-    <t>136238747</t>
-  </si>
-  <si>
-    <t>136239167</t>
-  </si>
-  <si>
-    <t>136242966</t>
-  </si>
-  <si>
-    <t>136242679</t>
-  </si>
-  <si>
-    <t>136243587</t>
-  </si>
-  <si>
-    <t>136244735</t>
-  </si>
-  <si>
-    <t>136245636</t>
-  </si>
-  <si>
-    <t>136246367</t>
-  </si>
-  <si>
-    <t>136247386</t>
-  </si>
-  <si>
-    <t>136247709</t>
-  </si>
-  <si>
-    <t>136247399</t>
-  </si>
-  <si>
-    <t>136248919</t>
-  </si>
-  <si>
-    <t>136248399</t>
-  </si>
-  <si>
-    <t>136249398</t>
-  </si>
-  <si>
-    <t>136249874</t>
-  </si>
-  <si>
-    <t>136251253</t>
+    <t>136255357</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  15.01.2026</t>
+  </si>
+  <si>
+    <t>136255500</t>
+  </si>
+  <si>
+    <t>136256081</t>
+  </si>
+  <si>
+    <t>136255752</t>
+  </si>
+  <si>
+    <t>136255887</t>
+  </si>
+  <si>
+    <t>136256287</t>
+  </si>
+  <si>
+    <t>136257278</t>
+  </si>
+  <si>
+    <t>136258316</t>
+  </si>
+  <si>
+    <t>136260832</t>
+  </si>
+  <si>
+    <t>136262055</t>
+  </si>
+  <si>
+    <t>136262385</t>
+  </si>
+  <si>
+    <t>136262700</t>
+  </si>
+  <si>
+    <t>136269526</t>
+  </si>
+  <si>
+    <t>136263738</t>
+  </si>
+  <si>
+    <t>136264660</t>
+  </si>
+  <si>
+    <t>136264451</t>
+  </si>
+  <si>
+    <t>136265819</t>
+  </si>
+  <si>
+    <t>136267521</t>
+  </si>
+  <si>
+    <t>136269130</t>
+  </si>
+  <si>
+    <t>136268660</t>
+  </si>
+  <si>
+    <t>136269040</t>
+  </si>
+  <si>
+    <t>136271828</t>
+  </si>
+  <si>
+    <t>136271915</t>
+  </si>
+  <si>
+    <t>136263248</t>
+  </si>
+  <si>
+    <t>Bloqueio Honda 15.01.2026</t>
   </si>
 </sst>
 </file>
@@ -536,7 +536,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -577,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,7 +739,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -793,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -829,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -847,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -865,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -883,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -901,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -919,7 +919,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -937,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -955,7 +955,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -973,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -991,26 +991,9 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1028,31 +1011,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA258AA-C0FA-470C-8E14-D26580C0C3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2D2A8-ED24-40ED-8F15-9AD92BD88BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,85 @@
     <t>971</t>
   </si>
   <si>
-    <t>136255357</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  15.01.2026</t>
-  </si>
-  <si>
-    <t>136255500</t>
-  </si>
-  <si>
-    <t>136256081</t>
-  </si>
-  <si>
-    <t>136255752</t>
-  </si>
-  <si>
-    <t>136255887</t>
-  </si>
-  <si>
-    <t>136256287</t>
-  </si>
-  <si>
-    <t>136257278</t>
-  </si>
-  <si>
-    <t>136258316</t>
-  </si>
-  <si>
-    <t>136260832</t>
-  </si>
-  <si>
-    <t>136262055</t>
-  </si>
-  <si>
-    <t>136262385</t>
-  </si>
-  <si>
-    <t>136262700</t>
-  </si>
-  <si>
-    <t>136269526</t>
-  </si>
-  <si>
-    <t>136263738</t>
-  </si>
-  <si>
-    <t>136264660</t>
-  </si>
-  <si>
-    <t>136264451</t>
-  </si>
-  <si>
-    <t>136265819</t>
-  </si>
-  <si>
-    <t>136267521</t>
-  </si>
-  <si>
-    <t>136269130</t>
-  </si>
-  <si>
-    <t>136268660</t>
-  </si>
-  <si>
-    <t>136269040</t>
-  </si>
-  <si>
-    <t>136271828</t>
-  </si>
-  <si>
-    <t>136271915</t>
-  </si>
-  <si>
-    <t>136263248</t>
-  </si>
-  <si>
-    <t>Bloqueio Honda 15.01.2026</t>
+    <t>136235713</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 14.01.2026</t>
+  </si>
+  <si>
+    <t>136236418</t>
+  </si>
+  <si>
+    <t>136249298</t>
+  </si>
+  <si>
+    <t>136236583</t>
+  </si>
+  <si>
+    <t>136236855</t>
+  </si>
+  <si>
+    <t>136237485</t>
+  </si>
+  <si>
+    <t>136237324</t>
+  </si>
+  <si>
+    <t>136239878</t>
+  </si>
+  <si>
+    <t>136238279</t>
+  </si>
+  <si>
+    <t>136238747</t>
+  </si>
+  <si>
+    <t>136239167</t>
+  </si>
+  <si>
+    <t>136242966</t>
+  </si>
+  <si>
+    <t>136242679</t>
+  </si>
+  <si>
+    <t>136243587</t>
+  </si>
+  <si>
+    <t>136244735</t>
+  </si>
+  <si>
+    <t>136245636</t>
+  </si>
+  <si>
+    <t>136246367</t>
+  </si>
+  <si>
+    <t>136247386</t>
+  </si>
+  <si>
+    <t>136247709</t>
+  </si>
+  <si>
+    <t>136247399</t>
+  </si>
+  <si>
+    <t>136248919</t>
+  </si>
+  <si>
+    <t>136248399</t>
+  </si>
+  <si>
+    <t>136249398</t>
+  </si>
+  <si>
+    <t>136249874</t>
+  </si>
+  <si>
+    <t>136251253</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -536,7 +539,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -577,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -793,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -829,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -847,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -865,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -883,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -901,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -919,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -937,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -955,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -973,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -991,9 +994,26 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1011,31 +1031,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2D2A8-ED24-40ED-8F15-9AD92BD88BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7237C20F-27CF-46BE-A587-9E110528048E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,7 @@
     <t>136251253</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 14.01.2026</t>
+    <t>Processado</t>
   </si>
 </sst>
 </file>
@@ -580,10 +580,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F2"/>
     </row>
@@ -598,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -616,10 +616,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F4"/>
     </row>
@@ -634,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -652,10 +652,10 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F6"/>
     </row>
@@ -670,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -688,10 +688,10 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F8"/>
     </row>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -724,10 +724,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F10"/>
     </row>
@@ -742,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -760,10 +760,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F12"/>
     </row>
@@ -778,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -796,10 +796,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F14"/>
     </row>
@@ -814,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -832,10 +832,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F16"/>
     </row>
@@ -850,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -868,10 +868,10 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F18"/>
     </row>
@@ -886,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -904,10 +904,10 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F20"/>
     </row>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -940,10 +940,10 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F22"/>
     </row>
@@ -958,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -976,10 +976,10 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F24"/>
     </row>
@@ -994,11 +994,12 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1011,11 +1012,12 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1031,31 +1033,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7237C20F-27CF-46BE-A587-9E110528048E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{7237C20F-27CF-46BE-A587-9E110528048E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
+    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -133,12 +133,16 @@
   </si>
   <si>
     <t>Processado</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao anexar arquivo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -200,34 +204,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -244,10 +248,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -282,7 +286,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -334,7 +338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -445,21 +449,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -476,7 +480,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -528,25 +532,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
+    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
+    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -601,7 +605,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F3"/>
     </row>
@@ -637,9 +641,11 @@
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -673,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F7"/>
     </row>
@@ -709,9 +715,11 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9"/>
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -745,7 +753,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F11"/>
     </row>
@@ -781,9 +789,11 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
+        <v>34</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -817,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F15"/>
     </row>
@@ -853,9 +863,11 @@
         <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
+        <v>34</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -889,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F19"/>
     </row>
@@ -925,9 +937,11 @@
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
+        <v>34</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -961,7 +975,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F23"/>
     </row>
@@ -997,9 +1011,11 @@
         <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
+        <v>34</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1022,12 +1038,12 @@
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{7237C20F-27CF-46BE-A587-9E110528048E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
+    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -133,16 +133,12 @@
   </si>
   <si>
     <t>Processado</t>
-  </si>
-  <si>
-    <t>Alerta: Falha ao anexar arquivo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -204,34 +200,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -248,10 +244,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -286,7 +282,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -338,7 +334,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -449,21 +445,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -480,7 +476,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -532,25 +528,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
-    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
-    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -641,11 +637,9 @@
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -717,9 +711,7 @@
       <c r="E9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -789,11 +781,9 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -863,11 +853,9 @@
         <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -937,11 +925,9 @@
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1011,11 +997,9 @@
         <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" t="s">
-        <v>35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1038,42 +1022,42 @@
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
+    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -133,12 +133,16 @@
   </si>
   <si>
     <t>Processado</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao anexar arquivo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -200,34 +204,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -244,10 +248,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -282,7 +286,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -334,7 +338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -445,21 +449,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -476,7 +480,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -528,25 +532,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
+    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
+    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -637,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F5"/>
     </row>
@@ -781,9 +785,11 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
+        <v>34</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -853,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F17"/>
     </row>
@@ -925,9 +931,11 @@
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
+        <v>34</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1022,12 +1030,12 @@
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962A6AAF-129D-41E1-9DEE-0F82BCCA5F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
+    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -133,16 +133,12 @@
   </si>
   <si>
     <t>Processado</t>
-  </si>
-  <si>
-    <t>Alerta: Falha ao anexar arquivo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -204,34 +200,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -248,10 +244,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -286,7 +282,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -338,7 +334,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -449,21 +445,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -480,7 +476,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -532,25 +528,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
-    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
-    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -785,11 +781,9 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -931,11 +925,9 @@
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1030,42 +1022,42 @@
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962A6AAF-129D-41E1-9DEE-0F82BCCA5F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A386E988-06F8-4B67-8F44-A4356D68D1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,88 +51,100 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>136280649</t>
+  </si>
+  <si>
     <t>971</t>
   </si>
   <si>
-    <t>136235713</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 14.01.2026</t>
-  </si>
-  <si>
-    <t>136236418</t>
-  </si>
-  <si>
-    <t>136249298</t>
-  </si>
-  <si>
-    <t>136236583</t>
-  </si>
-  <si>
-    <t>136236855</t>
-  </si>
-  <si>
-    <t>136237485</t>
-  </si>
-  <si>
-    <t>136237324</t>
-  </si>
-  <si>
-    <t>136239878</t>
-  </si>
-  <si>
-    <t>136238279</t>
-  </si>
-  <si>
-    <t>136238747</t>
-  </si>
-  <si>
-    <t>136239167</t>
-  </si>
-  <si>
-    <t>136242966</t>
-  </si>
-  <si>
-    <t>136242679</t>
-  </si>
-  <si>
-    <t>136243587</t>
-  </si>
-  <si>
-    <t>136244735</t>
-  </si>
-  <si>
-    <t>136245636</t>
-  </si>
-  <si>
-    <t>136246367</t>
-  </si>
-  <si>
-    <t>136247386</t>
-  </si>
-  <si>
-    <t>136247709</t>
-  </si>
-  <si>
-    <t>136247399</t>
-  </si>
-  <si>
-    <t>136248919</t>
-  </si>
-  <si>
-    <t>136248399</t>
-  </si>
-  <si>
-    <t>136249398</t>
-  </si>
-  <si>
-    <t>136249874</t>
-  </si>
-  <si>
-    <t>136251253</t>
-  </si>
-  <si>
-    <t>Processado</t>
+    <t>Bloqueios Honda 16.01.2026</t>
+  </si>
+  <si>
+    <t>136279796</t>
+  </si>
+  <si>
+    <t>136280068</t>
+  </si>
+  <si>
+    <t>136280809</t>
+  </si>
+  <si>
+    <t>136281748</t>
+  </si>
+  <si>
+    <t>136283017</t>
+  </si>
+  <si>
+    <t>136283599</t>
+  </si>
+  <si>
+    <t>136283640</t>
+  </si>
+  <si>
+    <t>136283793</t>
+  </si>
+  <si>
+    <t>136284587</t>
+  </si>
+  <si>
+    <t>136285487</t>
+  </si>
+  <si>
+    <t>136291933</t>
+  </si>
+  <si>
+    <t>136291798</t>
+  </si>
+  <si>
+    <t>136292207</t>
+  </si>
+  <si>
+    <t>136292651</t>
+  </si>
+  <si>
+    <t>136294450</t>
+  </si>
+  <si>
+    <t>134912954</t>
+  </si>
+  <si>
+    <t>136295992</t>
+  </si>
+  <si>
+    <t>136282263</t>
+  </si>
+  <si>
+    <t>136281899</t>
+  </si>
+  <si>
+    <t>136282412</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 16.01.2026</t>
+  </si>
+  <si>
+    <t>136298308</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 17.01.2026</t>
+  </si>
+  <si>
+    <t>136298687</t>
+  </si>
+  <si>
+    <t>136298820</t>
+  </si>
+  <si>
+    <t>136298947</t>
+  </si>
+  <si>
+    <t>136299136</t>
+  </si>
+  <si>
+    <t>136299187</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 17.01.2026</t>
   </si>
 </sst>
 </file>
@@ -539,7 +551,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,19 +583,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F2"/>
     </row>
@@ -592,16 +604,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F3"/>
     </row>
@@ -610,16 +622,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F4"/>
     </row>
@@ -628,16 +640,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F5"/>
     </row>
@@ -646,16 +658,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F6"/>
     </row>
@@ -664,16 +676,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F7"/>
     </row>
@@ -682,16 +694,16 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F8"/>
     </row>
@@ -700,16 +712,16 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F9"/>
     </row>
@@ -718,16 +730,16 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F10"/>
     </row>
@@ -736,16 +748,16 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F11"/>
     </row>
@@ -754,16 +766,16 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F12"/>
     </row>
@@ -772,13 +784,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -790,16 +802,16 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F14"/>
     </row>
@@ -808,16 +820,16 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F15"/>
     </row>
@@ -826,16 +838,16 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F16"/>
     </row>
@@ -844,16 +856,16 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F17"/>
     </row>
@@ -862,16 +874,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F18"/>
     </row>
@@ -880,16 +892,16 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F19"/>
     </row>
@@ -898,16 +910,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F20"/>
     </row>
@@ -916,13 +928,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -934,67 +946,67 @@
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1003,21 +1015,55 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A386E988-06F8-4B67-8F44-A4356D68D1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D9571F-FB01-47F7-8B18-37E4D1596FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,100 +51,61 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136280649</t>
+    <t>136301724</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 16.01.2026</t>
-  </si>
-  <si>
-    <t>136279796</t>
-  </si>
-  <si>
-    <t>136280068</t>
-  </si>
-  <si>
-    <t>136280809</t>
-  </si>
-  <si>
-    <t>136281748</t>
-  </si>
-  <si>
-    <t>136283017</t>
-  </si>
-  <si>
-    <t>136283599</t>
-  </si>
-  <si>
-    <t>136283640</t>
-  </si>
-  <si>
-    <t>136283793</t>
-  </si>
-  <si>
-    <t>136284587</t>
-  </si>
-  <si>
-    <t>136285487</t>
-  </si>
-  <si>
-    <t>136291933</t>
-  </si>
-  <si>
-    <t>136291798</t>
-  </si>
-  <si>
-    <t>136292207</t>
-  </si>
-  <si>
-    <t>136292651</t>
-  </si>
-  <si>
-    <t>136294450</t>
-  </si>
-  <si>
-    <t>134912954</t>
-  </si>
-  <si>
-    <t>136295992</t>
-  </si>
-  <si>
-    <t>136282263</t>
-  </si>
-  <si>
-    <t>136281899</t>
-  </si>
-  <si>
-    <t>136282412</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 16.01.2026</t>
-  </si>
-  <si>
-    <t>136298308</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 17.01.2026</t>
-  </si>
-  <si>
-    <t>136298687</t>
-  </si>
-  <si>
-    <t>136298820</t>
-  </si>
-  <si>
-    <t>136298947</t>
-  </si>
-  <si>
-    <t>136299136</t>
-  </si>
-  <si>
-    <t>136299187</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 17.01.2026</t>
+    <t>Bloqueios Honda 19.01.2026</t>
+  </si>
+  <si>
+    <t>136301812</t>
+  </si>
+  <si>
+    <t>136309357</t>
+  </si>
+  <si>
+    <t>136302690</t>
+  </si>
+  <si>
+    <t>136303415</t>
+  </si>
+  <si>
+    <t>136304524</t>
+  </si>
+  <si>
+    <t>136304789</t>
+  </si>
+  <si>
+    <t>136306869</t>
+  </si>
+  <si>
+    <t>136312719</t>
+  </si>
+  <si>
+    <t>136314843</t>
+  </si>
+  <si>
+    <t>136315876</t>
+  </si>
+  <si>
+    <t>136316628</t>
+  </si>
+  <si>
+    <t>136317211</t>
+  </si>
+  <si>
+    <t>136316727</t>
+  </si>
+  <si>
+    <t>136317483</t>
+  </si>
+  <si>
+    <t>136302924</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 19.01.2026</t>
   </si>
 </sst>
 </file>
@@ -551,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -592,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -610,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -628,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -646,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -664,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -682,7 +643,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -700,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -718,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -736,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -754,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -772,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -790,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -808,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -826,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -844,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -862,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -870,200 +831,31 @@
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1079,31 +871,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D9571F-FB01-47F7-8B18-37E4D1596FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231AB79C-3C6A-4DAD-89DC-EF83B30EA8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="28">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,61 +51,67 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136301724</t>
+    <t>136321907</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 19.01.2026</t>
-  </si>
-  <si>
-    <t>136301812</t>
-  </si>
-  <si>
-    <t>136309357</t>
-  </si>
-  <si>
-    <t>136302690</t>
-  </si>
-  <si>
-    <t>136303415</t>
-  </si>
-  <si>
-    <t>136304524</t>
-  </si>
-  <si>
-    <t>136304789</t>
-  </si>
-  <si>
-    <t>136306869</t>
-  </si>
-  <si>
-    <t>136312719</t>
-  </si>
-  <si>
-    <t>136314843</t>
-  </si>
-  <si>
-    <t>136315876</t>
-  </si>
-  <si>
-    <t>136316628</t>
-  </si>
-  <si>
-    <t>136317211</t>
-  </si>
-  <si>
-    <t>136316727</t>
-  </si>
-  <si>
-    <t>136317483</t>
-  </si>
-  <si>
-    <t>136302924</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 19.01.2026</t>
+    <t>Bloqueios Honda 20.01.2026</t>
+  </si>
+  <si>
+    <t>136322018</t>
+  </si>
+  <si>
+    <t>136322072</t>
+  </si>
+  <si>
+    <t>136322790</t>
+  </si>
+  <si>
+    <t>136322353</t>
+  </si>
+  <si>
+    <t>136324375</t>
+  </si>
+  <si>
+    <t>136323529</t>
+  </si>
+  <si>
+    <t>136324004</t>
+  </si>
+  <si>
+    <t>136325829</t>
+  </si>
+  <si>
+    <t>136325136</t>
+  </si>
+  <si>
+    <t>136327246</t>
+  </si>
+  <si>
+    <t>136329142</t>
+  </si>
+  <si>
+    <t>136329859</t>
+  </si>
+  <si>
+    <t>136330037</t>
+  </si>
+  <si>
+    <t>136334472</t>
+  </si>
+  <si>
+    <t>136334491</t>
+  </si>
+  <si>
+    <t>136335125</t>
+  </si>
+  <si>
+    <t>136338389</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 20.01.2026</t>
   </si>
 </sst>
 </file>
@@ -512,7 +518,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -553,7 +559,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -571,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -589,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -607,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -625,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -643,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -661,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -679,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -697,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -715,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -733,7 +739,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -751,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -769,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -787,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -805,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -823,39 +829,48 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231AB79C-3C6A-4DAD-89DC-EF83B30EA8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0E0029-791A-4CBA-BC9B-D1CEE4F131A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,67 +51,67 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136321907</t>
+    <t>136340622</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 20.01.2026</t>
-  </si>
-  <si>
-    <t>136322018</t>
-  </si>
-  <si>
-    <t>136322072</t>
-  </si>
-  <si>
-    <t>136322790</t>
-  </si>
-  <si>
-    <t>136322353</t>
-  </si>
-  <si>
-    <t>136324375</t>
-  </si>
-  <si>
-    <t>136323529</t>
-  </si>
-  <si>
-    <t>136324004</t>
-  </si>
-  <si>
-    <t>136325829</t>
-  </si>
-  <si>
-    <t>136325136</t>
-  </si>
-  <si>
-    <t>136327246</t>
-  </si>
-  <si>
-    <t>136329142</t>
-  </si>
-  <si>
-    <t>136329859</t>
-  </si>
-  <si>
-    <t>136330037</t>
-  </si>
-  <si>
-    <t>136334472</t>
-  </si>
-  <si>
-    <t>136334491</t>
-  </si>
-  <si>
-    <t>136335125</t>
-  </si>
-  <si>
-    <t>136338389</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 20.01.2026</t>
+    <t>Bloqueios Honda 21.01.2026</t>
+  </si>
+  <si>
+    <t>136343915</t>
+  </si>
+  <si>
+    <t>136343466</t>
+  </si>
+  <si>
+    <t>136345915</t>
+  </si>
+  <si>
+    <t>136344504</t>
+  </si>
+  <si>
+    <t>136356172</t>
+  </si>
+  <si>
+    <t>136352953</t>
+  </si>
+  <si>
+    <t>136347425</t>
+  </si>
+  <si>
+    <t>136347555</t>
+  </si>
+  <si>
+    <t>136347664</t>
+  </si>
+  <si>
+    <t>136347793</t>
+  </si>
+  <si>
+    <t>136350985</t>
+  </si>
+  <si>
+    <t>136351771</t>
+  </si>
+  <si>
+    <t>136355437</t>
+  </si>
+  <si>
+    <t>136354229</t>
+  </si>
+  <si>
+    <t>136353937</t>
+  </si>
+  <si>
+    <t>136354117</t>
+  </si>
+  <si>
+    <t>136356174</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 21.01.2026</t>
   </si>
 </sst>
 </file>
@@ -518,7 +518,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -871,6 +871,12 @@
         <v>6</v>
       </c>
       <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0E0029-791A-4CBA-BC9B-D1CEE4F131A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF10D919-E29D-408B-B818-C5595378257E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,67 +51,82 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136340622</t>
+    <t>136359821</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 21.01.2026</t>
-  </si>
-  <si>
-    <t>136343915</t>
-  </si>
-  <si>
-    <t>136343466</t>
-  </si>
-  <si>
-    <t>136345915</t>
-  </si>
-  <si>
-    <t>136344504</t>
-  </si>
-  <si>
-    <t>136356172</t>
-  </si>
-  <si>
-    <t>136352953</t>
-  </si>
-  <si>
-    <t>136347425</t>
-  </si>
-  <si>
-    <t>136347555</t>
-  </si>
-  <si>
-    <t>136347664</t>
-  </si>
-  <si>
-    <t>136347793</t>
-  </si>
-  <si>
-    <t>136350985</t>
-  </si>
-  <si>
-    <t>136351771</t>
-  </si>
-  <si>
-    <t>136355437</t>
-  </si>
-  <si>
-    <t>136354229</t>
-  </si>
-  <si>
-    <t>136353937</t>
-  </si>
-  <si>
-    <t>136354117</t>
-  </si>
-  <si>
-    <t>136356174</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 21.01.2026</t>
+    <t>Bloqueios Honda 22.01.2026</t>
+  </si>
+  <si>
+    <t>136359929</t>
+  </si>
+  <si>
+    <t>136360482</t>
+  </si>
+  <si>
+    <t>136362623</t>
+  </si>
+  <si>
+    <t>136362798</t>
+  </si>
+  <si>
+    <t>136371537</t>
+  </si>
+  <si>
+    <t>136363868</t>
+  </si>
+  <si>
+    <t>136372392</t>
+  </si>
+  <si>
+    <t>136365429</t>
+  </si>
+  <si>
+    <t>136365666</t>
+  </si>
+  <si>
+    <t>136365552</t>
+  </si>
+  <si>
+    <t>136366836</t>
+  </si>
+  <si>
+    <t>136367482</t>
+  </si>
+  <si>
+    <t>136369588</t>
+  </si>
+  <si>
+    <t>136374914</t>
+  </si>
+  <si>
+    <t>134535705</t>
+  </si>
+  <si>
+    <t>136372099</t>
+  </si>
+  <si>
+    <t>136371192</t>
+  </si>
+  <si>
+    <t>136372466</t>
+  </si>
+  <si>
+    <t>136373156</t>
+  </si>
+  <si>
+    <t>136374734</t>
+  </si>
+  <si>
+    <t>136375770</t>
+  </si>
+  <si>
+    <t>136363382</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.01.2026</t>
   </si>
 </sst>
 </file>
@@ -518,7 +533,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -559,7 +574,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -577,7 +592,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -595,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -613,7 +628,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -631,7 +646,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -649,7 +664,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -667,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -685,7 +700,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -703,7 +718,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -721,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -739,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -757,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -775,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -793,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -811,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -829,7 +844,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -847,7 +862,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -865,18 +880,102 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF10D919-E29D-408B-B818-C5595378257E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1C9FBD-85D2-4377-BF01-A4ED31426BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="47">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,82 +51,124 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136359821</t>
+    <t>136398663</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 22.01.2026</t>
-  </si>
-  <si>
-    <t>136359929</t>
-  </si>
-  <si>
-    <t>136360482</t>
-  </si>
-  <si>
-    <t>136362623</t>
-  </si>
-  <si>
-    <t>136362798</t>
-  </si>
-  <si>
-    <t>136371537</t>
-  </si>
-  <si>
-    <t>136363868</t>
-  </si>
-  <si>
-    <t>136372392</t>
-  </si>
-  <si>
-    <t>136365429</t>
-  </si>
-  <si>
-    <t>136365666</t>
-  </si>
-  <si>
-    <t>136365552</t>
-  </si>
-  <si>
-    <t>136366836</t>
-  </si>
-  <si>
-    <t>136367482</t>
-  </si>
-  <si>
-    <t>136369588</t>
-  </si>
-  <si>
-    <t>136374914</t>
-  </si>
-  <si>
-    <t>134535705</t>
-  </si>
-  <si>
-    <t>136372099</t>
-  </si>
-  <si>
-    <t>136371192</t>
-  </si>
-  <si>
-    <t>136372466</t>
-  </si>
-  <si>
-    <t>136373156</t>
-  </si>
-  <si>
-    <t>136374734</t>
-  </si>
-  <si>
-    <t>136375770</t>
-  </si>
-  <si>
-    <t>136363382</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.01.2026</t>
+    <t>Bloqueios Honda 24.01.2026</t>
+  </si>
+  <si>
+    <t>136398784</t>
+  </si>
+  <si>
+    <t>136398865</t>
+  </si>
+  <si>
+    <t>136399013</t>
+  </si>
+  <si>
+    <t>136398997</t>
+  </si>
+  <si>
+    <t>136399163</t>
+  </si>
+  <si>
+    <t>136399590</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 24.01.2026</t>
+  </si>
+  <si>
+    <t>136379090</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 23.01.2026</t>
+  </si>
+  <si>
+    <t>136379407</t>
+  </si>
+  <si>
+    <t>136390953</t>
+  </si>
+  <si>
+    <t>136381079</t>
+  </si>
+  <si>
+    <t>136381314</t>
+  </si>
+  <si>
+    <t>136382318</t>
+  </si>
+  <si>
+    <t>136389910</t>
+  </si>
+  <si>
+    <t>136388363</t>
+  </si>
+  <si>
+    <t>136383810</t>
+  </si>
+  <si>
+    <t>136385168</t>
+  </si>
+  <si>
+    <t>136385013</t>
+  </si>
+  <si>
+    <t>136385218</t>
+  </si>
+  <si>
+    <t>136386534</t>
+  </si>
+  <si>
+    <t>136387571</t>
+  </si>
+  <si>
+    <t>136388704</t>
+  </si>
+  <si>
+    <t>136389724</t>
+  </si>
+  <si>
+    <t>136389693</t>
+  </si>
+  <si>
+    <t>136392377</t>
+  </si>
+  <si>
+    <t>136391490</t>
+  </si>
+  <si>
+    <t>136391788</t>
+  </si>
+  <si>
+    <t>136392065</t>
+  </si>
+  <si>
+    <t>136393792</t>
+  </si>
+  <si>
+    <t>136395643</t>
+  </si>
+  <si>
+    <t>136394700</t>
+  </si>
+  <si>
+    <t>136397458</t>
+  </si>
+  <si>
+    <t>136383238</t>
+  </si>
+  <si>
+    <t>136383250</t>
+  </si>
+  <si>
+    <t>136384430</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 23.01.2026</t>
   </si>
 </sst>
 </file>
@@ -533,7 +575,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -573,8 +615,8 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>32</v>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -591,8 +633,8 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -609,8 +651,8 @@
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -627,8 +669,8 @@
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -645,8 +687,8 @@
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -663,8 +705,8 @@
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -681,8 +723,8 @@
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -691,291 +733,479 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -991,31 +1221,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1C9FBD-85D2-4377-BF01-A4ED31426BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4F4868-F7D3-4A59-BA0A-F83686AADBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4365" yWindow="3015" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -78,9 +78,6 @@
     <t>136399590</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 24.01.2026</t>
-  </si>
-  <si>
     <t>136379090</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
   </si>
   <si>
     <t>136384430</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 23.01.2026</t>
   </si>
 </sst>
 </file>
@@ -238,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -258,6 +252,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,8 +610,8 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -633,8 +628,8 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -651,8 +646,8 @@
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -669,8 +664,8 @@
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -687,8 +682,8 @@
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -705,8 +700,8 @@
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -723,26 +718,26 @@
       <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
+      <c r="D8" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F8"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -750,16 +745,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -767,16 +762,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -784,16 +779,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -801,16 +796,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,16 +813,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -835,16 +830,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -852,16 +847,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -869,16 +864,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -886,16 +881,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -903,16 +898,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -920,16 +915,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -937,16 +932,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -954,16 +949,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -971,16 +966,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -988,16 +983,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1005,16 +1000,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1022,16 +1017,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1039,16 +1034,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1056,16 +1051,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1073,16 +1068,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1090,16 +1085,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1107,16 +1102,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1119,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1141,16 +1136,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1158,16 +1153,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1175,16 +1170,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1192,16 +1187,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1221,31 +1216,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F64A8B5-4ED0-4CFE-A5D2-D29BE396B792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,102 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136401434</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 26.01.2026</t>
+  </si>
+  <si>
+    <t>136401612</t>
+  </si>
+  <si>
+    <t>136405623</t>
+  </si>
+  <si>
+    <t>136401952</t>
+  </si>
+  <si>
+    <t>136402250</t>
+  </si>
+  <si>
+    <t>136402621</t>
+  </si>
+  <si>
+    <t>136402942</t>
+  </si>
+  <si>
+    <t>136403229</t>
+  </si>
+  <si>
+    <t>136403483</t>
+  </si>
+  <si>
+    <t>136404475</t>
+  </si>
+  <si>
+    <t>136404412</t>
+  </si>
+  <si>
+    <t>136405254</t>
+  </si>
+  <si>
+    <t>136407105</t>
+  </si>
+  <si>
+    <t>136406232</t>
+  </si>
+  <si>
+    <t>136406148</t>
+  </si>
+  <si>
+    <t>136406767</t>
+  </si>
+  <si>
+    <t>136406912</t>
+  </si>
+  <si>
+    <t>136407048</t>
+  </si>
+  <si>
+    <t>136410890</t>
+  </si>
+  <si>
+    <t>136407707</t>
+  </si>
+  <si>
+    <t>136408433</t>
+  </si>
+  <si>
+    <t>136415399</t>
+  </si>
+  <si>
+    <t>136411626</t>
+  </si>
+  <si>
+    <t>136411712</t>
+  </si>
+  <si>
+    <t>136411654</t>
+  </si>
+  <si>
+    <t>136412442</t>
+  </si>
+  <si>
+    <t>136413143</t>
+  </si>
+  <si>
+    <t>136414028</t>
+  </si>
+  <si>
+    <t>136416049</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -455,7 +551,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +582,522 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -605,31 +1113,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F64A8B5-4ED0-4CFE-A5D2-D29BE396B792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,102 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136401434</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 26.01.2026</t>
-  </si>
-  <si>
-    <t>136401612</t>
-  </si>
-  <si>
-    <t>136405623</t>
-  </si>
-  <si>
-    <t>136401952</t>
-  </si>
-  <si>
-    <t>136402250</t>
-  </si>
-  <si>
-    <t>136402621</t>
-  </si>
-  <si>
-    <t>136402942</t>
-  </si>
-  <si>
-    <t>136403229</t>
-  </si>
-  <si>
-    <t>136403483</t>
-  </si>
-  <si>
-    <t>136404475</t>
-  </si>
-  <si>
-    <t>136404412</t>
-  </si>
-  <si>
-    <t>136405254</t>
-  </si>
-  <si>
-    <t>136407105</t>
-  </si>
-  <si>
-    <t>136406232</t>
-  </si>
-  <si>
-    <t>136406148</t>
-  </si>
-  <si>
-    <t>136406767</t>
-  </si>
-  <si>
-    <t>136406912</t>
-  </si>
-  <si>
-    <t>136407048</t>
-  </si>
-  <si>
-    <t>136410890</t>
-  </si>
-  <si>
-    <t>136407707</t>
-  </si>
-  <si>
-    <t>136408433</t>
-  </si>
-  <si>
-    <t>136415399</t>
-  </si>
-  <si>
-    <t>136411626</t>
-  </si>
-  <si>
-    <t>136411712</t>
-  </si>
-  <si>
-    <t>136411654</t>
-  </si>
-  <si>
-    <t>136412442</t>
-  </si>
-  <si>
-    <t>136413143</t>
-  </si>
-  <si>
-    <t>136414028</t>
-  </si>
-  <si>
-    <t>136416049</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -551,7 +455,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -582,522 +486,110 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="C8" s="6"/>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1113,31 +605,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE3E8F-E355-4314-ADE9-7ACED0E711DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,81 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136419563</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 27.01.2026</t>
+  </si>
+  <si>
+    <t>136425782</t>
+  </si>
+  <si>
+    <t>136420387</t>
+  </si>
+  <si>
+    <t>136420583</t>
+  </si>
+  <si>
+    <t>136426032</t>
+  </si>
+  <si>
+    <t>136422770</t>
+  </si>
+  <si>
+    <t>136424796</t>
+  </si>
+  <si>
+    <t>136424783</t>
+  </si>
+  <si>
+    <t>136425343</t>
+  </si>
+  <si>
+    <t>136425328</t>
+  </si>
+  <si>
+    <t>136426558</t>
+  </si>
+  <si>
+    <t>136425832</t>
+  </si>
+  <si>
+    <t>136426136</t>
+  </si>
+  <si>
+    <t>136426439</t>
+  </si>
+  <si>
+    <t>136427104</t>
+  </si>
+  <si>
+    <t>136428396</t>
+  </si>
+  <si>
+    <t>136430352</t>
+  </si>
+  <si>
+    <t>136430712</t>
+  </si>
+  <si>
+    <t>136434305</t>
+  </si>
+  <si>
+    <t>136435194</t>
+  </si>
+  <si>
+    <t>136435854</t>
+  </si>
+  <si>
+    <t>136436281</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 27.01.2026</t>
   </si>
 </sst>
 </file>
@@ -455,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +561,400 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -605,31 +970,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE3E8F-E355-4314-ADE9-7ACED0E711DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716EE1A5-6650-43C5-9989-1F78F860B5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,79 +51,88 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136419563</t>
+    <t>136452144</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 27.01.2026</t>
-  </si>
-  <si>
-    <t>136425782</t>
-  </si>
-  <si>
-    <t>136420387</t>
-  </si>
-  <si>
-    <t>136420583</t>
-  </si>
-  <si>
-    <t>136426032</t>
-  </si>
-  <si>
-    <t>136422770</t>
-  </si>
-  <si>
-    <t>136424796</t>
-  </si>
-  <si>
-    <t>136424783</t>
-  </si>
-  <si>
-    <t>136425343</t>
-  </si>
-  <si>
-    <t>136425328</t>
-  </si>
-  <si>
-    <t>136426558</t>
-  </si>
-  <si>
-    <t>136425832</t>
-  </si>
-  <si>
-    <t>136426136</t>
-  </si>
-  <si>
-    <t>136426439</t>
-  </si>
-  <si>
-    <t>136427104</t>
-  </si>
-  <si>
-    <t>136428396</t>
-  </si>
-  <si>
-    <t>136430352</t>
-  </si>
-  <si>
-    <t>136430712</t>
-  </si>
-  <si>
-    <t>136434305</t>
-  </si>
-  <si>
-    <t>136435194</t>
-  </si>
-  <si>
-    <t>136435854</t>
-  </si>
-  <si>
-    <t>136436281</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 27.01.2026</t>
+    <t>Bloqueios Honda 28.01.2026</t>
+  </si>
+  <si>
+    <t>136438850</t>
+  </si>
+  <si>
+    <t>136439499</t>
+  </si>
+  <si>
+    <t>136439804</t>
+  </si>
+  <si>
+    <t>136440732</t>
+  </si>
+  <si>
+    <t>136441257</t>
+  </si>
+  <si>
+    <t>136442856</t>
+  </si>
+  <si>
+    <t>136445038</t>
+  </si>
+  <si>
+    <t>136447827</t>
+  </si>
+  <si>
+    <t>136444877</t>
+  </si>
+  <si>
+    <t>136445437</t>
+  </si>
+  <si>
+    <t>136447085</t>
+  </si>
+  <si>
+    <t>136454290</t>
+  </si>
+  <si>
+    <t>136451327</t>
+  </si>
+  <si>
+    <t>136449033</t>
+  </si>
+  <si>
+    <t>136450645</t>
+  </si>
+  <si>
+    <t>136450587</t>
+  </si>
+  <si>
+    <t>136451994</t>
+  </si>
+  <si>
+    <t>136451488</t>
+  </si>
+  <si>
+    <t>136451808</t>
+  </si>
+  <si>
+    <t>136454451</t>
+  </si>
+  <si>
+    <t>136453163</t>
+  </si>
+  <si>
+    <t>136455100</t>
+  </si>
+  <si>
+    <t>136455046</t>
+  </si>
+  <si>
+    <t>136455632</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -530,7 +539,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -823,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -841,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -877,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -931,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -949,12 +958,66 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716EE1A5-6650-43C5-9989-1F78F860B5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,90 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136452144</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 28.01.2026</t>
-  </si>
-  <si>
-    <t>136438850</t>
-  </si>
-  <si>
-    <t>136439499</t>
-  </si>
-  <si>
-    <t>136439804</t>
-  </si>
-  <si>
-    <t>136440732</t>
-  </si>
-  <si>
-    <t>136441257</t>
-  </si>
-  <si>
-    <t>136442856</t>
-  </si>
-  <si>
-    <t>136445038</t>
-  </si>
-  <si>
-    <t>136447827</t>
-  </si>
-  <si>
-    <t>136444877</t>
-  </si>
-  <si>
-    <t>136445437</t>
-  </si>
-  <si>
-    <t>136447085</t>
-  </si>
-  <si>
-    <t>136454290</t>
-  </si>
-  <si>
-    <t>136451327</t>
-  </si>
-  <si>
-    <t>136449033</t>
-  </si>
-  <si>
-    <t>136450645</t>
-  </si>
-  <si>
-    <t>136450587</t>
-  </si>
-  <si>
-    <t>136451994</t>
-  </si>
-  <si>
-    <t>136451488</t>
-  </si>
-  <si>
-    <t>136451808</t>
-  </si>
-  <si>
-    <t>136454451</t>
-  </si>
-  <si>
-    <t>136453163</t>
-  </si>
-  <si>
-    <t>136455100</t>
-  </si>
-  <si>
-    <t>136455046</t>
-  </si>
-  <si>
-    <t>136455632</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -570,453 +486,109 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="C8" s="6"/>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
   </sheetData>
@@ -1033,31 +605,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDA15DF-1C0C-45C7-BF00-FAFAB021B2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,81 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136457601</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 29.01.2026</t>
+  </si>
+  <si>
+    <t>136458355</t>
+  </si>
+  <si>
+    <t>136461168</t>
+  </si>
+  <si>
+    <t>136461916</t>
+  </si>
+  <si>
+    <t>136462796</t>
+  </si>
+  <si>
+    <t>136462956</t>
+  </si>
+  <si>
+    <t>136463391</t>
+  </si>
+  <si>
+    <t>136463631</t>
+  </si>
+  <si>
+    <t>136465386</t>
+  </si>
+  <si>
+    <t>136466330</t>
+  </si>
+  <si>
+    <t>136467507</t>
+  </si>
+  <si>
+    <t>136468073</t>
+  </si>
+  <si>
+    <t>136469357</t>
+  </si>
+  <si>
+    <t>136470042</t>
+  </si>
+  <si>
+    <t>136470695</t>
+  </si>
+  <si>
+    <t>134157582</t>
+  </si>
+  <si>
+    <t>136471804</t>
+  </si>
+  <si>
+    <t>136472862</t>
+  </si>
+  <si>
+    <t>136473431</t>
+  </si>
+  <si>
+    <t>136473876</t>
+  </si>
+  <si>
+    <t>136471188</t>
+  </si>
+  <si>
+    <t>136461983</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 29.01.2026</t>
   </si>
 </sst>
 </file>
@@ -455,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +561,400 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -605,31 +970,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDA15DF-1C0C-45C7-BF00-FAFAB021B2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE07963-F841-462E-B5C3-A3A913F7ECD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="68">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,79 +51,187 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136457601</t>
+    <t>136477144</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 29.01.2026</t>
-  </si>
-  <si>
-    <t>136458355</t>
-  </si>
-  <si>
-    <t>136461168</t>
-  </si>
-  <si>
-    <t>136461916</t>
-  </si>
-  <si>
-    <t>136462796</t>
-  </si>
-  <si>
-    <t>136462956</t>
-  </si>
-  <si>
-    <t>136463391</t>
-  </si>
-  <si>
-    <t>136463631</t>
-  </si>
-  <si>
-    <t>136465386</t>
-  </si>
-  <si>
-    <t>136466330</t>
-  </si>
-  <si>
-    <t>136467507</t>
-  </si>
-  <si>
-    <t>136468073</t>
-  </si>
-  <si>
-    <t>136469357</t>
-  </si>
-  <si>
-    <t>136470042</t>
-  </si>
-  <si>
-    <t>136470695</t>
-  </si>
-  <si>
-    <t>134157582</t>
-  </si>
-  <si>
-    <t>136471804</t>
-  </si>
-  <si>
-    <t>136472862</t>
-  </si>
-  <si>
-    <t>136473431</t>
-  </si>
-  <si>
-    <t>136473876</t>
-  </si>
-  <si>
-    <t>136471188</t>
-  </si>
-  <si>
-    <t>136461983</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 29.01.2026</t>
+    <t>Bloqueios Honda 30.01.2026</t>
+  </si>
+  <si>
+    <t>136490038</t>
+  </si>
+  <si>
+    <t>136479282</t>
+  </si>
+  <si>
+    <t>136479311</t>
+  </si>
+  <si>
+    <t>136492715</t>
+  </si>
+  <si>
+    <t>136480822</t>
+  </si>
+  <si>
+    <t>136481175</t>
+  </si>
+  <si>
+    <t>136495212</t>
+  </si>
+  <si>
+    <t>133618070</t>
+  </si>
+  <si>
+    <t>136485277</t>
+  </si>
+  <si>
+    <t>136486860</t>
+  </si>
+  <si>
+    <t>136488121</t>
+  </si>
+  <si>
+    <t>136489325</t>
+  </si>
+  <si>
+    <t>136488324</t>
+  </si>
+  <si>
+    <t>136489711</t>
+  </si>
+  <si>
+    <t>136490572</t>
+  </si>
+  <si>
+    <t>136490810</t>
+  </si>
+  <si>
+    <t>136490823</t>
+  </si>
+  <si>
+    <t>136494128</t>
+  </si>
+  <si>
+    <t>136491765</t>
+  </si>
+  <si>
+    <t>136492400</t>
+  </si>
+  <si>
+    <t>136492646</t>
+  </si>
+  <si>
+    <t>136494987</t>
+  </si>
+  <si>
+    <t>136494363</t>
+  </si>
+  <si>
+    <t>136494968</t>
+  </si>
+  <si>
+    <t>136494937</t>
+  </si>
+  <si>
+    <t>136495863</t>
+  </si>
+  <si>
+    <t>136495135</t>
+  </si>
+  <si>
+    <t>136495791</t>
+  </si>
+  <si>
+    <t>136496345</t>
+  </si>
+  <si>
+    <t>136496880</t>
+  </si>
+  <si>
+    <t>136497476</t>
+  </si>
+  <si>
+    <t>136482202</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 30.01.2026</t>
+  </si>
+  <si>
+    <t>136500415</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 01.02.2026</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 01.02.2026</t>
+  </si>
+  <si>
+    <t>136497953</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 31.01.2026</t>
+  </si>
+  <si>
+    <t>136498100</t>
+  </si>
+  <si>
+    <t>136498064</t>
+  </si>
+  <si>
+    <t>136498127</t>
+  </si>
+  <si>
+    <t>136498186</t>
+  </si>
+  <si>
+    <t>136498274</t>
+  </si>
+  <si>
+    <t>136498402</t>
+  </si>
+  <si>
+    <t>136498385</t>
+  </si>
+  <si>
+    <t>136498519</t>
+  </si>
+  <si>
+    <t>136498631</t>
+  </si>
+  <si>
+    <t>136498840</t>
+  </si>
+  <si>
+    <t>136498885</t>
+  </si>
+  <si>
+    <t>136498994</t>
+  </si>
+  <si>
+    <t>136498795</t>
+  </si>
+  <si>
+    <t>136498865</t>
+  </si>
+  <si>
+    <t>136498866</t>
+  </si>
+  <si>
+    <t>136499160</t>
+  </si>
+  <si>
+    <t>136499417</t>
+  </si>
+  <si>
+    <t>136499500</t>
+  </si>
+  <si>
+    <t>136499552</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 31.01.2026</t>
   </si>
 </sst>
 </file>
@@ -530,7 +638,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,7 +895,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -823,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -841,7 +949,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,7 +967,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -877,7 +985,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,7 +1003,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,7 +1021,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -931,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -949,12 +1057,559 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -970,31 +1625,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE07963-F841-462E-B5C3-A3A913F7ECD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF798A0-A9F8-4E42-B32F-F7749FD73249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,187 +51,82 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136477144</t>
+    <t>136501644</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 30.01.2026</t>
-  </si>
-  <si>
-    <t>136490038</t>
-  </si>
-  <si>
-    <t>136479282</t>
-  </si>
-  <si>
-    <t>136479311</t>
-  </si>
-  <si>
-    <t>136492715</t>
-  </si>
-  <si>
-    <t>136480822</t>
-  </si>
-  <si>
-    <t>136481175</t>
-  </si>
-  <si>
-    <t>136495212</t>
-  </si>
-  <si>
-    <t>133618070</t>
-  </si>
-  <si>
-    <t>136485277</t>
-  </si>
-  <si>
-    <t>136486860</t>
-  </si>
-  <si>
-    <t>136488121</t>
-  </si>
-  <si>
-    <t>136489325</t>
-  </si>
-  <si>
-    <t>136488324</t>
-  </si>
-  <si>
-    <t>136489711</t>
-  </si>
-  <si>
-    <t>136490572</t>
-  </si>
-  <si>
-    <t>136490810</t>
-  </si>
-  <si>
-    <t>136490823</t>
-  </si>
-  <si>
-    <t>136494128</t>
-  </si>
-  <si>
-    <t>136491765</t>
-  </si>
-  <si>
-    <t>136492400</t>
-  </si>
-  <si>
-    <t>136492646</t>
-  </si>
-  <si>
-    <t>136494987</t>
-  </si>
-  <si>
-    <t>136494363</t>
-  </si>
-  <si>
-    <t>136494968</t>
-  </si>
-  <si>
-    <t>136494937</t>
-  </si>
-  <si>
-    <t>136495863</t>
-  </si>
-  <si>
-    <t>136495135</t>
-  </si>
-  <si>
-    <t>136495791</t>
-  </si>
-  <si>
-    <t>136496345</t>
-  </si>
-  <si>
-    <t>136496880</t>
-  </si>
-  <si>
-    <t>136497476</t>
-  </si>
-  <si>
-    <t>136482202</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 30.01.2026</t>
-  </si>
-  <si>
-    <t>136500415</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 01.02.2026</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 01.02.2026</t>
-  </si>
-  <si>
-    <t>136497953</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 31.01.2026</t>
-  </si>
-  <si>
-    <t>136498100</t>
-  </si>
-  <si>
-    <t>136498064</t>
-  </si>
-  <si>
-    <t>136498127</t>
-  </si>
-  <si>
-    <t>136498186</t>
-  </si>
-  <si>
-    <t>136498274</t>
-  </si>
-  <si>
-    <t>136498402</t>
-  </si>
-  <si>
-    <t>136498385</t>
-  </si>
-  <si>
-    <t>136498519</t>
-  </si>
-  <si>
-    <t>136498631</t>
-  </si>
-  <si>
-    <t>136498840</t>
-  </si>
-  <si>
-    <t>136498885</t>
-  </si>
-  <si>
-    <t>136498994</t>
-  </si>
-  <si>
-    <t>136498795</t>
-  </si>
-  <si>
-    <t>136498865</t>
-  </si>
-  <si>
-    <t>136498866</t>
-  </si>
-  <si>
-    <t>136499160</t>
-  </si>
-  <si>
-    <t>136499417</t>
-  </si>
-  <si>
-    <t>136499500</t>
-  </si>
-  <si>
-    <t>136499552</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 31.01.2026</t>
+    <t>Bloqueios Honda 02.02.2026</t>
+  </si>
+  <si>
+    <t>136501486</t>
+  </si>
+  <si>
+    <t>136501684</t>
+  </si>
+  <si>
+    <t>136502041</t>
+  </si>
+  <si>
+    <t>136502273</t>
+  </si>
+  <si>
+    <t>136502271</t>
+  </si>
+  <si>
+    <t>136503243</t>
+  </si>
+  <si>
+    <t>136504085</t>
+  </si>
+  <si>
+    <t>136504876</t>
+  </si>
+  <si>
+    <t>136504889</t>
+  </si>
+  <si>
+    <t>136506630</t>
+  </si>
+  <si>
+    <t>136507155</t>
+  </si>
+  <si>
+    <t>136507707</t>
+  </si>
+  <si>
+    <t>133986000</t>
+  </si>
+  <si>
+    <t>136510710</t>
+  </si>
+  <si>
+    <t>136511194</t>
+  </si>
+  <si>
+    <t>136511487</t>
+  </si>
+  <si>
+    <t>136512557</t>
+  </si>
+  <si>
+    <t>136512938</t>
+  </si>
+  <si>
+    <t>136513176</t>
+  </si>
+  <si>
+    <t>136513572</t>
+  </si>
+  <si>
+    <t>136515355</t>
+  </si>
+  <si>
+    <t>136518655</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 02.02.2026</t>
   </si>
 </sst>
 </file>
@@ -638,7 +533,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -679,7 +574,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -697,7 +592,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -715,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -733,7 +628,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -751,7 +646,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -769,7 +664,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -787,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -805,7 +700,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -823,7 +718,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -841,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -859,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -877,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -895,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -913,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -931,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -949,7 +844,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -967,7 +862,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -985,7 +880,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1003,7 +898,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1021,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1039,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1057,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1075,541 +970,12 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1625,31 +991,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF798A0-A9F8-4E42-B32F-F7749FD73249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83610AF-E896-40B6-9E66-8E3B6CDDC3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,82 +51,79 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136501644</t>
+    <t>136520229</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 02.02.2026</t>
-  </si>
-  <si>
-    <t>136501486</t>
-  </si>
-  <si>
-    <t>136501684</t>
-  </si>
-  <si>
-    <t>136502041</t>
-  </si>
-  <si>
-    <t>136502273</t>
-  </si>
-  <si>
-    <t>136502271</t>
-  </si>
-  <si>
-    <t>136503243</t>
-  </si>
-  <si>
-    <t>136504085</t>
-  </si>
-  <si>
-    <t>136504876</t>
-  </si>
-  <si>
-    <t>136504889</t>
-  </si>
-  <si>
-    <t>136506630</t>
-  </si>
-  <si>
-    <t>136507155</t>
-  </si>
-  <si>
-    <t>136507707</t>
-  </si>
-  <si>
-    <t>133986000</t>
-  </si>
-  <si>
-    <t>136510710</t>
-  </si>
-  <si>
-    <t>136511194</t>
-  </si>
-  <si>
-    <t>136511487</t>
-  </si>
-  <si>
-    <t>136512557</t>
-  </si>
-  <si>
-    <t>136512938</t>
-  </si>
-  <si>
-    <t>136513176</t>
-  </si>
-  <si>
-    <t>136513572</t>
-  </si>
-  <si>
-    <t>136515355</t>
-  </si>
-  <si>
-    <t>136518655</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 02.02.2026</t>
+    <t>Bloqueios Honda 03.02.2026</t>
+  </si>
+  <si>
+    <t>136520254</t>
+  </si>
+  <si>
+    <t>136520768</t>
+  </si>
+  <si>
+    <t>136522519</t>
+  </si>
+  <si>
+    <t>136522998</t>
+  </si>
+  <si>
+    <t>136525033</t>
+  </si>
+  <si>
+    <t>136525322</t>
+  </si>
+  <si>
+    <t>136527086</t>
+  </si>
+  <si>
+    <t>136528348</t>
+  </si>
+  <si>
+    <t>136528852</t>
+  </si>
+  <si>
+    <t>136529597</t>
+  </si>
+  <si>
+    <t>136529658</t>
+  </si>
+  <si>
+    <t>136531701</t>
+  </si>
+  <si>
+    <t>136536586</t>
+  </si>
+  <si>
+    <t>136532440</t>
+  </si>
+  <si>
+    <t>136533509</t>
+  </si>
+  <si>
+    <t>136534152</t>
+  </si>
+  <si>
+    <t>136534953</t>
+  </si>
+  <si>
+    <t>136535390</t>
+  </si>
+  <si>
+    <t>136536595</t>
+  </si>
+  <si>
+    <t>136536940</t>
+  </si>
+  <si>
+    <t>136537571</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 03.02.2026</t>
   </si>
 </sst>
 </file>
@@ -533,7 +530,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -574,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -592,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -610,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -628,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -646,7 +643,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -664,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -682,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -700,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -718,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -736,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -754,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -772,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -790,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -808,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -826,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -844,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -862,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -880,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -898,7 +895,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -916,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -934,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -952,30 +949,12 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83610AF-E896-40B6-9E66-8E3B6CDDC3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE00D6D-58C0-4960-BA98-3C41D2F8DFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,79 +51,94 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136520229</t>
+    <t>136545806</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 03.02.2026</t>
-  </si>
-  <si>
-    <t>136520254</t>
-  </si>
-  <si>
-    <t>136520768</t>
-  </si>
-  <si>
-    <t>136522519</t>
-  </si>
-  <si>
-    <t>136522998</t>
-  </si>
-  <si>
-    <t>136525033</t>
-  </si>
-  <si>
-    <t>136525322</t>
-  </si>
-  <si>
-    <t>136527086</t>
-  </si>
-  <si>
-    <t>136528348</t>
-  </si>
-  <si>
-    <t>136528852</t>
-  </si>
-  <si>
-    <t>136529597</t>
-  </si>
-  <si>
-    <t>136529658</t>
-  </si>
-  <si>
-    <t>136531701</t>
-  </si>
-  <si>
-    <t>136536586</t>
-  </si>
-  <si>
-    <t>136532440</t>
-  </si>
-  <si>
-    <t>136533509</t>
-  </si>
-  <si>
-    <t>136534152</t>
-  </si>
-  <si>
-    <t>136534953</t>
-  </si>
-  <si>
-    <t>136535390</t>
-  </si>
-  <si>
-    <t>136536595</t>
-  </si>
-  <si>
-    <t>136536940</t>
-  </si>
-  <si>
-    <t>136537571</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 03.02.2026</t>
+    <t>Bloqueios Honda 04.02.2026</t>
+  </si>
+  <si>
+    <t>136541441</t>
+  </si>
+  <si>
+    <t>136541976</t>
+  </si>
+  <si>
+    <t>136543217</t>
+  </si>
+  <si>
+    <t>136545001</t>
+  </si>
+  <si>
+    <t>136545824</t>
+  </si>
+  <si>
+    <t>133897994</t>
+  </si>
+  <si>
+    <t>136547202</t>
+  </si>
+  <si>
+    <t>136547694</t>
+  </si>
+  <si>
+    <t>136549542</t>
+  </si>
+  <si>
+    <t>136551893</t>
+  </si>
+  <si>
+    <t>136552481</t>
+  </si>
+  <si>
+    <t>136552087</t>
+  </si>
+  <si>
+    <t>136552065</t>
+  </si>
+  <si>
+    <t>136553550</t>
+  </si>
+  <si>
+    <t>136554239</t>
+  </si>
+  <si>
+    <t>136554510</t>
+  </si>
+  <si>
+    <t>136556313</t>
+  </si>
+  <si>
+    <t>136555368</t>
+  </si>
+  <si>
+    <t>136555672</t>
+  </si>
+  <si>
+    <t>136556543</t>
+  </si>
+  <si>
+    <t>136556540</t>
+  </si>
+  <si>
+    <t>136558423</t>
+  </si>
+  <si>
+    <t>136558464</t>
+  </si>
+  <si>
+    <t>136558614</t>
+  </si>
+  <si>
+    <t>136558772</t>
+  </si>
+  <si>
+    <t>136559262</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 04.02.2026</t>
   </si>
 </sst>
 </file>
@@ -530,7 +545,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,7 +622,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,7 +712,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,7 +730,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,7 +802,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -823,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -841,7 +856,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -877,7 +892,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,7 +910,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -931,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -949,12 +964,100 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE00D6D-58C0-4960-BA98-3C41D2F8DFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,96 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136545806</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 04.02.2026</t>
-  </si>
-  <si>
-    <t>136541441</t>
-  </si>
-  <si>
-    <t>136541976</t>
-  </si>
-  <si>
-    <t>136543217</t>
-  </si>
-  <si>
-    <t>136545001</t>
-  </si>
-  <si>
-    <t>136545824</t>
-  </si>
-  <si>
-    <t>133897994</t>
-  </si>
-  <si>
-    <t>136547202</t>
-  </si>
-  <si>
-    <t>136547694</t>
-  </si>
-  <si>
-    <t>136549542</t>
-  </si>
-  <si>
-    <t>136551893</t>
-  </si>
-  <si>
-    <t>136552481</t>
-  </si>
-  <si>
-    <t>136552087</t>
-  </si>
-  <si>
-    <t>136552065</t>
-  </si>
-  <si>
-    <t>136553550</t>
-  </si>
-  <si>
-    <t>136554239</t>
-  </si>
-  <si>
-    <t>136554510</t>
-  </si>
-  <si>
-    <t>136556313</t>
-  </si>
-  <si>
-    <t>136555368</t>
-  </si>
-  <si>
-    <t>136555672</t>
-  </si>
-  <si>
-    <t>136556543</t>
-  </si>
-  <si>
-    <t>136556540</t>
-  </si>
-  <si>
-    <t>136558423</t>
-  </si>
-  <si>
-    <t>136558464</t>
-  </si>
-  <si>
-    <t>136558614</t>
-  </si>
-  <si>
-    <t>136558772</t>
-  </si>
-  <si>
-    <t>136559262</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 04.02.2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +455,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -576,488 +486,110 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="C8" s="6"/>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1073,31 +605,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F691382-7579-4B9D-9F97-9161675CB9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,75 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136566293</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 05.02.2026</t>
+  </si>
+  <si>
+    <t>136562768</t>
+  </si>
+  <si>
+    <t>136564871</t>
+  </si>
+  <si>
+    <t>136565160</t>
+  </si>
+  <si>
+    <t>136567743</t>
+  </si>
+  <si>
+    <t>136567571</t>
+  </si>
+  <si>
+    <t>136577588</t>
+  </si>
+  <si>
+    <t>136570496</t>
+  </si>
+  <si>
+    <t>136579113</t>
+  </si>
+  <si>
+    <t>136572470</t>
+  </si>
+  <si>
+    <t>136573137</t>
+  </si>
+  <si>
+    <t>136574313</t>
+  </si>
+  <si>
+    <t>136575921</t>
+  </si>
+  <si>
+    <t>136577134</t>
+  </si>
+  <si>
+    <t>136577718</t>
+  </si>
+  <si>
+    <t>136579066</t>
+  </si>
+  <si>
+    <t>136579392</t>
+  </si>
+  <si>
+    <t>136580085</t>
+  </si>
+  <si>
+    <t>136561640</t>
+  </si>
+  <si>
+    <t>136561873</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 05.02.2026</t>
   </si>
 </sst>
 </file>
@@ -455,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +555,364 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
-    </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -605,31 +928,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F691382-7579-4B9D-9F97-9161675CB9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D850C7B-4B12-47F7-9C01-80ED21FE944D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="58">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,80 +51,164 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136566293</t>
+    <t>136586549</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 05.02.2026</t>
-  </si>
-  <si>
-    <t>136562768</t>
-  </si>
-  <si>
-    <t>136564871</t>
-  </si>
-  <si>
-    <t>136565160</t>
-  </si>
-  <si>
-    <t>136567743</t>
-  </si>
-  <si>
-    <t>136567571</t>
-  </si>
-  <si>
-    <t>136577588</t>
-  </si>
-  <si>
-    <t>136570496</t>
-  </si>
-  <si>
-    <t>136579113</t>
-  </si>
-  <si>
-    <t>136572470</t>
-  </si>
-  <si>
-    <t>136573137</t>
-  </si>
-  <si>
-    <t>136574313</t>
-  </si>
-  <si>
-    <t>136575921</t>
-  </si>
-  <si>
-    <t>136577134</t>
-  </si>
-  <si>
-    <t>136577718</t>
-  </si>
-  <si>
-    <t>136579066</t>
-  </si>
-  <si>
-    <t>136579392</t>
-  </si>
-  <si>
-    <t>136580085</t>
-  </si>
-  <si>
-    <t>136561640</t>
-  </si>
-  <si>
-    <t>136561873</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 05.02.2026</t>
+    <t>Bloqueios Honda  29.11.2025</t>
+  </si>
+  <si>
+    <t>136587680</t>
+  </si>
+  <si>
+    <t>136591023</t>
+  </si>
+  <si>
+    <t>136593143</t>
+  </si>
+  <si>
+    <t>136594528</t>
+  </si>
+  <si>
+    <t>136595169</t>
+  </si>
+  <si>
+    <t>136597814</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  06.02.2026</t>
+  </si>
+  <si>
+    <t>136599021</t>
+  </si>
+  <si>
+    <t>136599586</t>
+  </si>
+  <si>
+    <t>136601000</t>
+  </si>
+  <si>
+    <t>136602075</t>
+  </si>
+  <si>
+    <t>136605557</t>
+  </si>
+  <si>
+    <t>136602867</t>
+  </si>
+  <si>
+    <t>136607632</t>
+  </si>
+  <si>
+    <t>136604307</t>
+  </si>
+  <si>
+    <t>136604967</t>
+  </si>
+  <si>
+    <t>136608183</t>
+  </si>
+  <si>
+    <t>136608187</t>
+  </si>
+  <si>
+    <t>136608599</t>
+  </si>
+  <si>
+    <t>136608541</t>
+  </si>
+  <si>
+    <t>136609141</t>
+  </si>
+  <si>
+    <t>136610983</t>
+  </si>
+  <si>
+    <t>136611087</t>
+  </si>
+  <si>
+    <t>136601473</t>
+  </si>
+  <si>
+    <t>136587939</t>
+  </si>
+  <si>
+    <t>136591555</t>
+  </si>
+  <si>
+    <t>136591323</t>
+  </si>
+  <si>
+    <t>136591433</t>
+  </si>
+  <si>
+    <t>136597142</t>
+  </si>
+  <si>
+    <t>136607945</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 06.02.2026</t>
+  </si>
+  <si>
+    <t>136614756</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  07.02.2026</t>
+  </si>
+  <si>
+    <t>136615082</t>
+  </si>
+  <si>
+    <t>136615290</t>
+  </si>
+  <si>
+    <t>136616498</t>
+  </si>
+  <si>
+    <t>136617298</t>
+  </si>
+  <si>
+    <t>136619074</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 07.02.2026</t>
+  </si>
+  <si>
+    <t>135595844</t>
+  </si>
+  <si>
+    <t>135595524</t>
+  </si>
+  <si>
+    <t>135612243</t>
+  </si>
+  <si>
+    <t>135621231</t>
+  </si>
+  <si>
+    <t>135623225</t>
+  </si>
+  <si>
+    <t>135623181</t>
+  </si>
+  <si>
+    <t>136626843</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  08.02.2026</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 08.02.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,14 +226,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -187,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -202,9 +278,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -524,7 +597,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -565,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -583,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -601,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -619,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -637,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -655,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -669,250 +742,627 @@
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>9</v>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
+      <c r="D43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86B95D3-721F-4A20-AB3B-443EA55B4E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,75 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136635040</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 09.02.2026</t>
+  </si>
+  <si>
+    <t>136634811</t>
+  </si>
+  <si>
+    <t>136636398</t>
+  </si>
+  <si>
+    <t>136635979</t>
+  </si>
+  <si>
+    <t>136636159</t>
+  </si>
+  <si>
+    <t>136636934</t>
+  </si>
+  <si>
+    <t>136637781</t>
+  </si>
+  <si>
+    <t>136639750</t>
+  </si>
+  <si>
+    <t>136641819</t>
+  </si>
+  <si>
+    <t>136642907</t>
+  </si>
+  <si>
+    <t>136644056</t>
+  </si>
+  <si>
+    <t>136645203</t>
+  </si>
+  <si>
+    <t>136645562</t>
+  </si>
+  <si>
+    <t>136650513</t>
+  </si>
+  <si>
+    <t>136650710</t>
+  </si>
+  <si>
+    <t>136651604</t>
+  </si>
+  <si>
+    <t>136651970</t>
+  </si>
+  <si>
+    <t>136655830</t>
+  </si>
+  <si>
+    <t>136655910</t>
+  </si>
+  <si>
+    <t>136654623</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 09.02.2026</t>
   </si>
 </sst>
 </file>
@@ -455,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +555,367 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
-    </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -605,31 +931,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86B95D3-721F-4A20-AB3B-443EA55B4E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188DD526-9811-4B42-83D2-864B7CE7C22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,73 +51,88 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136635040</t>
+    <t>136686831</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 09.02.2026</t>
-  </si>
-  <si>
-    <t>136634811</t>
-  </si>
-  <si>
-    <t>136636398</t>
-  </si>
-  <si>
-    <t>136635979</t>
-  </si>
-  <si>
-    <t>136636159</t>
-  </si>
-  <si>
-    <t>136636934</t>
-  </si>
-  <si>
-    <t>136637781</t>
-  </si>
-  <si>
-    <t>136639750</t>
-  </si>
-  <si>
-    <t>136641819</t>
-  </si>
-  <si>
-    <t>136642907</t>
-  </si>
-  <si>
-    <t>136644056</t>
-  </si>
-  <si>
-    <t>136645203</t>
-  </si>
-  <si>
-    <t>136645562</t>
-  </si>
-  <si>
-    <t>136650513</t>
-  </si>
-  <si>
-    <t>136650710</t>
-  </si>
-  <si>
-    <t>136651604</t>
-  </si>
-  <si>
-    <t>136651970</t>
-  </si>
-  <si>
-    <t>136655830</t>
-  </si>
-  <si>
-    <t>136655910</t>
-  </si>
-  <si>
-    <t>136654623</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 09.02.2026</t>
+    <t>Bloqueios Honda 10.02.2026</t>
+  </si>
+  <si>
+    <t>136681623</t>
+  </si>
+  <si>
+    <t>136666899</t>
+  </si>
+  <si>
+    <t>136667194</t>
+  </si>
+  <si>
+    <t>136670762</t>
+  </si>
+  <si>
+    <t>136667357</t>
+  </si>
+  <si>
+    <t>136669265</t>
+  </si>
+  <si>
+    <t>136671578</t>
+  </si>
+  <si>
+    <t>136686039</t>
+  </si>
+  <si>
+    <t>136678048</t>
+  </si>
+  <si>
+    <t>136679190</t>
+  </si>
+  <si>
+    <t>136681644</t>
+  </si>
+  <si>
+    <t>136681652</t>
+  </si>
+  <si>
+    <t>136685592</t>
+  </si>
+  <si>
+    <t>136687429</t>
+  </si>
+  <si>
+    <t>136685582</t>
+  </si>
+  <si>
+    <t>136686008</t>
+  </si>
+  <si>
+    <t>136686372</t>
+  </si>
+  <si>
+    <t>136687105</t>
+  </si>
+  <si>
+    <t>136687280</t>
+  </si>
+  <si>
+    <t>136687303</t>
+  </si>
+  <si>
+    <t>136688324</t>
+  </si>
+  <si>
+    <t>136688847</t>
+  </si>
+  <si>
+    <t>136690649</t>
+  </si>
+  <si>
+    <t>136690773</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 10.02.2026</t>
   </si>
 </sst>
 </file>
@@ -524,7 +539,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -565,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -583,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -601,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -619,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -637,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -655,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -673,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -691,7 +706,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -709,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -727,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -745,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -763,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -781,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -799,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -817,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -835,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -853,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -871,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -889,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -907,15 +922,102 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188DD526-9811-4B42-83D2-864B7CE7C22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A893A3A9-4207-44AC-972C-320964167EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,88 +51,94 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136686831</t>
+    <t>BLOQUEIOS HONDA 11.02.2026</t>
+  </si>
+  <si>
+    <t>136694138</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 10.02.2026</t>
-  </si>
-  <si>
-    <t>136681623</t>
-  </si>
-  <si>
-    <t>136666899</t>
-  </si>
-  <si>
-    <t>136667194</t>
-  </si>
-  <si>
-    <t>136670762</t>
-  </si>
-  <si>
-    <t>136667357</t>
-  </si>
-  <si>
-    <t>136669265</t>
-  </si>
-  <si>
-    <t>136671578</t>
-  </si>
-  <si>
-    <t>136686039</t>
-  </si>
-  <si>
-    <t>136678048</t>
-  </si>
-  <si>
-    <t>136679190</t>
-  </si>
-  <si>
-    <t>136681644</t>
-  </si>
-  <si>
-    <t>136681652</t>
-  </si>
-  <si>
-    <t>136685592</t>
-  </si>
-  <si>
-    <t>136687429</t>
-  </si>
-  <si>
-    <t>136685582</t>
-  </si>
-  <si>
-    <t>136686008</t>
-  </si>
-  <si>
-    <t>136686372</t>
-  </si>
-  <si>
-    <t>136687105</t>
-  </si>
-  <si>
-    <t>136687280</t>
-  </si>
-  <si>
-    <t>136687303</t>
-  </si>
-  <si>
-    <t>136688324</t>
-  </si>
-  <si>
-    <t>136688847</t>
-  </si>
-  <si>
-    <t>136690649</t>
-  </si>
-  <si>
-    <t>136690773</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 10.02.2026</t>
+    <t>Bloqueios Honda 11.02.2026</t>
+  </si>
+  <si>
+    <t>136694221</t>
+  </si>
+  <si>
+    <t>136704381</t>
+  </si>
+  <si>
+    <t>136695493</t>
+  </si>
+  <si>
+    <t>136697344</t>
+  </si>
+  <si>
+    <t>136699345</t>
+  </si>
+  <si>
+    <t>136704060</t>
+  </si>
+  <si>
+    <t>136702262</t>
+  </si>
+  <si>
+    <t>133793066</t>
+  </si>
+  <si>
+    <t>136704506</t>
+  </si>
+  <si>
+    <t>136705996</t>
+  </si>
+  <si>
+    <t>136707689</t>
+  </si>
+  <si>
+    <t>136708959</t>
+  </si>
+  <si>
+    <t>136709165</t>
+  </si>
+  <si>
+    <t>136711830</t>
+  </si>
+  <si>
+    <t>136543184</t>
+  </si>
+  <si>
+    <t>136712542</t>
+  </si>
+  <si>
+    <t>136712690</t>
+  </si>
+  <si>
+    <t>136698466</t>
+  </si>
+  <si>
+    <t>136698532</t>
+  </si>
+  <si>
+    <t>136698798</t>
+  </si>
+  <si>
+    <t>136705823</t>
+  </si>
+  <si>
+    <t>136706727</t>
+  </si>
+  <si>
+    <t>136711541</t>
+  </si>
+  <si>
+    <t>136707634</t>
+  </si>
+  <si>
+    <t>136709437</t>
+  </si>
+  <si>
+    <t>133980729</t>
   </si>
 </sst>
 </file>
@@ -539,7 +545,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -571,16 +577,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,16 +595,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,16 +613,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,16 +631,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,16 +649,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,16 +667,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,16 +685,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,16 +703,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,16 +721,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,16 +739,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,16 +757,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,16 +775,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,16 +793,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,16 +811,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -823,16 +829,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -841,16 +847,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,16 +865,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -877,16 +883,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,16 +901,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,16 +919,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -931,16 +937,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -949,16 +955,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -967,16 +973,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -985,16 +991,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1003,21 +1009,55 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A893A3A9-4207-44AC-972C-320964167EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A907B6-1E3C-49D2-BF76-A2B9D2256723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,94 +51,88 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 11.02.2026</t>
-  </si>
-  <si>
-    <t>136694138</t>
+    <t>136715939</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 11.02.2026</t>
-  </si>
-  <si>
-    <t>136694221</t>
-  </si>
-  <si>
-    <t>136704381</t>
-  </si>
-  <si>
-    <t>136695493</t>
-  </si>
-  <si>
-    <t>136697344</t>
-  </si>
-  <si>
-    <t>136699345</t>
-  </si>
-  <si>
-    <t>136704060</t>
-  </si>
-  <si>
-    <t>136702262</t>
-  </si>
-  <si>
-    <t>133793066</t>
-  </si>
-  <si>
-    <t>136704506</t>
-  </si>
-  <si>
-    <t>136705996</t>
-  </si>
-  <si>
-    <t>136707689</t>
-  </si>
-  <si>
-    <t>136708959</t>
-  </si>
-  <si>
-    <t>136709165</t>
-  </si>
-  <si>
-    <t>136711830</t>
-  </si>
-  <si>
-    <t>136543184</t>
-  </si>
-  <si>
-    <t>136712542</t>
-  </si>
-  <si>
-    <t>136712690</t>
-  </si>
-  <si>
-    <t>136698466</t>
-  </si>
-  <si>
-    <t>136698532</t>
-  </si>
-  <si>
-    <t>136698798</t>
-  </si>
-  <si>
-    <t>136705823</t>
-  </si>
-  <si>
-    <t>136706727</t>
-  </si>
-  <si>
-    <t>136711541</t>
-  </si>
-  <si>
-    <t>136707634</t>
-  </si>
-  <si>
-    <t>136709437</t>
-  </si>
-  <si>
-    <t>133980729</t>
+    <t>Bloqueios Honda 12.02.2026</t>
+  </si>
+  <si>
+    <t>136716030</t>
+  </si>
+  <si>
+    <t>136716066</t>
+  </si>
+  <si>
+    <t>136716804</t>
+  </si>
+  <si>
+    <t>136716989</t>
+  </si>
+  <si>
+    <t>136717422</t>
+  </si>
+  <si>
+    <t>136717935</t>
+  </si>
+  <si>
+    <t>136720468</t>
+  </si>
+  <si>
+    <t>136720448</t>
+  </si>
+  <si>
+    <t>136719120</t>
+  </si>
+  <si>
+    <t>136716137</t>
+  </si>
+  <si>
+    <t>136720357</t>
+  </si>
+  <si>
+    <t>133217176</t>
+  </si>
+  <si>
+    <t>136721963</t>
+  </si>
+  <si>
+    <t>136723575</t>
+  </si>
+  <si>
+    <t>136724189</t>
+  </si>
+  <si>
+    <t>136724235</t>
+  </si>
+  <si>
+    <t>136736201</t>
+  </si>
+  <si>
+    <t>136726435</t>
+  </si>
+  <si>
+    <t>136727056</t>
+  </si>
+  <si>
+    <t>136734032</t>
+  </si>
+  <si>
+    <t>136730831</t>
+  </si>
+  <si>
+    <t>136732672</t>
+  </si>
+  <si>
+    <t>136734487</t>
+  </si>
+  <si>
+    <t>136735693</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 12.02.2026</t>
   </si>
 </sst>
 </file>
@@ -545,7 +539,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -577,16 +571,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,16 +589,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,16 +607,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,16 +625,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,16 +643,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,16 +661,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,16 +679,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,16 +697,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,16 +715,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,16 +733,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,16 +751,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,16 +769,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -793,16 +787,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,16 +805,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -829,16 +823,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -847,16 +841,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -865,16 +859,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -883,16 +877,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -901,16 +895,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -919,16 +913,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -937,16 +931,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -955,16 +949,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -973,16 +967,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -991,16 +985,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1009,55 +1003,21 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0C8C88-1CE2-4CD1-9B48-6298AD0D0479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="77">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,216 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136769994</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 16.02.2026</t>
+  </si>
+  <si>
+    <t>136770129</t>
+  </si>
+  <si>
+    <t>136770876</t>
+  </si>
+  <si>
+    <t>136771405</t>
+  </si>
+  <si>
+    <t>136771846</t>
+  </si>
+  <si>
+    <t>136768663</t>
+  </si>
+  <si>
+    <t>136770441</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 16.02.2026</t>
+  </si>
+  <si>
+    <t>136766087</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 14.02.2026</t>
+  </si>
+  <si>
+    <t>136766101</t>
+  </si>
+  <si>
+    <t>136766513</t>
+  </si>
+  <si>
+    <t>136766127</t>
+  </si>
+  <si>
+    <t>136766691</t>
+  </si>
+  <si>
+    <t>136766722</t>
+  </si>
+  <si>
+    <t>136766154</t>
+  </si>
+  <si>
+    <t>136767231</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 14.02.2026</t>
+  </si>
+  <si>
+    <t>136740974</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 13.02.2026</t>
+  </si>
+  <si>
+    <t>136742561</t>
+  </si>
+  <si>
+    <t>136756371</t>
+  </si>
+  <si>
+    <t>136749324</t>
+  </si>
+  <si>
+    <t>136747292</t>
+  </si>
+  <si>
+    <t>136270998</t>
+  </si>
+  <si>
+    <t>136760895</t>
+  </si>
+  <si>
+    <t>136747970</t>
+  </si>
+  <si>
+    <t>136752295</t>
+  </si>
+  <si>
+    <t>136752645</t>
+  </si>
+  <si>
+    <t>136753658</t>
+  </si>
+  <si>
+    <t>136755753</t>
+  </si>
+  <si>
+    <t>136760486</t>
+  </si>
+  <si>
+    <t>136757631</t>
+  </si>
+  <si>
+    <t>136758890</t>
+  </si>
+  <si>
+    <t>136759708</t>
+  </si>
+  <si>
+    <t>136759651</t>
+  </si>
+  <si>
+    <t>136759704</t>
+  </si>
+  <si>
+    <t>136057163</t>
+  </si>
+  <si>
+    <t>136762700</t>
+  </si>
+  <si>
+    <t>136762984</t>
+  </si>
+  <si>
+    <t>136758165</t>
+  </si>
+  <si>
+    <t>136759553</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 13.02.2026</t>
+  </si>
+  <si>
+    <t>136776574</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 18.02.2026</t>
+  </si>
+  <si>
+    <t>136776702</t>
+  </si>
+  <si>
+    <t>136777453</t>
+  </si>
+  <si>
+    <t>136778475</t>
+  </si>
+  <si>
+    <t>136779409</t>
+  </si>
+  <si>
+    <t>136779106</t>
+  </si>
+  <si>
+    <t>136780983</t>
+  </si>
+  <si>
+    <t>136781149</t>
+  </si>
+  <si>
+    <t>136781143</t>
+  </si>
+  <si>
+    <t>136783841</t>
+  </si>
+  <si>
+    <t>136784573</t>
+  </si>
+  <si>
+    <t>136784169</t>
+  </si>
+  <si>
+    <t>136784477</t>
+  </si>
+  <si>
+    <t>136786681</t>
+  </si>
+  <si>
+    <t>136786736</t>
+  </si>
+  <si>
+    <t>136787501</t>
+  </si>
+  <si>
+    <t>136788520</t>
+  </si>
+  <si>
+    <t>136789311</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 18.02.2026</t>
+  </si>
+  <si>
+    <t>136774124</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 17.02.2026</t>
+  </si>
+  <si>
+    <t>136774252</t>
+  </si>
+  <si>
+    <t>132616741</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 17.02.2026</t>
   </si>
 </sst>
 </file>
@@ -455,7 +665,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +696,1032 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -605,31 +1737,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375C8FD1-1391-4DBA-BD88-02720029D64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,108 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136793903</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 19.02.2026</t>
+  </si>
+  <si>
+    <t>136792464</t>
+  </si>
+  <si>
+    <t>136792758</t>
+  </si>
+  <si>
+    <t>136793219</t>
+  </si>
+  <si>
+    <t>136804016</t>
+  </si>
+  <si>
+    <t>136794330</t>
+  </si>
+  <si>
+    <t>136794089</t>
+  </si>
+  <si>
+    <t>136794438</t>
+  </si>
+  <si>
+    <t>136798482</t>
+  </si>
+  <si>
+    <t>136798520</t>
+  </si>
+  <si>
+    <t>136795924</t>
+  </si>
+  <si>
+    <t>136797730</t>
+  </si>
+  <si>
+    <t>136799782</t>
+  </si>
+  <si>
+    <t>136798119</t>
+  </si>
+  <si>
+    <t>136799211</t>
+  </si>
+  <si>
+    <t>136800289</t>
+  </si>
+  <si>
+    <t>136807476</t>
+  </si>
+  <si>
+    <t>136803722</t>
+  </si>
+  <si>
+    <t>136803432</t>
+  </si>
+  <si>
+    <t>136803648</t>
+  </si>
+  <si>
+    <t>136803875</t>
+  </si>
+  <si>
+    <t>136805562</t>
+  </si>
+  <si>
+    <t>136804844</t>
+  </si>
+  <si>
+    <t>136805429</t>
+  </si>
+  <si>
+    <t>136806378</t>
+  </si>
+  <si>
+    <t>136806970</t>
+  </si>
+  <si>
+    <t>136807254</t>
+  </si>
+  <si>
+    <t>136807942</t>
+  </si>
+  <si>
+    <t>136807685</t>
+  </si>
+  <si>
+    <t>136807820</t>
+  </si>
+  <si>
+    <t>136809430</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 19.02.2026</t>
   </si>
 </sst>
 </file>
@@ -455,7 +557,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +588,556 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -605,31 +1153,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216B7A71-C29E-40FA-A575-753875B4547F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="28">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,69 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136837279</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 23.02.2026</t>
+  </si>
+  <si>
+    <t>136837466</t>
+  </si>
+  <si>
+    <t>136844329</t>
+  </si>
+  <si>
+    <t>136837667</t>
+  </si>
+  <si>
+    <t>136845045</t>
+  </si>
+  <si>
+    <t>136837963</t>
+  </si>
+  <si>
+    <t>136838111</t>
+  </si>
+  <si>
+    <t>136838296</t>
+  </si>
+  <si>
+    <t>136839698</t>
+  </si>
+  <si>
+    <t>136845047</t>
+  </si>
+  <si>
+    <t>136841675</t>
+  </si>
+  <si>
+    <t>136843115</t>
+  </si>
+  <si>
+    <t>136842745</t>
+  </si>
+  <si>
+    <t>136844747</t>
+  </si>
+  <si>
+    <t>136846228</t>
+  </si>
+  <si>
+    <t>136846389</t>
+  </si>
+  <si>
+    <t>136846633</t>
+  </si>
+  <si>
+    <t>136837257</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 23.02.2026</t>
   </si>
 </sst>
 </file>
@@ -486,109 +549,348 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
   </sheetData>
@@ -605,31 +907,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216B7A71-C29E-40FA-A575-753875B4547F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0798B40D-51AC-4196-AD6E-C8161A7C43AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,67 +51,121 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136837279</t>
+    <t>136863543</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 23.02.2026</t>
-  </si>
-  <si>
-    <t>136837466</t>
-  </si>
-  <si>
-    <t>136844329</t>
-  </si>
-  <si>
-    <t>136837667</t>
-  </si>
-  <si>
-    <t>136845045</t>
-  </si>
-  <si>
-    <t>136837963</t>
-  </si>
-  <si>
-    <t>136838111</t>
-  </si>
-  <si>
-    <t>136838296</t>
-  </si>
-  <si>
-    <t>136839698</t>
-  </si>
-  <si>
-    <t>136845047</t>
-  </si>
-  <si>
-    <t>136841675</t>
-  </si>
-  <si>
-    <t>136843115</t>
-  </si>
-  <si>
-    <t>136842745</t>
-  </si>
-  <si>
-    <t>136844747</t>
-  </si>
-  <si>
-    <t>136846228</t>
-  </si>
-  <si>
-    <t>136846389</t>
-  </si>
-  <si>
-    <t>136846633</t>
-  </si>
-  <si>
-    <t>136837257</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 23.02.2026</t>
+    <t>Bloqueios Honda 24.02.2026</t>
+  </si>
+  <si>
+    <t>136850734</t>
+  </si>
+  <si>
+    <t>136850915</t>
+  </si>
+  <si>
+    <t>136850896</t>
+  </si>
+  <si>
+    <t>136850888</t>
+  </si>
+  <si>
+    <t>136852907</t>
+  </si>
+  <si>
+    <t>136851902</t>
+  </si>
+  <si>
+    <t>136853947</t>
+  </si>
+  <si>
+    <t>136853942</t>
+  </si>
+  <si>
+    <t>136854681</t>
+  </si>
+  <si>
+    <t>136857577</t>
+  </si>
+  <si>
+    <t>136858207</t>
+  </si>
+  <si>
+    <t>136858037</t>
+  </si>
+  <si>
+    <t>136859425</t>
+  </si>
+  <si>
+    <t>136859897</t>
+  </si>
+  <si>
+    <t>136859889</t>
+  </si>
+  <si>
+    <t>136856623</t>
+  </si>
+  <si>
+    <t>136857484</t>
+  </si>
+  <si>
+    <t>136856706</t>
+  </si>
+  <si>
+    <t>136863862</t>
+  </si>
+  <si>
+    <t>136864763</t>
+  </si>
+  <si>
+    <t>136864927</t>
+  </si>
+  <si>
+    <t>136868062</t>
+  </si>
+  <si>
+    <t>136865564</t>
+  </si>
+  <si>
+    <t>136865643</t>
+  </si>
+  <si>
+    <t>136868119</t>
+  </si>
+  <si>
+    <t>136866523</t>
+  </si>
+  <si>
+    <t>136867328</t>
+  </si>
+  <si>
+    <t>136867659</t>
+  </si>
+  <si>
+    <t>136869304</t>
+  </si>
+  <si>
+    <t>136868996</t>
+  </si>
+  <si>
+    <t>136869272</t>
+  </si>
+  <si>
+    <t>136869807</t>
+  </si>
+  <si>
+    <t>136870185</t>
+  </si>
+  <si>
+    <t>136871192</t>
+  </si>
+  <si>
+    <t>136871659</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 24.02.2026</t>
   </si>
 </sst>
 </file>
@@ -518,7 +572,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -559,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -577,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -595,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -613,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -631,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -649,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -667,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -685,7 +739,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -703,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -721,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -739,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -757,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -775,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -793,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -811,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -829,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -847,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -865,33 +919,325 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1DB28889-AA36-4690-9DCC-7FD7D2233760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B2506E-30FF-48F0-84CE-E3A62C978842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDFC634-219E-447B-9B0A-71D946DB5AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,105 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.02.2026</t>
+  </si>
+  <si>
+    <t>136880371</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 25.02.2026</t>
+  </si>
+  <si>
+    <t>136881281</t>
+  </si>
+  <si>
+    <t>136881298</t>
+  </si>
+  <si>
+    <t>136883133</t>
+  </si>
+  <si>
+    <t>136886733</t>
+  </si>
+  <si>
+    <t>136883684</t>
+  </si>
+  <si>
+    <t>136884352</t>
+  </si>
+  <si>
+    <t>136886701</t>
+  </si>
+  <si>
+    <t>136888246</t>
+  </si>
+  <si>
+    <t>136887953</t>
+  </si>
+  <si>
+    <t>136888048</t>
+  </si>
+  <si>
+    <t>136888123</t>
+  </si>
+  <si>
+    <t>136889440</t>
+  </si>
+  <si>
+    <t>136890591</t>
+  </si>
+  <si>
+    <t>136873315</t>
+  </si>
+  <si>
+    <t>136890421</t>
+  </si>
+  <si>
+    <t>136874772</t>
+  </si>
+  <si>
+    <t>136878648</t>
+  </si>
+  <si>
+    <t>136886478</t>
+  </si>
+  <si>
+    <t>136878221</t>
+  </si>
+  <si>
+    <t>136875535</t>
+  </si>
+  <si>
+    <t>136876672</t>
+  </si>
+  <si>
+    <t>136876836</t>
+  </si>
+  <si>
+    <t>136877468</t>
+  </si>
+  <si>
+    <t>136877430</t>
+  </si>
+  <si>
+    <t>136877378</t>
+  </si>
+  <si>
+    <t>136878778</t>
+  </si>
+  <si>
+    <t>136879156</t>
+  </si>
+  <si>
+    <t>136873739</t>
+  </si>
+  <si>
+    <t>136873332</t>
   </si>
 </sst>
 </file>
@@ -455,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -486,110 +585,539 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDFC634-219E-447B-9B0A-71D946DB5AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A636030A-653F-4222-BFA0-5786307B1922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,103 +51,73 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 25.02.2026</t>
-  </si>
-  <si>
-    <t>136880371</t>
+    <t>136905270</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 25.02.2026</t>
-  </si>
-  <si>
-    <t>136881281</t>
-  </si>
-  <si>
-    <t>136881298</t>
-  </si>
-  <si>
-    <t>136883133</t>
-  </si>
-  <si>
-    <t>136886733</t>
-  </si>
-  <si>
-    <t>136883684</t>
-  </si>
-  <si>
-    <t>136884352</t>
-  </si>
-  <si>
-    <t>136886701</t>
-  </si>
-  <si>
-    <t>136888246</t>
-  </si>
-  <si>
-    <t>136887953</t>
-  </si>
-  <si>
-    <t>136888048</t>
-  </si>
-  <si>
-    <t>136888123</t>
-  </si>
-  <si>
-    <t>136889440</t>
-  </si>
-  <si>
-    <t>136890591</t>
-  </si>
-  <si>
-    <t>136873315</t>
-  </si>
-  <si>
-    <t>136890421</t>
-  </si>
-  <si>
-    <t>136874772</t>
-  </si>
-  <si>
-    <t>136878648</t>
-  </si>
-  <si>
-    <t>136886478</t>
-  </si>
-  <si>
-    <t>136878221</t>
-  </si>
-  <si>
-    <t>136875535</t>
-  </si>
-  <si>
-    <t>136876672</t>
-  </si>
-  <si>
-    <t>136876836</t>
-  </si>
-  <si>
-    <t>136877468</t>
-  </si>
-  <si>
-    <t>136877430</t>
-  </si>
-  <si>
-    <t>136877378</t>
-  </si>
-  <si>
-    <t>136878778</t>
-  </si>
-  <si>
-    <t>136879156</t>
-  </si>
-  <si>
-    <t>136873739</t>
-  </si>
-  <si>
-    <t>136873332</t>
+    <t>Bloqueios Honda 26.02.2026</t>
+  </si>
+  <si>
+    <t>136903112</t>
+  </si>
+  <si>
+    <t>136907635</t>
+  </si>
+  <si>
+    <t>136907154</t>
+  </si>
+  <si>
+    <t>136907669</t>
+  </si>
+  <si>
+    <t>136907188</t>
+  </si>
+  <si>
+    <t>136908412</t>
+  </si>
+  <si>
+    <t>136894922</t>
+  </si>
+  <si>
+    <t>136891726</t>
+  </si>
+  <si>
+    <t>136891774</t>
+  </si>
+  <si>
+    <t>136895025</t>
+  </si>
+  <si>
+    <t>136895284</t>
+  </si>
+  <si>
+    <t>136897454</t>
+  </si>
+  <si>
+    <t>136904781</t>
+  </si>
+  <si>
+    <t>136893795</t>
+  </si>
+  <si>
+    <t>136894047</t>
+  </si>
+  <si>
+    <t>136909356</t>
+  </si>
+  <si>
+    <t>136901229</t>
+  </si>
+  <si>
+    <t>136897060</t>
+  </si>
+  <si>
+    <t>136899358</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 26.02.2026</t>
   </si>
 </sst>
 </file>
@@ -554,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -586,16 +556,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -604,16 +574,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -622,16 +592,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -640,16 +610,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -658,16 +628,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -676,16 +646,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -694,16 +664,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -712,16 +682,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -730,16 +700,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -748,16 +718,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -766,16 +736,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -784,16 +754,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -802,16 +772,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -820,16 +790,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -838,16 +808,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -856,16 +826,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -874,16 +844,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -892,16 +862,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -910,16 +880,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -928,16 +898,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -945,179 +915,19 @@
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1133,31 +943,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A636030A-653F-4222-BFA0-5786307B1922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3715F97-E20B-40A7-89A0-07D32168F1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,73 +51,91 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136905270</t>
+    <t>136921526</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 26.02.2026</t>
-  </si>
-  <si>
-    <t>136903112</t>
-  </si>
-  <si>
-    <t>136907635</t>
-  </si>
-  <si>
-    <t>136907154</t>
-  </si>
-  <si>
-    <t>136907669</t>
-  </si>
-  <si>
-    <t>136907188</t>
-  </si>
-  <si>
-    <t>136908412</t>
-  </si>
-  <si>
-    <t>136894922</t>
-  </si>
-  <si>
-    <t>136891726</t>
-  </si>
-  <si>
-    <t>136891774</t>
-  </si>
-  <si>
-    <t>136895025</t>
-  </si>
-  <si>
-    <t>136895284</t>
-  </si>
-  <si>
-    <t>136897454</t>
-  </si>
-  <si>
-    <t>136904781</t>
-  </si>
-  <si>
-    <t>136893795</t>
-  </si>
-  <si>
-    <t>136894047</t>
-  </si>
-  <si>
-    <t>136909356</t>
-  </si>
-  <si>
-    <t>136901229</t>
-  </si>
-  <si>
-    <t>136897060</t>
-  </si>
-  <si>
-    <t>136899358</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 26.02.2026</t>
+    <t>Bloqueios Honda  27.02.2026</t>
+  </si>
+  <si>
+    <t>136923205</t>
+  </si>
+  <si>
+    <t>136923107</t>
+  </si>
+  <si>
+    <t>134265206</t>
+  </si>
+  <si>
+    <t>136924365</t>
+  </si>
+  <si>
+    <t>136925320</t>
+  </si>
+  <si>
+    <t>136927050</t>
+  </si>
+  <si>
+    <t>136927497</t>
+  </si>
+  <si>
+    <t>136912224</t>
+  </si>
+  <si>
+    <t>136910861</t>
+  </si>
+  <si>
+    <t>136917952</t>
+  </si>
+  <si>
+    <t>136911401</t>
+  </si>
+  <si>
+    <t>136913246</t>
+  </si>
+  <si>
+    <t>136916392</t>
+  </si>
+  <si>
+    <t>136917525</t>
+  </si>
+  <si>
+    <t>136917314</t>
+  </si>
+  <si>
+    <t>136919341</t>
+  </si>
+  <si>
+    <t>136918785</t>
+  </si>
+  <si>
+    <t>134339023</t>
+  </si>
+  <si>
+    <t>136914185</t>
+  </si>
+  <si>
+    <t>136915282</t>
+  </si>
+  <si>
+    <t>136919649</t>
+  </si>
+  <si>
+    <t>136923177</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 27.02.2026</t>
+  </si>
+  <si>
+    <t>136881080</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  28.02.2026</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 28.02.2026</t>
   </si>
 </sst>
 </file>
@@ -565,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -583,7 +601,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -601,7 +619,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -619,7 +637,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -637,7 +655,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -655,7 +673,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -673,7 +691,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -691,7 +709,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -709,7 +727,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -727,7 +745,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -745,7 +763,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -763,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -781,7 +799,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -799,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -817,7 +835,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -835,7 +853,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -853,7 +871,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -871,7 +889,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -889,7 +907,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -907,23 +925,83 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -943,31 +1021,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>